--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1235,7 +1235,7 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1501,7 +1501,7 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1843,17 +1843,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
@@ -1881,17 +1881,17 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Error</t>
         </is>
       </c>
     </row>
@@ -1962,12 +1962,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1995,12 +1995,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2831,7 +2831,7 @@
       <c r="E46" s="3" t="n"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2869,7 +2869,7 @@
       <c r="E47" s="3" t="n"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3097,7 +3097,7 @@
       <c r="E53" s="3" t="n"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3135,7 +3135,7 @@
       <c r="E54" s="3" t="n"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -4307,7 +4307,7 @@
       <c r="E84" s="3" t="n"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -4505,7 +4505,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -4538,7 +4538,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -4571,7 +4571,7 @@
       <c r="E92" s="3" t="n"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -4703,7 +4703,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -4901,7 +4901,7 @@
       <c r="E102" s="3" t="n"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -5066,7 +5066,7 @@
       <c r="E107" s="3" t="n"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -5231,7 +5231,7 @@
       <c r="E112" s="3" t="n"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -5363,7 +5363,7 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -5561,7 +5561,7 @@
       <c r="E122" s="3" t="n"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -5627,7 +5627,7 @@
       <c r="E124" s="3" t="n"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -5731,7 +5731,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -5792,7 +5792,7 @@
       <c r="E129" s="3" t="n"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -5825,7 +5825,7 @@
       <c r="E130" s="3" t="n"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -5891,7 +5891,7 @@
       <c r="E132" s="3" t="n"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -5924,7 +5924,7 @@
       <c r="E133" s="3" t="n"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -5957,7 +5957,7 @@
       <c r="E134" s="3" t="n"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -5990,7 +5990,7 @@
       <c r="E135" s="3" t="n"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -6225,7 +6225,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -6390,7 +6390,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -6588,7 +6588,7 @@
       <c r="E153" s="3" t="n"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -6687,7 +6687,7 @@
       <c r="E156" s="3" t="n"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -6918,7 +6918,7 @@
       <c r="E163" s="3" t="n"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6951,7 +6951,7 @@
       <c r="E164" s="3" t="n"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -6984,7 +6984,7 @@
       <c r="E165" s="3" t="n"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -7091,7 +7091,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -7161,7 +7161,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -7194,7 +7194,7 @@
       <c r="E171" s="3" t="n"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -7260,7 +7260,7 @@
       <c r="E173" s="3" t="n"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -7298,7 +7298,7 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -7524,7 +7524,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -7623,7 +7623,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -8089,7 +8089,7 @@
       <c r="E198" s="3" t="n"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -8291,7 +8291,7 @@
       <c r="E204" s="3" t="n"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -8329,7 +8329,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8427,7 +8427,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -8691,7 +8691,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -8729,7 +8729,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -8922,7 +8922,7 @@
       <c r="E223" s="3" t="n"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -8955,7 +8955,7 @@
       <c r="E224" s="3" t="n"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -8992,7 +8992,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -9157,7 +9157,7 @@
       <c r="E230" s="3" t="n"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -9227,7 +9227,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -9260,7 +9260,7 @@
       <c r="E233" s="3" t="n"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -9524,7 +9524,7 @@
       <c r="E241" s="3" t="n"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -9557,7 +9557,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -9986,7 +9986,7 @@
       <c r="E255" s="3" t="n"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -10019,7 +10019,7 @@
       <c r="E256" s="3" t="n"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
@@ -10551,7 +10551,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
@@ -10828,7 +10828,7 @@
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1172,6 +1172,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1210,6 +1215,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="73" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -1248,6 +1258,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -1286,6 +1301,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -1324,6 +1344,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1362,6 +1387,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="252" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -1400,6 +1430,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="85" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -1435,7 +1470,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1476,6 +1516,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="49" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -1514,6 +1559,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="49" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -1552,6 +1602,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="241" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -1590,6 +1645,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1628,6 +1688,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="49" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -1663,6 +1728,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
@@ -1704,6 +1774,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="61" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1742,6 +1817,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="109" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -1780,6 +1860,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="109" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1818,6 +1903,11 @@
           <t>0</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="409.5" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -1856,6 +1946,11 @@
           <t>Error</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="409.5" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -2532,7 +2627,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10960,7 +11055,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -51349,6 +51349,16 @@
           <t>&lt;p&gt;The content of this ILS is covered at Form 2 (Grade 10) Kenyan curriculum. &lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Observe the following images &lt;/strong&gt;&lt;br&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;What is shown in the images?&lt;br&gt;What functions do the objects in the images serve?&lt;br&gt;What makes the objects able to achieve the role they play?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -51372,6 +51382,16 @@
           <t>&lt;p&gt;Observe the following video.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="73" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
@@ -51395,6 +51415,16 @@
         </is>
       </c>
       <c r="E4" s="3" t="n"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="25" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
@@ -51418,6 +51448,16 @@
           <t>&lt;p&gt;What happens to the extension when force on the spring increases?&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="25" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
@@ -51441,6 +51481,16 @@
           <t>&lt;p&gt;What do you think is the relationship between the applied forces (weight of suspended mass) to the extensions on the spring?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="25" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -51464,6 +51514,16 @@
           <t>&lt;p&gt;Is the measure of extension on the spring the same when loading the masses as when offloading?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="252" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
@@ -51487,6 +51547,16 @@
           <t>&lt;p&gt;          Materials that are able to regain their original size when force deforming them is withdrawn are said to be elastic.&lt;/p&gt;&lt;p&gt;The measure of extension on an elastic material is proportional to the force exerted on them.&lt;br&gt;This essentially means that an increase in extending force leads to an increase in size of the material.&lt;br&gt;This however has a limit beyond which the material won’t be able to regain its initial size after the deforming force is withdrawn.&lt;br&gt;The greatest extent within which a deformed material is able to regain its size after deformation is called its elastic limit.&lt;br&gt;The extension of a material within the elastic limit is called elastic deformation while extension beyond the material’s elastic limit is called plastic deformation.&lt;br&gt;In this case then;&lt;br&gt;        The extension on an elastic material is directly proportional to the force applied as long as the elastic limit is not exceeded.&lt;br&gt;This is called the Hooke’s Law.&lt;br&gt;In expression form&lt;br&gt;                       F α  e&lt;br&gt;Introducing a constant k of proportionality,&lt;br&gt;                       F = ke&lt;br&gt;The constant k is called the spring constant of the material being considered.&lt;br&gt;When the force is in N and extension in m, the units of k are N/m.&lt;br&gt;For elastic materials that need to withstand large forces without suffering permanent deformation, their value of k should be large.&lt;br&gt;This ensures small extension when large forces are exerted on them.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="85" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
@@ -51510,6 +51580,16 @@
         </is>
       </c>
       <c r="E9" s="3" t="n"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="121" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
@@ -51533,6 +51613,16 @@
         </is>
       </c>
       <c r="E10" s="3" t="n"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="49" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
@@ -51556,6 +51646,16 @@
         </is>
       </c>
       <c r="E11" s="3" t="n"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="49" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
@@ -51579,6 +51679,16 @@
         </is>
       </c>
       <c r="E12" s="3" t="n"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="241" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
@@ -51602,6 +51712,16 @@
         </is>
       </c>
       <c r="E13" s="3" t="n"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="49" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -51625,6 +51745,16 @@
         </is>
       </c>
       <c r="E14" s="3" t="n"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="49" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
@@ -51648,6 +51778,16 @@
         </is>
       </c>
       <c r="E15" s="3" t="n"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="25" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -51671,6 +51811,16 @@
         </is>
       </c>
       <c r="E16" s="3" t="n"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="61" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -51694,6 +51844,16 @@
         </is>
       </c>
       <c r="E17" s="3" t="n"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="109" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
@@ -51717,6 +51877,16 @@
         </is>
       </c>
       <c r="E18" s="3" t="n"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="109" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -51740,6 +51910,16 @@
           <t>&lt;p&gt;Below you will find a brief tutorial and in this link a set of images to get you started&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;a href="https://www.dropbox.com/sh/qaig4v6gk888p1o/AACVOInogIUloVIKcbxNBjQVa?dl=0" target="_blank"&gt;Salsa J images&lt;/a&gt; and tutorial&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;After you finish the proposed exercises you are ready to proceed to the next stage. Let's start with some basic informatin on how to measure the luminosity of objects in the sky.  Start by reading the Photomotry Basics Document below:&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="409.5" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
@@ -51763,6 +51943,16 @@
           <t>Photometry with Salsa J (based on the activity from Faulkes Telescope Education Program - Daniel Duggan &amp; Sarah Roberts). Photometry is the measurement of the intensity or brightness in a particular waveband (e.g. the optical) of an astronomical object, such as a star or galaxy by adding up all of the light from the object. For example, a star looks like a point of light when you look at it just with your eyes but the Earth's atmosphere smears it out into something that looks like a round blob when you use a telescope to look at it. In order to measure the total light coming from the star, we must add up all of the light from the smeared out star. Photometry is used to generate light curves of objects such as variable stars and supernovae, where we are interested in variability of light output by the system over time. It can also be used to discover exoplanets or to estimate the mass of a black hole candidate, by measuring fluctuations in the intensity of a star's light over time. These instructions explain how photometry can be carried out on groups, or clusters of stars, from images taken with different filters, in order to plot a colour magnitude diagram. An explanation on magnitudes can be found at the end of this document in Appendix 1. Instructions Before we can start the photometry, we have to work out our aperture radius - this defines the radius of the circle that is used to count the pixel values in the image. The radius of the circle is very important - if the radius is too small, it will not count all the light coming from the star and if it is too big, it may count too much background sky or other stars in the image. Therefore you may not get accurate measurements. SalsaJ automatically sets the radius as the Full Width Half Maximum (FWHM) of the stars in the image. The FWHM is used to describe the width of an object in the image. Stars in astronomical images have a specific profile when plotted as a graph of pixel values and that profile should be the same for each star in the image. The FWHM is a measure of the telescope's optics, the image recording CCD and the atmosphere through which the light passes. FWHM When determining the brightness of a star, the software sums the brightness over all pixels receiving light from that star. To do this the effective width of the star must be determined for each image before measuring the brightness of the stars on that image. One way to estimate the FWHM is to look at a slice across the star. The slice will probably look something like the diagram on the next page (without the arrows and label). The base of the slice is at the value for the background sky. The top of the peak represents the counts measured in the brightest pixel along the slice within the star. The difference between the top of the peak and the base is the height of the peak. The FWHM is the number of pixels across the peak at a point halfway up from the base. FWHM is displayed graphically like this: In order to do photometry, we recommend you work out your own optimum star radius in order to get more accurate results. To do this you must conduct a simple experiment, collect data and plot a graph - using Microsoft Excel (or another spreadsheet package that can plot graphs) makes this exercise much easier and quicker. The idea is to test several different aperture radii and compare the intensity values you get for each radius by plotting a graph of radius against intensity. To do this, go back to SalsaJ, then to Analyse&gt;Photometry Settings. Select force Star Radius and choose the value 6. Next, go to Analyse&gt;Photometry and another empty window will then appear entitled 'Photometry'. Using the mouse, click on a star in your image. The intensity of the object is calculated by adding up all the pixel values within the radius of the aperture. We can clearly see that the chosen radius is too small. Let's increase it a bit to 8. Click on the star again and a new measurement will appear. Still the radius is too small. Increase the value to 10 and continue until you reach a radius of 40 You should have something like this: In Excel (or other package) create two columns for Radius and Intensity then, add radius and the intensity value from SalsaJ. (You can save the values directly from the Photometry window in file.xls format and convert it to Excel. You should have a set of results that looks like this: Star's Star's Sky's Sky's Index Image X Y intensity radius intensity radius 1 ptstar2.fts 283 2 ptstar2.fts 283 211 34841 6 477 9 3 ptstar2.fts 283 4 ptstar2.fts 283 211 75460 8 300 12 5 ptstar2.fts 283 6 ptstar2.fts 283 211 117922 10 187 15 7 ptstar2.fts 283 8 ptstar2.fts 283 211 155160 12 123 18 9 ptstar2.fts 283 ptstar2.fts 283 211 187485 14 83 21 10 ptstar2.fts 283 11 ptstar2.fts 283 211 211802 16 62 24 12 ptstar2.fts 283 13 ptstar2.fts 283 211 229401 18 50 27 14 ptstar2.fts 283 15 ptstar2.fts 283 211 242610 20 43 30 16 ptstar2.fts 283 17 ptstar2.fts 283 211 252117 22 38 33 18 211 258799 24 36 36 211 264426 26 34 39 211 268427 28 33 42 211 271693 30 32 45 211 276987 35 31 52 211 279995 40 31 60 211 283728 50 31 75 211 284816 55 30 82 211 286119 60 30 90 We are interested in the variation of intensity with increasing aperture radius. When you plot a graph of this data, you should get something that looks like this: Counts Aperture Radius You can see the rapid rise of intensity as the radius of the aperture increases. This is because more of the star is included in the increasing radii of the apertures. The graph begins to flatten out when we have all of the star within the aperture, but keeps rising gradually as more and more of the background sky is included. From this graph, we can see that the best radius to use is about 10 - this is around the point where the star's intensity stops increasing so rapidly. There is however, not just one correct answer and a value of 12 or 14 could also be considered appropriate. Once you have chosen the best aperture radius, this can be set for the remainder of your photometry analysis on this image. It is advisable to carry out this exercise every time you come to work with a new set of images as the FWHM of objects change due to the seeing conditions at the time of observation so new aperture radii will need to be calculated for new images. However, if you are carrying out photometry on the star, but in two different wavelengths (such as B and V), then you should use the same radius for both images to ensure that you are comparing 'like with like'. Measuring the Counts of a Star Let's continue using the same images as before PTstar1 PTstar2. Now with the established value for the aperture of 18 we will measure the brightness in both images What is the brightness of PTstar1 in Counts? What is the brightness of PTstar2 in Counts? You will find out that the values greatly change from one image to the other. These images are actually of the same star and the star itself has not changed. However, they were taken on two different nights and the seeing certainly varied a lot. In these images we can't compare the brightness of the star with other stars in the field. So in the next activity we will choose a better target. When the field has more stars it is easy to make a mistake. If you are not sure you selected the correct star you can delete a line in the photometry measurements window by selecting the line, then chosing Edit in the Menu and then Cut. Comparing Two Images of the Same Region Images for this activity are listed below. In each image the target star is on the left and the reference star is on the right. This images containing a Cepheid Variable, a star with a very well know variability and very often used and to help evaluate distances to nearby galaxies. For this part of the activity we will use the following images: PTnight1, PTnight2, PTnight3, and PTnight4. You may open and work on these images simultaneously or one at a time. PTnight1 - https://www.dropbox.com/s/gkgyaya8zuqn5ez/ptnight1.fts PTnight2 - https://www.dropbox.com/s/2hcpbvtrw90p0gt/ptnight2.fts PTnight3 - https://www.dropbox.com/s/xnttgf4h98o74dp/ptnight3.fts PTnight4 - https://www.dropbox.com/s/wk8m53gno9dub0k/ptnight4.fts Use the photometry tool to measure the brightness of the target star and the reference star Reference star Variable star</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="409.5" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -51786,6 +51976,16 @@
           <t>BLACK HOLES IN MY SCHOOL Observing Stellar Mass Black Hole Candidates This module integrates an online training course introducing participants to the use of the inquiry methodology and the integration of ICT tools in schools practices. This module is devoted to the implementation of a research based experiment where students can be involved in the identification of stellar mass black hole candidates and the procedure to measure their mass limits. Learning outcomes At the end of this module participants should know the procedure used to identify black hole candidates and how to determine the mass limits of a compact object in a binary system. Rationale This module introduces participants to the technique used to determine the mass limits of a compact companion to a visible star. Resources Set of images of black hole candidates Salsa J Excel Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project Eclipsing Binary Stars The most common stellar mass black hole candidates live in binary systems where one of the components is a compact object (a black hole or neutron star) and the other a 'normal' star. The light curve of a binary system can allow us to study the different components. Take for instance the example below: In the case where one of the components is a compact object we only see the 'normal' star (usually a main sequence star or anevolved red giant). In the case of Low Mass X-ray Binaries (LMXBs), these stars fill their Roche Lobes and therefore acquire a pear (or teardrop) shape. As the two objects orbit their common centre of mass, different parts of the system are visible to us. Depending on the Figure 1 Light curve of binary star Kepler-16 (Credit: NASA) inclination of the system (where 0° is a face-on orbit and 90° is an edge-on orbit) a limit on the mass of the compact object can be established. The image in Figure 2 shows the infrared light curve of the black hole candidate A0620-00. Depending on the position of the companion star and the compact object, with its accretion disc (see fig.4), we see different amounts of light coming towards the observer. Remember that we don't see the individual components; we only observe a dot whose brightness changes in time. It is from the study of these changes in the form of a light curve that we can start to infer some of its characteristics. Figure 2 Infrared light curve of A0620-00 (a binary system where the compact object is a strong black hole candidate). Credit: Shahbaz et al, 1994. Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project Finding the minimum mass for the black hole candidate XTE J1118+480 The object we will study is the black hole candidate XTE J1118+480. It was discovered in March 2000 by the Rossi X-ray Timing Explorer satellite. It is approximately 6 000 light-years away in the constellation of Ursa Major. The system is composed of a compact object and a low mass star (less than 2 solar masses). The compact object is pulling matter from its companion and the intense, time-variable heating of this material in the accretion disc helped astronomers discover this object. This heating means that the disc emits copious amounts of X- rays. Figure 3 Location of the black hole candidate XTE J1118+480 (Credit: Black Hole Encyclopedia) The optical component of this system (the star; Figure 4 Here we find an artist impression of the KV UMa) already appeared in images (some binary system XTE J1118+480 composed by a low mass over 40 years old) and it appears to be star and a compact object. The material of the following a looping path that takes in out of the companion star is attracted by the intense disc of our Galaxy (see Figure 5). Studies of this gravitational field of the compact object forming an trajectory indicate that the object might have accretion disc. Credit: Hynes been inside a globular cluster and was probably kicked out after the supernova explosion of the massive progenitor star that gave birth to the compact object. The estimated mass of this black hole candidate is around 7 solar masses. This is precisely what we want to confirm with this exercise. Figure 5 Artist impression of the path of the XTEJ1118+480 through the disc of our Galaxy. Credit: STScI Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project The data we will analyse are a sequence of 62 images obtained by Faulkes Telescope North taken on 13/05/2009. We will analyse this images using Salsa J and Excel. The images show several stars surrounding the object we wish to study. We will select some of these stars to be comparison stars in our study. The procedure is to make photometry measurements of all the comparison stars and the black hole candidate for all the images. If we are fortunate, the brightness (or intensity) of the comparison stars should remain constant (although there are variations in the images based on weather) as a function of time while the brightness of the binary system containing the black hole candidate should vary. By plotting the intensity against time we should see variability and can use this to estimate the mass of the non-visible compact object. Figure 6 The finding chart (the map of stars locating the object and the comparison stars). XTE J1118+480 is denoted by the two black lines the comparison stars are shown as 1, 2, 3. (Image from Faulkes Telescope North) First, we need to determine the best aperture radius before proceeding with the photometry. Figure 7 Evaluating the best aperture with Salsa J, as explained in the photometry lesson Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project Previous studies show show that average star in this image has a FWHM of 4 pixeis In practice, a good choice for the radius of an aperture is about 1.5 or 2.0 times the FWHM. In the examples below the value used was 6 for the aperture radius. Now you can start to measure the intensity for the 3 comparison stars and for the black hole candidate. Make the measurements in each image for all 4 objects. Since the images are 2 Mb each, it is best to process no more than 20 images at a time. Alternatively, you can distribute the images amongst a group of students and collate the group's results later, ensuring that each group use the same aperture radius and the same comparison stars. You can choose to 'tile' them (in Salsa J, 'Tile' is under 'Window') which will make it easier to perform the procedure. It is important to process the images in order which is easy if you follow their number. Figure 8 Selection of 20 images, tiled and then reordered Make sure you adjust the brightness and contrast in all images in order to be able to see all the objects. If you can't see all of them don't use the particular image. Sometimes if you close and reopen the image the brightness and contrast appear better. Since we will be working with relative magnitudes, where we are comparing intensities of the comparison stars and the black hole candidate we don't have to worry about absolute magnitudes and standard stars etc. We are not looking for the absolute value of the magnitude of the object but the variations to its intensity relative to other stars in the same image. You will also need the Modified Julian Date (MJD) for each image. You find this information in the header of FTS images. In Salsa J you select the Show Info under the Image menu and in the header you will find the value for MJD. This is the value to be used on the x-axis of your graph. Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project After removing a couple of images, your results should look like this: star 1 10000 star 2 9000 star 3 8000 xte J1118 7000 6000 5000 4000 3000 counts 54964.24506 54964.2528 54964.26055 54964.26829 54964.27603 54964.28377 54964.29263 54964.30037 54964.30905 54964.31678 54964.32451 54964.33576 54964.3435 54964.35124 54964.35897 54964.36671 54964.37761 54964.38534 54964.39307 54964.40339 Julian Date Figure 9 Plot of counts over time From this graph we can clearly see that our target varies far more than the comparison stars. We already know that the orbit of the visible star and compact object around each other is periodic. Finding the orbital period is complicated and time demanding. But we can make a rough estimate from the graph above since it is showing evidence that the whole period is in the set of images. We can try to adapt the value of the period that best fit our purposes. You students can play a bit with the value of the period and try to find the best fit. Scientists already know the period of this object P= 4.08 hrs = 0.17 days. (http://adsabs.harvard.edu/abs/2001ApJ...556...42W) A nice tutorial on the calculation of periodicity and determination of phase in variable systems can be found here: http://www.aavso.org/files/Chapter12.pdf The formula to transform the Julian dates in Phase is the following = 0 Where the MJD is given in the header of each image, T0 is the MJD of the first image and the period is 0.17 days. The result should look like this. Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project 9900 8900 7900 6900 xte J1118 5900 Average star Counts 4900 3900 0.2 0.4 0.6 0.8 1 0 Phase Using the formula to determine the mass limit of the compact object ( ) = 13 sin 3 = 23 ( 2 + 1)2 2 where M1 and M2 are the masses of the compact object and the companion star respectively, P the orbital period, i.e., the time it takes for the star to complete an orbit, G is the universal gravitational constant, i is the inclination of the orbital plane of the system with the line of sight of the observer and K2 the radial velocity of the visible star We can use the radial velocity of the visible component of this system was determined to be ~ 700 km s-1 , the mass of the companion is ~ 6.1 Solar Masses (http://adsabs.harvard.edu/abs/2001ApJ...556...42W) Both of these are determined using spectrocopy the companion mass is inferred once we know its spectral class and several spectra can be taken to determine the object's radial velocity. Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project P = 0.17 * 24 * 60 * 60 = 14 688 s Msolar = 1.9891 × 1030 kg Assuming all the above values we end up with the following value for the mass limit of this black hole candidate: ( ) = 13 sin 3 = 14 688 (700 1) 3 ( 2 + 1)2 2 6.67384 10 11m3 kg 1 s 2 ( ) = 13 sin 3 = 1.2 1031 ~ 6.3 ( 2 + 1)2 These calculations used approximate values but reached a very good guess for the mass of the stellar black hole candidate XTE J1118+480. The assumed value for the mass function (the minimum mass) is of the order of 6.1 Msolar (http://arxiv.org/pdf/astro-ph/0104032.pdf) Images and parts of the text credited to Fraser Lewis (Faulkes Telescope Educational Team) BHIMS is developed in the framework of the SoNetTE project</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="181" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
@@ -51809,6 +52009,16 @@
         </is>
       </c>
       <c r="E22" s="3" t="n"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="409.5" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -51832,6 +52042,16 @@
           <t>Observation Planning Observation Planning Using Stellarium to plan an observing session Author: Sarah Roberts Observation Planning Observation Planning - Using Stellarium to plan an observing session Stellarium Stellarium is free planetarium software which allows the night sky to be viewed from any location on Earth, on any date. The software can be downloaded from www.stellarium.org. A patch which sets up Stellarium so that its default location is at FTN, and an azimuthal grid is visible on the sky, is also available on the Faulkes Telescope website at: http://www.faulkes-telescope.com/index.php?page=186 With such a patch, the opening screen of Stellarium looks like the image here. The viewing direction is to the South (as noted by the S), the azimuthal grid is visible, and there are many deep sky objects which have been labelled. For users who have not downloaded the FT patch, the azimuthal grid and deep sky object names can be toggled on/off the sky by clicking on the grid and nebulae buttons shown here. The boxes at the bottom of the Stellarium screen can be selected or de-selected, to, among other things, turn on the names of the deep sky objects, label the constellations and remove the horizon from the screen. It is worth playing with these buttons to familiarise yourself with the different features in Stellarium. Page 2 of 6 Observation Planning - Using Stellarium to plan an observing session Setting the location for your FT observing session An important button on the tool bar in Stellarium is the 'Configuration Window' button - this is the spanner icon . By clicking on this button, a window appears. This window give the options for changing your date and time, and location, aswell as the landscape, video and rendering options. If you are using the down- loaded FT configuration patch, your location will automatically be set as the position of FTN. This can be changed to any other location (e.g FTS) by either clicking on the map, or by entering the longitude and latitude of the location underneath the map. Observation Planning Setting the date and time for your FT observing session From the configuration window menu, select 'Date &amp; Time'. The next window will give you options for changing the date and time, time zone and time speed in Stellarium. Set the date and time to correspond to that of your FT observing session, Click on the square in the top right hand corner of the configu- ration window to close it once you are happy with the set up of the viewing time and loca- tion. Page 3 of 6 Observation Planning Observation Planning - Using Stellarium to plan an observing session Looking around the sky in Stellarium By clicking on the question mark button, or typing 'h' in the Stellarium window, you can see which keyboard buttons correspond to commands in Stellarium. For example, to zoom in/out of the sky in Stellarium, you can either use the roller ball of your mouse (if you have one), or use the 'Page Up/Down' buttons on your keyboard. The sky can be scrolled around by left clicking on it, and dragging it with the mouse. Alternatively, you can use the arrow keys on your keyboard. Setting up the best view to plan your FT observing session In order to use Stellarium to help you plan your FT observing session, the time, date and location should be set correctly through the configuration window. Next, zoom right out of the Stellarium window and scroll the sky until the zenith (the point directly overhead) is at the centre of the screen. The lowest altitude limit of the Faulkes Telescopes is 25 degrees. Thus, all objects which you choose for your observing session should be above 25 degrees from the horizon. Ideally, to minimize the amount of atmosphere the telescope looks through when observing, this limit should be anything above 30 degrees. Thus, any object within the 30 degree circle in the Stellarium view can be observed with the Faulkes Telescopes. The best order of observing can be decided from the positions of ob- jects in the sky. Page 4 of 6 Observation Planning Observation Planning - Using Stellarium to plan an observing session Selecting objects in Stellarium In order to zoom in on images in Stellarium, click on the object with the left mouse button, and press the space bar to centre on it. On the left we have centered upon NGC 7662. Now we wish to magnify the image. This is done by using the Page Up/Down keys on your keyboard, or your roller ball on your mouse. The zoomed in view of this object can be seen below. At the top left hand corner, some information is given on the selected object. Page 5 of 6 Observation Planning Observation Planning - Using Stellarium to plan an observing session When zooming in further on the object, a credit for the image is displayed, as shown below. This particular image of NGC 7662 was taken by the FT Team. You can add your own im- ages into the Stellarium database, so that your images appear on the sky, as this one has done. More information on how to do this can be found in the Stellarium user guide which can be downloaded from the Stellarium website. Page 6 of 6</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="409.5" customHeight="1">
       <c r="A24" s="2" t="inlineStr">
@@ -51855,6 +52075,16 @@
           <t>Stellar mass black holes Black holes are regions of space time where gravity shows all its glory and triumph and are thus very important examples of applicability and importance of General Relativity. They are mysterious objects which existence is still not completely proved. To definite proof of their existence would be finding evidence of the existence of an event horizon, a point of no return. Until such proof arrives the correct attitude is to call them black hole candidates, no matter how promising the many observations of are. In spite of all this veil of mystery and uncertainty black holes are the simplest objects in the Universe. They can be completely characterized by only 3 parameters: charge, mass and angular momentum. This implies that black holes in the centre of galaxies and those living in stellar systems have only one fundamental difference: their mass. There are strong arguments implying that stellar mass black holes might be born from the supernovae which occur after the death of some high mas stars, stars with masses 8 times the mass of our Sun or bigger. These big stars have a very short existence (in the order of millions of years, which is very short when compared to the life of a star like our Sun. Our Sun exists for nearly 4.5 billion years (109 years) and is in halfway through its life time. The final stage of the life of a high mass star is in the form of a supernova explosion. The remains of the progenitor star are expected to be in general either a neutron star or a black hole, depending, in part, on the mass of the remaining object. So far we know nearly 2 dozen of very strong stellar mass black hole candidates in our own Galaxy. Their proximity turns them in real laboratories where we can study their characteristics and thus gain knowledge about their true nature and perhaps infer probable characteristics of those living in the centre of galaxies. An artistic view of a stellar mass black hole system is depicted in fig 1. Companion Star Accretion Disk Compact Object (Black Hole Candidate) Figure 1 Artist Impression of Stellar Black Hole Candidate A0620-00. A binary system composed of a low mass star and a compact object. The material of the companion star is attracted by the intense gravitational field of the compact object forming an accretion disc surrounding it. (Credit and Copyright: Robert Hynes) 1 How stellar mass black holes form? Let's begin by gaining some understanding of the life cycle of stars. Figure 2 Two different evolutionary cycles of stars depending on the initial mass (Credit: NASA) In figure 2 the life cycle of stars are presented depicting two major evolutionary paths, depending on the initial mass of the star. In the central part of this artist impression a nebula of gas and dust gives birth to stars with different masses. In the left part of the image it is represented the evolutive cycle of a low mass star (like our Sun), that will end up its life as a white dwarf. In the right part of the image it is represented the evolutive path of a high mass star that will end up as a neutron star or a black hole. The luminosity of stars during most of their lives is due to nuclear reaction where Hydrogen is being fused into Helium. These reactions are only possible due to the extreme temperatures existing in the interior of such objects. The radiative pressure that generates from such phenomena counterbalances the gravity field originated by the star's own mass, enabling the star to stay in a state of equilibrium. When the fuel diminishes (in this case Hydrogen), the radiation pressure diminishes and the star's core contracts due to the action of the gravitational field. There is an increase in temperature in the regions closer to the core, which makes it possible for the hydrogen combustion layer to move gradually towards the surface. The star, in search for a new equilibrium state, will expand. The radio of the star increases and the star transforms into a red giant or in a red supergiant depending on its initial mass. While the star expands the core contracts. There is a new increase in temperature and depending on the original mass of the star, the temperature and density may increase enough to originate new reactions and start transforming Helium core into a mixture of Carbon and Oxygen, or , in higher mass stars, oxygen, neon and magnesium. During this period the external layers of the star are dispersed in the interstellar medium (in high mass stars, the lost fraction represents a big part of the 2 total mass), while the core, where fuel (heavier elements) also starts to run out, continues to contract and heating to higher temperatures. The element transformation continues until the formation of Iron. Iron is a stable element and to transform it into heavier elements the star would need an external source of energy. From this moment on the star gets unstable and ends up in a supernova explosion where all the outer layers are released to the interstellar medium. Elements heavier then Iron are formed in this phase. Stars like our Sun (low mass stars) have a much longer life cycle, with a duration of the order of billions of years and end up their lives in the form of a white dwarf. They start by fusing their Hydrogen fuel into Helium. The gravitational field originated by the star mass is not enough to effectively ignite the fusion of Helium into heavier elements. Our Sun exists for at least 4.5 billion years and it is estimated that it is in half of its life cycle. Stars with a mass higher than 8 solar masses will follow a much shorter life cycle, of the order of millions of years. Due to their higher mass they need more fuel in order to maintain the equilibrium state, thus consuming more rapidly their source of energy. It is believed that their end state will be in the form of a neutron star or a black hole. White Dwarfs Figure 3 - NGC 2440 is a Planetary Nebula located 4000 light years away from Earth. The central star evolved to a white dwarf after ejecting its outer layers originating this beautiful planetary nebula (Credit: NASA &amp; Hubble Heritage Team) Low mass stars end up their life cycle in a much more pacific way when the core slowly lose contact with the outer layer. High energy photons originating from the stellar core slowly excite the material of these outer layers, already very diluted and dispersed, producing as a result the incredible beautiful planetary nebula as the one in figure 3. 3 The remaining part of the star has the form of a white dwarf. In these stars matter is so compressed that atomic core are glued to each other. A state where there are no atoms only nuclei and free electrons. The collapse of the star is now stopped by the electrons degeneracy pressure, a pressure that emerges from the impossibility of 2 electrons occupying the same position at the same time. If we try to put 2 electrons in the same orbit an effect similar to electromagnetic repulsion, when we try to approach particles with the same charge, will appear. In this case the effect is known as the Pauli exclusion principle: two electrons can't occupy the same quantum state . In the core of the stellar remains the pressure is so large that the necessary conditions for such a force to appear and the degeneracy of electrons is then responsible for stopping the gravitational collapse, thus stabilizing the star. White dwarfs are extremely hot and emit thermal radiation. The first white dwarf observed was Sirius B, companion of Sirius, one of the brightest stars in our skies. Sirius B has a radius smaller than that of the Earth but has almost the same mass as our Sun. White dwarfs are so dense that a tea spoon of their material would weight 50 ton, by Earth standards! The discovery that the electrons degeneracy pressure could halt the collapse of a star was made by an Indian physicist, Subrahmanyan Chandrasekhar, when he was 20 year old, while making the boat trip that took him from India to England where he was about to start his Phd. He calculated that only stellar remains that had a mass lower than 1.44 times the mass of the Sun could reach a state o equilibrium due to the electrons degeneracy pressure. This will be the destiny of our star, the Sun. When this limit is surpassed the continuation of the collapse is inevitable until the next stage, where it can be halted again in the formation of neutron stars. Neutron Stars Figure 4 - The Crab nebula (M1) in the direction of the constellation Taurus, taken by the Hubble Space Telescope (lower left). The details to the right are showing a composite of visible light (red) and X-rays (blue) with the pulsar as central star. At the shock front in 0.3 light-years distance from the pulsar, the ultrarelativistic wind of electrons and positrons collides with the surrounding nebula. (Credits: NASA) 4 If the progenitor star has an initial mass higher than 8 solar masses, the transformation cycle of Hydrogen into Helium and so on towards heavier elements will continue until the stage where the core of the star is composed essentially by Iron. In order to transform iron in heavier elements it is necessary to find an external source of energy. In the absence of the radiative pressure from the core of the star the collapse is inevitable and very quick. The star loses contact with the outer layers. With a mass higher than 1.44 solar masses, the electron degeneracy pressure is not enough to halt the gravitational force and the star's core collapses. The electrons can't resist the gravitational pull and start interacting with protons from the core producing neutrons. In this case, and provided the mass is not higher than 3 solar masses, a new equilibrium state can be reached, this time due to the degenerative pressure of the neutrons, the quantum effect that prevent neutrons to occupy the same state. The pressure created by this package of neutrons will counterbalance the gravitational force and the star will reach a new equilibrium state in the form of a neutron star. In Figure 4 we can see an image of the Crab Nebula, a supernova remnant, at a distance of 6 000 light years from Earth, first observed by the British amateur astronomer John Bevis. In the right hand side of the image we can see the interior of the nebula where a pulsar was observed (a neutron star that emits regular radio pulses). The pulsar is visible in the central part of the image. The rotational period of a pulsar is extremely small. In the case of the crab nebula's pulsar it is 33 times per second. Figure 5 High mass star's life cycle ends when the core is essentially constituted by Iron, a stable element that can't be transformed into heavier elements unless an external source of energy is provided to the star (Credit: NASA) As mentioned before, if the progenitor star has an initial mass around 8 solar masses, the transformation cycle continue until a state where the star's core is constituted essentially by Iron. At this stage the star resembles an onion where each layer is constituted by different elements, produced during the evolutionary cycle of the star. The outer layers that can't follow the collapse of the core undergoe a slower contracting process ending up with a collision with the degenerate core. This process ends up in the form of a supernova explosion type II, one of the most energetic phenomena in the Universe. In this phase the star releases into the interstellar medium all the elements that it has produced in its interior. The interaction of the radiation coming from the core with the star's layers, during the explosion, will generate the necessary energy for the emergency of elements heavier than Iron. This is the 5 mechanism with which the Universe is enriched with the elements for the periodic table that didn't exist in the primordial Universe, that was constituted basically by Hydrogen and Helium and a small quantity of Lithium. As Carl Sagan use to say, we are all children of the stars, all made of stardust. The remains of such an explosion, depending on the mass, can be a neutron star or a black hole. Neutron stars have usually a radius of around 10 km, usually with a mass of the order of 1.5 solar masses. The first detection of a neutron star was made by an Northern Ireland astronomer, Jocelyn Bell, a Phd student at the time of the discovery, in 1967. She discovered a radio signal that pulsed with such an amazing periodicity that at the beginning she thought could be a message from aliens. Soon it was confirmed to be a signal coming from a neutron star. These objects have intense magnetic fields (in fact they have the most intense magnetic field that we can measure in the Universe, billions of times stronger than the Earth's magnetic field). These magnetic fields originate the vibration of the electrons, responsible for the emission of radio waves. Neutron stars with such characteristics are known as pulsars. These are objects with fast rotation and their pulses can have a periodicity of milliseconds. The final effect is similar to the light emitted by lighthouses. Important to be noted however that not all neutron stars are pulsars. Black Holes If the remains of the progenitor star has a mass higher than 3 solar masses, which may happen in cases where the original star may have masses higher than 40 solar masses (the relation between the initial mass and the mass of the remaining object is not yet well established), then not even the degeneracy pressure of neutrons can stop the gravitational collapse and the star will contract due to its own gravitational field giving birth to a black hole. A black hole is by definition a region of the Universe where nothing can come out of, not even light. This sole property was responsible for the baptism of such obejcts as black holes by the theoretical physicist John Wheeler in 1967. In fact, the existence of objects where the scape velocity where higher than the speed of light (the minimum necessary speed for an object to escape the gravitational attraction of the body), was already predicted in 1783 by an English priest, John Michell, and in 1796 by Pierre Simon Laplace, both predictions based in the Newtonian Mechanics. The big change since then is that at the time this predictions where made it was not known that the speed of light was a limiting value. The escape velocity on Earth is 40.248 km/h, already reached by aerospace technology. However, if the density of our planet increased a lot, if we contracted the whole Earth to a radius of 10 mm then the scape velocity would increase and surpass the 300 000 km/s, a speed higher than the velocity of light, thus impossible to reach. In the framework of General Relativity the existence of black holes emerges as a marginal result to one of the most important solutions to Einstein equations, the solution discovered in 1915 by Karl Schwarzschild. This solution describes the vacuum region external to a static and spherical body. It is perfect to study the dynamics in the Solar System and provided important proofs of predictions made by Einstein's theory. This solution predicts that a body may contract to a value inferior to a 6 certain radius, the Schwarzschild radius (also known as event horizon), turning into a black hole. In km this value is equivalent to 3 times the mass of the star in solar mass units. G = Newton's gravitational constant = 6.67 x 10-11m3s-2kg-1 C= light speed = 3.00 x 108 m/s 1 Mʘ (1 Solar Mass) 1.99 x 1030 kg 13,34 x 10 11 M m3 2 m Schwarzchild Radius = 2 GM/c2 = 9 x 1016 kgm2 2 = 1,482 x 10 27 M kg = m 1,482 x 10 27 x 2 x 1030 M Mʘ M Schwarzschild Radius = 2 GM/c2 3 Mʘ Approximately 3 times the mass of the star in solar mass units and the result given in km. A typical black hole candidate has a mass of approximately 10 solar masses and an event horizon of approximately 30 km. Most neutron stars and black hole candidates discovered so far are part of a binary system composed by a star of a known spectral type and a compact object. The intense gravitational field of these objects will attract the material of the companion star forming an accretion disk around the compact object. The inner part of the disc is subject to a gravitational field more intense and emit higher energy radiation, in the X-ray part of the spectrum. This is the most effective method of discovering such objects, but is not the only one. How do we detect stellar mass black holes ? (these part of the text is only to get you familiarized with all characteristics related to this field of research) Figure 6 UHURU satellite (freedom in Swahili). Was the first satellite completely devoted to the study of cosmic X-ray sources. It discovered over 400 sources, among them several X-ray emitting binary systems. 7 From the 60's on astronomers started to have available the necessary technology to observe the sky in the X-ray waveband. Until then there was no knowledge of the existence of an X-ray emitting source in the Universe beyond our Sun. X-rays can't pass through our atmosphere, therefore only spacecraft above it can study the Universe in this wavelengths. The first such device was launched in 1962 by a team of North American scientists. The Italian Ricardo Giacconi, who won the physics Nobel Prize in 2002 for his contribution for X-ray astronomy, was among them. The first discovered source was Sco X-1, receiving this name for being the first X-ray source in the constellation of Scorpius. At that time this source was a mystery to the astronomers: it emitted thousands of time more energy in X-ray than in visible light, and in this waveband the source was billions of times brighter than the Sun! These mysterious sources of radiation started to be unveiled with the launch of the UHURU satellite (Figure 6). This event marked the beginning of a new era of important discoveries unveiling a completely different Universe that could not be seen in the optical. Nowadays there are several active satellites observing the sky in X-ray: Chandra (NASA), XMM- Newton (ESA), RXTE (NASA), ALEXIS (LANL). Compact Object High Mass Star Accretion Disk Figure 7 Scheme of the mechanism of accretion by stellar winds. Credit: NUCLIO (C.Zurita) 8 Hundreds of X-ray sources where detected so far, concentrated in the plane of our Galaxy. Many of these sources are binary systems composed by a star of a known spectral type and a compact object. The gravitational field of this object attracts the material of the companion star. In the regions closer to the compact object high energetic phenomena take place and we can observe the emission of X- rays. In the cases where the non-visible component is a neutron star or a black hole they are called X-ray binaries. If the compact object is a white dwarf, in spite the fact that they are also sources of X- ray, they are called cataclysmic variables. This last case is easy to spot since their X-ray emission is not as intense as in the case of the more compact objects. In an interesting paradox, these extremely compact objects are almost impossible to detect when isolated. They are discovered for being responsible for extremely energetic phenomenon that for a short period of time transform them into strong X-ray emitters. Neutron stars and black holes are responsible for the most energetic phenomena in the Universe, they can be discovered via their interaction with the surrounding medium or objects such as those in binary sytems. The first system detected, in which the compact object is a strong stellar mass black hole candidate, was Cygnus X-1, in 1972 by the UHURU satellite. It is estimated that the compact object has a mass of the order of 5 times the mass of the Sun concentrated in a few kilometres. Its luminosity is due to accretion of matter coming from the companion star, a blue supergiant. Supergiant stars are continuously losing mass due to stellar winds. Part of this gas can be attracted by the compact object releasing X-rays (figure 7). The gas may then form a small accretion disk. In the inner regions of this disc energy might reach high levels, so high that we can observe X-rays. Figure 8 Scheme of a binary system formed by a Be star and a neutron star. The X-ray emission occurs when the neutron star, in a particular point of its orbit, enters the circumstellar disk and attracts part of the gas. The X-ray flux increases abruptly at each passage of the neutron star throughtout the disc. Credit: NUCLIO (C.Zurita) 9 The high mass companion star can also be of the Be type. The B stars are high mass stars much hotter and much bigger than our Sun. The Be are a subtype of this category and is characterized by having a circumstellar disc formed, probably, by the mass of the star lost from the equatorial zones due to its fast rotation. The binary systems formed by a Be star and a neutron star will also produce X-rays if the neutron star, at a certain point of its orbit around the star, penetrates the disc and accrete part of the gas and are therefore known as Be/X-ray binaries. There are other 2 types of systems in which the companion star has a lower mass than the Sun e therefore are called low mass X-ray binaries. In these systems the accretion is produced by the material overflowing the Roche lobe, the volume around the star within which the material is gravitationally attached to it. In a binary system, there is a common point between the Roche lobe of the two components, the so called Lagrange point. This is the equilibrium point between the gravitical forces of the two components of the system, in other words, a point where any object would be equally attracted by the star and the compact object. Figure 9 Scheme of a low mass X-ray binary with Roche lobes represented. The star fill its Roche lobe and acquires the shape of a pear. All material inside the yellow lobe is attached to the star e in the blue lobe to the compact object. The gas in the Lagrange point will flow through this point in the direction of the higher gravitational field. The flux carries with it the angular momentum of the star (rotating at the same speed as the star), thus it won't fall directly to the compact object forming around the star an accretion disc. The point of impact of the gas flow with the disc is called hot spot for being hotter and brighter than the disc itself. In the internal regions of the disc the potential energy of the gas is so high that will originate X-rays. The Lagrange point is of particular importance since it is the simplest route for the gas to flow from one star to the other. In certain phases of the evolution of the star it can fill its Roche Lobe. This happens in low mass binaries where the star will deform until acquiring the form of a pear. The gas 10 existing in the external regions, near the Lagrange point will then be attracted by the compact object. Since the system is rotation, the material being transferred will fall in spiral shape in the direction of the compact component forming an accretion disc around it. The accretion process produces X-ray and via reprocessing in the disc, visible radiation. Eventually the accretion mechanism via overflow of the Roche lob can also appear in high mass systems alongside with accretion from solar winds. The fact that we observe X-rays is not an evidence of the existence of black holes. It is an evidence of the existence of a compact object, which can be a white dwarf, a neutron star or a black hole. The case of white dwarfs is easily solved since, among the binaries with a compact object; these are the weakest X-ray emitters. However, if the compact object is a neutron star or a black hole, than the distinction is more complicated since the gravitational potential of a black hole and a neutron star is very similar and their observational properties very similar. If the binary system contains a neutron star, as seen before, may emit regular pulses. Since the magnetic field of the neutron star is very intense the gas may be accreted by the magnetic poles producing the same effect as a light house emitting radio pulses. These systems are so called X-ray pulsars. Sometimes the magnetic field are not so strong, as in the case of the low mass X-ray binaries, and the pulses are not so regular but more erratic and unstable. In these cases we say that they present quasi-periodic oscillations (QPOs). In addition they can also produce thermonuclear flashes in the surface of the neutron star. The flashes are produced when the gas (mainly hydrogen) accreted accumulates in the surface until the conditions are appropriate to start nuclear reactions that first consumes the Hydrogen and then the resulting Helium. Since Helium's fusion is explosive flashes can be observed with more or less regularity. In summary, if we observe pulses or flashes in a X-ray binary, we can be sure it contains a neutron star. But not all neutron stars emit pulses or flashes. In such cases, one way to distinguish between a neutron star and a black hole is by determining the mass of the non-visible component. If the mass of the object is above 3 solar masses than we have a strong black hole candidate. 11 Figure 10 Artistic impression of Centaurs X-3 a high mass X-ray binary located at 30 000 light years from Earth. The compact object is a neutron star with a mass around 0.8 solar masses in orbit around a blue super giant. This was the first system where periodic X-ray pulses where detected. (Credit: Dany Page) How can we determine the mass of a stellar mass black hole ? Most stars live in binary systems. If one of the components of the systems have enough mass, it will end up its days in the form of a supernova. The remain will be transformed into a compact object, a neutron star or a black hole. If the binary system survives the supernova explosion, it can then create a low mas X-ray binariy (or LMXB). We only know about 150 such objects in our Galaxy, a low number when compared to the 100 billion stars in our Galaxy. From these 150 less than 2 dozen have an estimate for the minimum mass of the compact object. It is precisely from the orbit of stars around non visible objects that we can determine the mass of the compact component in a X-ray binary. 12 Low mass star filling its Roche Lobe Compact Object Matter flowing from the companion start to the compact object Accretion Disk Figure 11 Artist impression of the low mass X-ray binary A0620-00. Discovered in 1975 it rapidly became a promising stellar mass black hole candidate, a prototype to the study of other candidates. However, the definitive determination of its mass was not yet possible and the limits to its value are too close to the limiting value for a neutron star, around 3 solar masses. (Credit: Robert Hynes) Low mass X-ray binaries are almost always detected by being strong X-ray emitters. In some of these systems the strong emission phase is a transient phase, i.e., has a very short duration. In these systems the flow of matter in the direction of the compact object has a spasmodic behaviour. Most of the time, matter coming from the star will accumulate in the outer parts of the disc until an instability is generated and the gas us suddenly accreted. An intense eruption is produced and the brightness of the system may have a variation of 5 to 6 magnitudes. After a period that might last a few months the system returns to its normal rhythm, a phase coined as quiescent phase. In this phase all the important studies to determine this system's parameters take place. Contrary to what happens in persistant X-ray binaries, in which the emission coming from the disc continues, in the transient X-ray binaries the intense emission stops and allows other characteristics of the system to be observed. Once the accretion disc stops being so bright, the companion star becomes visible again. The X-ray transients go completely unnoticed in the middle of hundreds of millions of stars until the moment of the eruptions. The interval between eruptions in these cases is very long taking sometimes decades to take place again. For this reason the discovery of such objects is not so frequent. 13 The mass function Figure 12 Scheme of a binary system. The compact object (mass M1) and the companion star (mass M2) are orbiting the centre of mass (CM) of the system with radical velocity K1 and K2 respectively. Since the compact object is not visible we have to extract all the necessary information by observing the companion star and its orbit. Credit: NUCLIO (C.Zurita) When a transient system is discovered, it is necessary to wait several months for the star to be responsible for the major emission coming from the binary system and not the disc. By then the observation of the companion star are crucial in order to determine the orbital parameter of the system and be able to apply Kepler's third law. This law states that the square of the orbital period is proportional to the cube of the average distance between the components of the system. We have to remember that Kepler's third law emerges naturally from the application of the Newton's Universal Law of Gravitation to the movement of planets and can therefore be generalized to any two bodies orbiting each other. With the application of Kepler's law to the star we are closer to our objective, determining the mas of the invisible compact object around which the other star is orbiting, i.e., determine the mass of the possible black hole. After some mathematical manipulation in the formula of Kepler's third law we end up in a relation between the orbital parameters of the binary system: where M1 and M2 are the masses of the compact object and the companion star respectively, P the orbital period, i.e., the time it takes for the star to complete an orbit, G is the universal gravitational constant, i is the inclination of the orbital plane of the system with with the line of sight of the observer and K2 the radial velocity of the visible star. If we are interested in an lower limit for the mass of the compact object, not exactly its mass, then things are much simpler. The mass of the star M2 can't be smaller than zero, neither the inclination angle can be higher than 90 degrees whi ch implies that the mass of the compact object has to be necessarily bigger than the quantity that is left when we make i= 90º and M2 =0, i.e.: 14 This quantity, called the mass function f(M)is extremely important since it allows us to obtain in simple mode the indirect evidence for the existence of black holes. If f(M) is higher than 3 solar masses, the mass of the compact object will certainly be higher than this limiting value and, as we already discussed, a neutron star must have a limiting mass smaller than this value. So we can conclude that the compact object must be a black hole. It seems very paradoxal that one of the best evidences for the existence of one of the most exotic objects ever imagined by physicists, and the best example of the applicability of general relativity, comes from the application of simple Newtonian mechanics. The radial velocity of the star Fingerprint of the star's chemical components Star with no motion Star moving away Star moving towards the observer Figure 13 The analysis of the spectral lines of a star allows us to determine its composition. When the star is moving the spectral lines appear to be shifted from the position they would have in a stationary reference frame. If the object is moving away from the observer the lines will appear to be shifted towards red. If the object is approaching the observer the lines will appear to be shifted towards the blue part of the electromagnetic spectrum. (Credit: NASA) In order to calculate the mass function, besides the orbital period that can be easily determined by observing the visible star, we also need to know its radial velocity, the velocity in the direction of the observer. This can be determined by the Doppler effect: if an emitting source is moving, the wavelength of the signal , measuring by an observer at rest, changes according to the velocity of the source. This effect explains why the whistle of a train (sound waves) acquire a lower pitch (a smaller 15 wavelength) when it moves away. Although it is not possible to listen to the stars, the Doppler effect can be also applied. The light of the stars are produced by nuclear reactions in their core having to cross the whole star before being released to space. A typical star like our Sun is fundamentally composed by Hydrogen and small quantities of other elements such as Helium, Carbon, Nitrogen, Oxygen, etc. When the light goes through them, these elements absorb certain wavelengths depending on the element. As a result, the observed spectrum is full of lines. In the case of a binar</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="85" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -51878,6 +52108,16 @@
           <t>&lt;p&gt;Ever wondered how buildings are measured and structured orderly so we can live safely in it?&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Oh Yes!  With the knowledge of Trigonometry you can know the correct slope of a roof, the proper height of a building, rise of a stairway and many much more fun stuffs like working on a video game, building different industrial machines and automobiles etc.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Isn't this fun to know, so lets dive in to know more about Trigonometry!!!&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="133" customHeight="1">
       <c r="A26" s="2" t="inlineStr">
@@ -51901,6 +52141,16 @@
           <t>&lt;p&gt;With the unit circle, we see this correspondence (or direct relationship) by definition between the functions sin θ and cos θ and the y-coordinate and the x-coordinate, respectively, of point P much more clearly. When considering the unit circle, we’re dealing with a circle whose center is at the origin O (0,0) and whose radius is one unit in length.  &lt;/p&gt;&lt;p&gt;In the unit circle, the terminal side of any angle θ in standard position intersects the unit circle at a point P(x,y), so that the length of segment OP = r = 1.  Now, substituting r = 1 into the definitions of sine and cosine, we have the following results:&lt;br&gt;sin θ = y/r &lt;br&gt;       = y/1&lt;br&gt;sin θ = y&lt;br&gt; cos θ = x/r &lt;br&gt;       = x/1 &lt;br&gt;cos θ = x&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="25" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -51924,6 +52174,16 @@
         </is>
       </c>
       <c r="E27" s="3" t="n"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="49" customHeight="1">
       <c r="A28" s="2" t="inlineStr">
@@ -51947,6 +52207,16 @@
         </is>
       </c>
       <c r="E28" s="3" t="n"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="49" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -51970,6 +52240,16 @@
         </is>
       </c>
       <c r="E29" s="3" t="n"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="49" customHeight="1">
       <c r="A30" s="2" t="inlineStr">
@@ -51993,6 +52273,16 @@
         </is>
       </c>
       <c r="E30" s="3" t="n"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="97" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -52016,6 +52306,16 @@
           <t>&lt;p&gt;With this ILS you can learn about the vision and perception of colors:&lt;br&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Colors in the nature.&lt;/li&gt;&lt;li&gt; Digital or RGB colors in technology.&lt;/li&gt;&lt;li&gt; Color perception.&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;Target group: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;Age: 10-14 years old.&lt;/li&gt;&lt;/ul&gt;&lt;ul&gt;&lt;li&gt;You can use "The color of the light" laboratory as tool: Use the threesliders (red, green and blue) to select your color combination. Then send the new values to the RGB led and compare the real result with the virtual color square below the sliders.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="121" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -52039,6 +52339,16 @@
           <t>&lt;p&gt;Take a look around the room that you are in. Notice how the various images and colors that you see update constantly as you turn your head and re-direct your attention. Although the images appear to be seamless, each blending imperceptibly into the next, they are in reality being updated almost continuously by the vision apparatus of your eyes and brain. The seamless quality in the images that you see is possible because human vision updates images, including the details of motion and color, on a time scale so rapid that a "break in the action" is almost never perceived.&lt;/p&gt;&lt;p&gt;&lt;br&gt;Watch the video "Simply color mixing" below:&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="109" customHeight="1">
       <c r="A33" s="2" t="inlineStr">
@@ -52062,6 +52372,16 @@
           <t>&lt;p&gt;A concept map is a visual representation of your thoughts, information and knowledge. A concept map contains concepts and relationships between these concepts that are visually represented by means of arrows and colours. This helps you organize information and provides a structure that makes you come up with new ideas more easily.&lt;/p&gt;&lt;br&gt;Tips to create a concept map:&lt;br&gt;&lt;ul&gt;&lt;li&gt;Avoid linking everything to everything and focus on the main relations between concepts.&lt;/li&gt;&lt;li&gt;Also think of concepts that are not related to each other.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="121" customHeight="1">
       <c r="A34" s="2" t="inlineStr">
@@ -52085,6 +52405,16 @@
           <t>&lt;p&gt;&lt;strong&gt;The Physics of Color: How are we able to see things?&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;"Color is the visual effect that is caused by the spectral composition of the light emitted, transmitted, or reflected by objects."&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;strong&gt;1. The Formation of Human Vision:&lt;/strong&gt;&lt;br&gt;Color originates in light. Sunlight, as we perceive it, is colorless. The rainbow is testimony to the fact that all the colors of the spectrum are present in white light. As illustrated in the picture below, light goes from the source (the sun) to the object (the orange), and finally to the detector: the eye and brain (See the figure "How the eye sees" below).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="409.5" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -52108,6 +52438,16 @@
           <t>&lt;p&gt;What is the mechanism that causes the light passing through the optic nerve is shown in our brain as sharp image? The human eye is an organ that reacts to light and has several purposes. As a conscious sense organ, the mammalian eye allows vision. The human eye can distinguish about 10 million colors. &lt;/p&gt;&lt;p&gt;The eyes and a camera share a lot in common. If you want to learn more you can view how the eye works in the following video: &lt;a href="http://www.healthline.com/vpvideo/vision" target="_blank"&gt;http://www.healthline.com/vpvideo/vision&lt;/a&gt;&lt;br&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;2. The Physics of Color:&lt;/strong&gt;&lt;br&gt;How is it possible that people can see some colors and not others?&lt;br&gt;Electromagnetic radiation is characterized by its wavelength (or frequency) and its intensity. When the wavelength is within the visible spectrum (the range of wavelengths humans can perceive, approximately from 390 nm to 700 nm), it is known as "visible light".&lt;br&gt;Most light sources emit light at many different wavelengths; a source's spectrum is a distribution giving its intensity at each wavelength.&lt;br&gt;Why we can see a combination of colors?.&lt;br&gt;When the wavelength is within the visible spectrum (the range of wavelengths humans can perceive, approximately from 390 nm to 700 nm), it is known as "visible light". These combinations offer different colors.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;strong&gt;3. Primary colors:&lt;/strong&gt;&lt;br&gt;Here we will answer the previous questions. What are the primary colors and how their combination can generate other colors, are there different types of combinations?&lt;br&gt;Primary colors (or primary colours) are sets of colors that can be combined to make a useful range of colors. For human applications, three primary colors are usually used, since human color vision is trichromatic. For additive combination of colors, as in overlapping projected lights or in CRTdisplays, the primary colors normally used are red, green, and blue. For subtractive combination of colors, as in mixing of pigments or dyes, such as in printing, the primaries normally used are cyan, magenta, and yellow, though the set of red, yellow, blue is popular among artists (see RGB color model, CMYK color model, and RYB color model for more on these popular sets of primary colors).&lt;br&gt;Any particular choice for a given set of primary colors is derived from the spectral sensitivity of each of the human cone photoreceptors; three colors that fall within each of the sensitivity ranges of each of the human cone cells are red, green, and blue. Other sets of colors can be used, though not all will well approximate the full range of color perception. For example, an early color photographic process, autochrome, typically used orange, green, and violet primaries. However, unless negative amounts of a color are allowed the gamut will be restricted by the choice of primaries. The combination of any two primary colors creates a secondary color (See the primary colors figure below).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="193" customHeight="1">
       <c r="A36" s="2" t="inlineStr">
@@ -52131,6 +52471,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Tips for Research&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Research question: A research question is a question you find interesting to try to answer by conducting research.&lt;/li&gt;&lt;li&gt;Experiment: An experiment is a scientific test in which you perform a series of actions and carefully observe their effects in order to learn about something (http://www.merriam-webster.com/dictionary/experime...).&lt;/li&gt;&lt;li&gt;RGB LED laboratory "The color of the light": In this laboratory there is a lamp that you can turn on and off, and send three different colors mixed to observe the final result.&lt;/li&gt;&lt;/ul&gt;&lt;br&gt;&lt;strong&gt;Tips to set up an experiment:&lt;/strong&gt;&lt;br&gt;&lt;ul&gt;&lt;li&gt;Design experiments to test given theories.&lt;/li&gt;&lt;li&gt;Keep experiments plain and simple.&lt;/li&gt;&lt;li&gt;Vary one thing at a time. Keep in mind that some concepts are made up of multiple concepts (e.g. speed = distance/time).&lt;/li&gt;&lt;li&gt;Keep general settings the same across experiments.&lt;/li&gt;&lt;li&gt;Make use of simple values&lt;/li&gt;&lt;li&gt;Make use of extreme values&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="109" customHeight="1">
       <c r="A37" s="2" t="inlineStr">
@@ -52154,6 +52504,16 @@
         </is>
       </c>
       <c r="E37" s="3" t="n"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="157" customHeight="1">
       <c r="A38" s="2" t="inlineStr">
@@ -52177,6 +52537,16 @@
           <t>&lt;p&gt;Tips for Writing a ConclusionExperiment: &lt;/p&gt;&lt;ul&gt;&lt;li&gt;An experiment is a scientific test in which you perform a series of actions and carefully observe their effects in order to learn about something (&lt;a href="http://www.merriam-webster.com/dictionary/experime...).Research" target="_blank"&gt;http://www.merriam-webster.com/dictionary/experime...&lt;/a&gt; &lt;/li&gt;&lt;li&gt;A research question is a question you find interesting to try to answer by conducting research.&lt;/li&gt;&lt;li&gt;Conclusion tool: The conclusion tool is a tool to help you draw conclusions regarding your research question based on the results you obtained.&lt;/li&gt;&lt;li&gt;Conclusions: Your conclusions summarize how your results answer your original research question (http://www.sciencebuddies.org/science-fair-project...).&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="109" customHeight="1">
       <c r="A39" s="2" t="inlineStr">
@@ -52200,6 +52570,16 @@
           <t>&lt;p&gt;If you cannot answer your research question, ask yourself the following questions:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;Did your research question contain one thing you observed/measured and one thing that influenced this?&lt;/li&gt;&lt;li&gt;Could you answer your research question within the LED RGB laboratory with the objects and equipment available?&lt;/li&gt;&lt;li&gt;Did you design your experiment in such a way that you could answer your research question?&lt;/li&gt;&lt;li&gt;Do you think it is possible to answer your research question if you checked other combinations?&lt;/li&gt;&lt;/ul&gt;When this is not the case, ask your teacher for help.</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="25" customHeight="1">
       <c r="A40" s="2" t="inlineStr">
@@ -52223,6 +52603,16 @@
           <t>&lt;p&gt;Sometimes you can see a rainbow in the sky. When does this happen?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -52246,6 +52636,16 @@
           <t>&lt;p&gt;What could cause that you can see a rainbow?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="37" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -52269,6 +52669,16 @@
           <t>&lt;p&gt;In this lesson you will discover more about this. You will find out whether your thoughts are correct. Press  "The colour of light" to go on.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="85" customHeight="1">
       <c r="A43" s="2" t="inlineStr">
@@ -52292,6 +52702,16 @@
         </is>
       </c>
       <c r="E43" s="3" t="n"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="97" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -52315,6 +52735,16 @@
         </is>
       </c>
       <c r="E44" s="3" t="n"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="37" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -52338,6 +52768,16 @@
           <t>&lt;p&gt;Make further explorations by changing things in the program above. If you're done press "&lt;strong&gt;What did you discover?&lt;/strong&gt;"&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="85" customHeight="1">
       <c r="A46" s="2" t="inlineStr">
@@ -52361,6 +52801,16 @@
         </is>
       </c>
       <c r="E46" s="3" t="n"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="49" customHeight="1">
       <c r="A47" s="2" t="inlineStr">
@@ -52384,6 +52834,16 @@
         </is>
       </c>
       <c r="E47" s="3" t="n"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="73" customHeight="1">
       <c r="A48" s="2" t="inlineStr">
@@ -52407,6 +52867,16 @@
           <t>&lt;p&gt;The École polytechnique fédérale de Lausanne (EPFL) is a research institute and university in Lausanne, Switzerland, that specializes in natural sciences and engineering.[4] It is one of the two Swiss Federal Institutes of Technology, and it has three main missions: education, research and technology transfer at the highest international level.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="229" customHeight="1">
       <c r="A49" s="2" t="inlineStr">
@@ -52430,6 +52900,16 @@
           <t>&lt;p&gt;The roots of modern-day EPFL can be traced back to the foundation of a private school under the name École spéciale de Lausanne in 1853 at the initiative of Lois Rivier, a graduate of the École Centrale Paris and John Gay, the then professor and rector of the Académie de Lausanne. At its inception it had only 11 students and the offices was located at Rue du Valentin in Lausanne. In 1869, it became the technical department of the public Académie de Lausanne. When the Académie was reorganised and acquired the status of a university in 1890, the technical faculty changed its name to École d'ingénieurs de l'Université de Lausanne. In 1946, it was renamed the École polytechnique de l'Université de Lausanne (EPUL). In 1969, the EPUL was separated from the rest of the University of Lausanne and became a federal institute under its current name. EPFL, like ETH Zurich, is thus directly controlled by the Swiss federal government. In contrast, all other universities in Switzerland are controlled by their respective cantonal governments. Following the nomination of Patrick Aebischer as president in 2000, EPFL has started to develop into the field of life sciences. It absorbed the Swiss Institute for Experimental Cancer Research (ISREC) in 2008.[12]&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="133" customHeight="1">
       <c r="A50" s="2" t="inlineStr">
@@ -52453,6 +52933,16 @@
           <t>&lt;p&gt;In 1946, there were 360 students. In 1969, EPFL had 1,400 students and 55 professors. In the past two decades the university has grown rapidly and as of 2012 roughly 14,000 people study or work on campus, about 9,300 of these being Bachelor, Master or PhD students. As EPFL first became a federal institute under its current name in 1969, with a student body of then less than 1500, the university is included in the Times Higher Education list of top 100 universities under 50 years old. The environment at modern day EPFL is highly international with the school now attracting top students and researchers from all over the world. More than 125 countries are represented on the campus and the university has two official languages, French and English.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="409.5" customHeight="1">
       <c r="A51" s="2" t="inlineStr">
@@ -52476,6 +52966,16 @@
           <t>Like every public university in Switzerland, EPFL is obliged to grant admission to every Swiss resident who took the maturitÃ© high-school certificate recognized by the Swiss Federation. However, international students are required to have a final grade average of 80% or above of the maximum grade of the upper secondary school national system. As such, for Swiss students, EPFL is not selective in its undergraduate admission procedures. The real selection process happens during the first year of study. This period is called the propaedeutic cycle and the students must pass a block examination of all the courses taken during the first year at the end of the cycle. If the weighted average is insufficient, a student is required to retake the entire first year of coursework if they wish to continue their studies at the school. Roughly 50% of students fail the first year of study, and many of them choose to drop out rather than repeat the first year.[13] The failure rate for the propaedeutic cycle differs between fields of study, it is highest for Mathematics, Physics and Electrical Engineering majors where only 30""40% of students pass the first year. For foreign students, the selection procedure towards the undergraduate program is rather strict, and since most undergraduate courses are taught in French, foreign students must provide documentation of having acquired a level B2 proficiency as measured on the CEF scale, though C1 proficiency is recommended. As at all universities in Switzerland, the academic year is divided into two semesters. Regular time to reach graduation is six semesters for the Bachelor of Science degree and four additional semesters for the Master of Science degree. Though only 58% of the student's who manage to graduate are able to graduate within this time-period.[13] The possibility to study abroad for one or two semesters is offered during the 3rd year of study under certain conditions as EPFL maintains several long-standing student exchange programs, such as the junior year engineering and science program with Carnegie Mellon University in the United States, as well as a graduate Aeronautics and Aerospace program with the ISAE in France. The final semester is dedicated to writing a thesis. Entrepreneurship is actively encouraged to foster a start-up culture among the student body as evident by the EPFL Innovation Park being an integral part of campus. Since 1997, 12 start-ups have been created per year on average by EPFL students and faculty. In the year 2013, a total of 105 million CHF was raised by EPFL start-ups.[14]</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="395" customHeight="1">
       <c r="A52" s="2" t="inlineStr">
@@ -52499,6 +52999,16 @@
           <t>&lt;p&gt;The three most widely observed international university rankings, QS World University Rankings, Academic Ranking of World Universities and Times Higher Education World University Rankings ranks EPFL 5th, 2nd and 5th respectively in Europe in their 2017 rankings. In the rankings EPFL competes with Cambridge, Oxford, Imperial College London and its sister institution, ETH Zurich, for the European top five spots in Engineering and Technology.&lt;/p&gt;&lt;p&gt;QS World University Ranking 2017/2018 ranks EPFL as the world's 12th best university across all fields, and world 11th in the Natural Sciences subcategory.[15] Academic Ranking of World Universities 2016 ranks EPFL world 11th and Europe 2nd in the Engineering, Technology and Computer Sciences category.[16] THE World University Rankings 2016–2017 ranks EPFL world 11th in the Engineering and Technology subcategory.[17]&lt;br&gt;EPFL typically scores high on faculty to student ratio, international outlook and scientific impact. The specialized CWTS Leiden Ranking[18] that "aims to provide highly accurate measurements of the scientific impact of universities" ranks EPFL world 13th, and 1st in Europe in the 2013 rankings for all the sciences.&lt;br&gt;Although EPFL generally ranks among the worlds best universities on measures such as citation index, international outlook and scientific impact, due to the young age and small size of the school, it tends to rank comparatively low in name-brand surveys. A recent example of this being the Times 2017 reputation ranking where EPFL was ranked world 45th, comparatively low for EPFL.[19] In recent years, multiple EPFL faculty members have been selected as Young Global Leader or as Young Scientist by the World Economic Forum, increasing the visibility of EPFL outside tech circles.[20]&lt;br&gt;The Times 100 Under 50 Rankings is a ranking of the top 100 universities in the world under 50 years old. Since EPFL in its current form was formed in 1969, EPFL is included in this ranking. EPFL was ranked 1st in the world for three years in a row in 2015,[21] 2016 [22][23] and 2017.[24] Times Higher Education also ranked EPFL as the most international university in the world two years in a row 2014[25] and 2015.[26]&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="61" customHeight="1">
       <c r="A53" s="2" t="inlineStr">
@@ -52522,6 +53032,16 @@
         </is>
       </c>
       <c r="E53" s="3" t="n"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="61" customHeight="1">
       <c r="A54" s="2" t="inlineStr">
@@ -52545,6 +53065,16 @@
         </is>
       </c>
       <c r="E54" s="3" t="n"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="409.5" customHeight="1">
       <c r="A55" s="2" t="inlineStr">
@@ -52568,6 +53098,16 @@
           <t>Homepage Hacker Noon AMA W/ BLOCKSTACK CEOAILATESTTOP2.0CRYPTODEVJOIN COMMUNITY A guide to giving your cats their annual performance review Go to the profile of Thryn Thryn Dec 19, 2016  My cat Linus, who is kind of a jerk but I just love his fuzzy little face. As the year draws to a close, it’s time to sit down with your cats and give them feedback on how they’ve been performing. To help you prepare for the conversation, I’ve written a few guidelines from my own experiences.  Evaluate against a standard When thinking about how your cat is meeting expectations, ensure that you are evaluating against a standard. It should take into account the cat’s level which is ultimately based on age and breed. A level 2 cat such as a 6 month old Persian kitten will not have the same performance expectations as a level 5 cat like an 8-year-old gray tabby. Ideally you’ve discussed these expectations with your cat at length. They should be reasonable and achievable while still providing enough of a challenge to allow for personal growth. Some sample performance goals can include: number of hours of expected sleep during the day (aim for 16–18); time spent playing in boxes; level of cuteness on a scale from 1–10 (this should be maintained with self-grooming and a general posture of perky ears and wide eyes).  Focus on impact In order to help your cat grow, your feedback must be specific and actionable. By using the situation-behavior-impact (SBI) model, your cat will be able to understand the rationale behind your feedback. An example conversation might go: “Skittles, when I was sleeping and you jumped on the bed and meowed in my face at 4am, it woke me up and that made me feel angry and tired all day. One way you can have more positive impact is to STFU and sleep until at least 8am.”  How to frame a needs-improvement discussion This can be challenging. Your cat might get defensive, or worse, ignore you entirely and pretend that she doesn’t understand you. Don’t be fooled. She understands everything you say. When your cat is not meeting expectations, you’ll need to be prepared with a performance improvement plan or PIP. This PIP should include specific steps your cat will need to take in order to meet the expectations of her role and level. You can tell her, for example, that the number of times she jumps on the counter and gets her poo-poo paws all over your food prep areas is unacceptable and must be reduced by at least 80% over the next quarter.  It may be necessary to remind her just what a lucky SOB she is to have food and a warm place to sleep on these cold winter nights. Help your cat understand the consequences if performance does not improve. It may be necessary to remind her just what a lucky SOB she is to have food and a warm place to sleep on these cold winter nights. As your cat’s manager, you should also be aware of your own role in her performance. Are you present enough? Does she get adequate space to grow, play? Have you provided the necessary toys and furniture to scratch? It’s unfair to punish your cats for scratching the couch and destroying your nice things if you haven’t given them a proper scratching post.  Cupcake Schoolbus tries to demonstrate impact by destroying my f-ing blinds. When to give team feedback vs individual feedback You should be having regular individual 1:1s with your cats. Any negative feedback should be given privately so as not to embarrass or shame one cat in front of the group. However, some feedback can be given in a group setting when it benefits the whole team. For example, you can share with all of your cats how much you appreciate their adorable fuzzy faces and how cute they are when they make biscuits on your lap before curling up for a good snuggle.  Skittles, I loved that time you tried to jump on the bookshelf but completely missed and fell. I laughed for days. Don’t leave out the positive You might be more concerned with your cat’s negative behaviors but it’s important to show appreciation where it is due. Again, follow the SBI model: “Skittles, I loved that time you tried to jump on the bookshelf but completely missed and fell. I laughed for days. The video got me over 50 likes on Instagram.” Remember it’s your job to support your cats as they grow, encourage them to lean in, and work hard at being cats.  Follow Linus and Cupcake Schoolbus on Instagram @linus_hates_cupcake  CatsLeadershipManagementSatireWork Go to the profile of Thryn Thryn Medium member since Jul 2018 Design Manager at Google  Hacker Noon Hacker Noon how hackers start their afternoons.  Hacker Noon Never miss a story from Hacker Noon, when you sign up for Medium. Learn more</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="25" customHeight="1">
       <c r="A56" s="2" t="inlineStr">
@@ -52595,6 +53135,16 @@
           <t>Sea Order of Magn ude Evaluate Evaluate Evaluate Evaluate Compare nown Valu- caICUIate</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="25" customHeight="1">
       <c r="A57" s="2" t="inlineStr">
@@ -52622,6 +53172,16 @@
           <t>How does an electric car run? FUNCTIONAL MODELING Evaluate Reflect</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="25" customHeight="1">
       <c r="A58" s="2" t="inlineStr">
@@ -52645,6 +53205,16 @@
         </is>
       </c>
       <c r="E58" s="3" t="n"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="59" ht="25" customHeight="1">
       <c r="A59" s="2" t="inlineStr">
@@ -52672,6 +53242,16 @@
           <t>&lt;p&gt;The electric car has a battery which powers a motor that rotates the wheels.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="25" customHeight="1">
       <c r="A60" s="2" t="inlineStr">
@@ -52695,6 +53275,16 @@
         </is>
       </c>
       <c r="E60" s="3" t="n"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="274" customHeight="1">
       <c r="A61" s="2" t="inlineStr">
@@ -52722,6 +53312,16 @@
           <t>From outside most electric cars look exactly like fossil fuel-powered cars. An electric car lacks a tailpipe and gas tank, but the overall structure is basically the same. Under the bonnet, instead of a huge engine all you will see is an electric motor and its controller. The electric motor needs no oil, no tune-ups, and since there is no tailpipe emissions, it does not necessitate any smog checks. The electric vehicle power source is the battery which acts as a "gas tank" and supplies the electric motor with the energy necessary to move the vehicle. This gives the car acceleration. When the vehicle is idle there is no electrical current being processed, so energy is not being used up. The controller acts as a regulator, and controls the amount of power received from the batteries so the motor does not burn out. This battery powers all of the electronic devices in the car, just like the battery in a gas-powered car. Everything else in the electric car is basically the same as its gas-powered equivalent: transmission, brakes, air conditioning, and airbags. Since electric vehicles use an electric motor, the driver can take advantage of the motor's momentum when pressure is applied on the brakes. Instead of converting all the potential energy in the motor into heat like a fossil fuel-powered car does, an electric car uses the forward momentum of the motor to recharge the battery. This process is called regenerative braking. References: 1) http://www.electricvehiclesmalta.eu/e-driving/how-do-electric-vehicles- work 2) https://www.fueleconomy.gov/feg/hybridtech.shtml</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="25" customHeight="1">
       <c r="A62" s="2" t="inlineStr">
@@ -52749,6 +53349,16 @@
           <t>How is the working of the car affected by various parameters? QUALITATIVE MODELING Evaluate Reflect</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="274" customHeight="1">
       <c r="A63" s="2" t="inlineStr">
@@ -52776,6 +53386,16 @@
           <t>From outside most electric cars look exactly like fossil fuel-powered cars. An electric car lacks a tailpipe and gas tank, but the overall structure is basically the same. Under the bonnet, instead of a huge engine all you will see is an electric motor and its controller. The electric motor needs no oil, no tune-ups, and since there is no tailpipe emissions, it does not necessitate any smog checks. The electric vehicle power source is the battery which acts as a "gas tank" and supplies the electric motor with the energy necessary to move the vehicle. This gives the car acceleration. When the vehicle is idle there is no electrical current being processed, so energy is not being used up. The controller acts as a regulator, and controls the amount of power received from the batteries so the motor does not burn out. This battery powers all of the electronic devices in the car, just like the battery in a gas-powered car. Everything else in the electric car is basically the same as its gas-powered equivalent: transmission, brakes, air conditioning, and airbags. Since electric vehicles use an electric motor, the driver can take advantage of the motor's momentum when pressure is applied on the brakes. Instead of converting all the potential energy in the motor into heat like a fossil fuel-powered car does, an electric car uses the forward momentum of the motor to recharge the battery. This process is called regenerative braking. References: 1) http://www.electricvehiclesmalta.eu/e-driving/how-do-electric-vehicles- work 2) https://www.fueleconomy.gov/feg/hybridtech.shtml</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="25" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -52803,6 +53423,16 @@
           <t>How is the power required related to other parameters? QUANTITATIVE MODELING Evaluate Reflect</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="274" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
@@ -52830,6 +53460,16 @@
           <t>From outside most electric cars look exactly like fossil fuel-powered cars. An electric car lacks a tailpipe and gas tank, but the overall structure is basically the same. Under the bonnet, instead of a huge engine all you will see is an electric motor and its controller. The electric motor needs no oil, no tune-ups, and since there is no tailpipe emissions, it does not necessitate any smog checks. The electric vehicle power source is the battery which acts as a "gas tank" and supplies the electric motor with the energy necessary to move the vehicle. This gives the car acceleration. When the vehicle is idle there is no electrical current being processed, so energy is not being used up. The controller acts as a regulator, and controls the amount of power received from the batteries so the motor does not burn out. This battery powers all of the electronic devices in the car, just like the battery in a gas-powered car. Everything else in the electric car is basically the same as its gas-powered equivalent: transmission, brakes, air conditioning, and airbags. Since electric vehicles use an electric motor, the driver can take advantage of the motor's momentum when pressure is applied on the brakes. Instead of converting all the potential energy in the motor into heat like a fossil fuel-powered car does, an electric car uses the forward momentum of the motor to recharge the battery. This process is called regenerative braking. References: 1) http://www.electricvehiclesmalta.eu/e-driving/how-do-electric-vehicles- work 2) https://www.fueleconomy.gov/feg/hybridtech.shtml</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="25" customHeight="1">
       <c r="A66" s="2" t="inlineStr">
@@ -52853,6 +53493,16 @@
         </is>
       </c>
       <c r="E66" s="3" t="n"/>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="25" customHeight="1">
       <c r="A67" s="2" t="inlineStr">
@@ -52876,6 +53526,16 @@
         </is>
       </c>
       <c r="E67" s="3" t="n"/>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="25" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -52899,6 +53559,16 @@
         </is>
       </c>
       <c r="E68" s="3" t="n"/>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="37" customHeight="1">
       <c r="A69" s="2" t="inlineStr">
@@ -52922,6 +53592,16 @@
           <t>&lt;p&gt;FORM ONE,KENYAN CURRICULUM&lt;/p&gt;&lt;p&gt;topic:Particulate nature of matter&lt;br&gt;subtopic: Rate of diffusion&lt;br&gt;objective:To determine factors affecting rate of diffusion&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -52945,6 +53625,16 @@
           <t>&lt;p&gt;1. from the video what is your understanding of diffusion?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -52968,6 +53658,16 @@
           <t>&lt;p&gt;2. How does temperature affects rate of diffusion?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="49" customHeight="1">
       <c r="A72" s="2" t="inlineStr">
@@ -52991,6 +53691,16 @@
         </is>
       </c>
       <c r="E72" s="3" t="n"/>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="73" customHeight="1">
       <c r="A73" s="2" t="inlineStr">
@@ -53014,6 +53724,16 @@
           <t>&lt;p&gt;1. press start button to begin the experiment&lt;/p&gt;&lt;p&gt;2. regulate temperature from low-medium-high by adjusting temperature button&lt;/p&gt;&lt;p&gt;3. regulate molecular mass from low-medium-high by adjusting molecular mass button&lt;/p&gt;&lt;p&gt;4. press 'remove barrier' button to observe how the molecules randomly interact &lt;/p&gt;&lt;p&gt;5. press 'reset experiment' to start again&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="73" customHeight="1">
       <c r="A74" s="2" t="inlineStr">
@@ -53037,6 +53757,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Introduction&lt;/strong&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Plants need light to survive. Plants make their own food from light energy, carbon dioxide, water, nutrients and minerals. The process by which plants use light energy to make their own food is called photosynthesis. During photosynthesis plants produce and release oxygen as a byproduct. Photosynthesis occurs in the green parts of plants.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="49" customHeight="1">
       <c r="A75" s="2" t="inlineStr">
@@ -53060,6 +53790,16 @@
           <t>&lt;p&gt;Next you will explore how light and season of year affect photosynthesis in aquarium plants. Click on the tab &lt;strong&gt;Explore&lt;/strong&gt; at the top of your screen.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="25" customHeight="1">
       <c r="A76" s="2" t="inlineStr">
@@ -53083,6 +53823,16 @@
         </is>
       </c>
       <c r="E76" s="3" t="n"/>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="25" customHeight="1">
       <c r="A77" s="2" t="inlineStr">
@@ -53106,6 +53856,16 @@
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="25" customHeight="1">
       <c r="A78" s="2" t="inlineStr">
@@ -53129,6 +53889,16 @@
         </is>
       </c>
       <c r="E78" s="3" t="n"/>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="25" customHeight="1">
       <c r="A79" s="2" t="inlineStr">
@@ -53152,6 +53922,16 @@
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="37" customHeight="1">
       <c r="A80" s="2" t="inlineStr">
@@ -53175,6 +53955,16 @@
           <t>&lt;p&gt;This is a short investigation in how you deal with the concepts of transcription and translation.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Please watch the following YouTube video:&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="25" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -53198,6 +53988,16 @@
         </is>
       </c>
       <c r="E81" s="3" t="n"/>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="121" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -53221,6 +54021,16 @@
           <t>&lt;p&gt;Use the Haber process to synthesize ammonia (NH3) from nitrogen (N2) and hydrogen (H2), according to the following balanced chemical equation:&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;  N2(g) + 3H2(g)  →2NH3(g)&lt;br&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;As the manager of the plant, your job is to produce the maximum amount of NH3 for the least amount of money during each 24-hour shift.&lt;/p&gt;&lt;p&gt;&lt;br&gt;You can adjust several independent variables using the Control Panel and analyze the results (including yield, time to equilibrium, and net profit) on the output monitor. You’ll want to vary each independent variable to determine how it affects the results.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="25" customHeight="1">
       <c r="A83" s="2" t="inlineStr">
@@ -53244,6 +54054,16 @@
         </is>
       </c>
       <c r="E83" s="3" t="n"/>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="73" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -53267,6 +54087,16 @@
         </is>
       </c>
       <c r="E84" s="3" t="n"/>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="109" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -53290,6 +54120,16 @@
         </is>
       </c>
       <c r="E85" s="3" t="n"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="61" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -53313,6 +54153,16 @@
           <t>&lt;p&gt;The human eye is the organ of sight.&lt;br&gt;The eye organ detects light, and converts it to electrochemical impulses in neurons.&lt;br&gt;Rod and cone cells in the retina allow us see light, figure out &lt;br&gt;perception of depth (how near and far objects are) and to differentiate &lt;br&gt;color.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="87" ht="85" customHeight="1">
       <c r="A87" s="2" t="inlineStr">
@@ -53336,6 +54186,16 @@
           <t>&lt;p&gt;The individual components of the eye work in a manner similar to a &lt;br&gt;camera. Each part plays a vital role in providing clear vision. A human &lt;br&gt;eye is like a camera with the cornea, which is like a lens cover. As the&lt;br&gt; eye’s main focusing element, the cornea takes widely diverging rays of &lt;br&gt;light and bends them through the pupil, the dark, round opening in the &lt;br&gt;center of the colored iris. The iris and pupil act like the aperture of a&lt;br&gt; camera.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="88" ht="217" customHeight="1">
       <c r="A88" s="2" t="inlineStr">
@@ -53359,6 +54219,16 @@
           <t>&lt;p&gt;Next in line is the lens which acts like the lens in a camera, helping to focus light to the back of the eye.&lt;br&gt;The very back of the eye is lined with a layer called the retina &lt;br&gt;which is similar to the film in a camera. The retina is a membrane &lt;br&gt;containing photoreceptor nerve cells that line the inside back wall of &lt;br&gt;the eye. The receptor cells (rods and cones) of the retina change the &lt;br&gt;light rays into electrical impulses and send them through the optic &lt;br&gt;nerve to the brain where an image is perceived. The center 10% of the &lt;br&gt;retina is called the macula. This is responsible for your sharp vision, &lt;br&gt;your reading vision.&lt;br&gt;The peripheral retina is responsible for the peripheral vision. As &lt;br&gt;with the camera, if the “film” is bad in the eye (i.e. the retina), no &lt;br&gt;matter how good the rest of the eye is you will not get a good picture.&lt;br&gt;The human eye is remarkable. It accommodates to changing lighting &lt;br&gt;conditions and focuses light rays originating from various distances &lt;br&gt;from the eye. When all of the components of the eye function properly, &lt;br&gt;light is converted to impulses and conveyed to the brain where an image &lt;br&gt;is perceived.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -53382,6 +54252,16 @@
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="90" ht="25" customHeight="1">
       <c r="A90" s="2" t="inlineStr">
@@ -53405,6 +54285,16 @@
           <t>&lt;ul&gt;&lt;li&gt;Concentrated refers to chemical solutions that have high concentrations of a large amount of solute in the solution&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="91" ht="25" customHeight="1">
       <c r="A91" s="2" t="inlineStr">
@@ -53428,6 +54318,16 @@
           <t>&lt;em&gt;&lt;/em&gt;&lt;strong&gt;&lt;/strong&gt;Dilute solutions contains a small amount of solvent compared with the amount of solvent</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="92" ht="37" customHeight="1">
       <c r="A92" s="2" t="inlineStr">
@@ -53451,6 +54351,16 @@
         </is>
       </c>
       <c r="E92" s="3" t="n"/>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="93" ht="97" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -53474,6 +54384,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;Each DNA nucleotide consists of a nitrogenous base (adenine, thymine, cytosine or guanine), a sugar (deoxyribose) and a phosphate group. There are four different types of nucleotides that differ on the nitrogenous base.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;Having remembered what we already know, it is time to move on to the next phase!&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="94" ht="61" customHeight="1">
       <c r="A94" s="2" t="inlineStr">
@@ -53497,6 +54417,16 @@
         </is>
       </c>
       <c r="E94" s="3" t="n"/>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="37" customHeight="1">
       <c r="A95" s="2" t="inlineStr">
@@ -53520,6 +54450,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;Watch the rest of the video to remember what we have learned about proteins and amino acids.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="96" ht="49" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -53543,6 +54483,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;Perhaps the conceptual map has helped you answer the question you created. The rest of the video we watch will help you confirm your thoughts!&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="97" ht="97" customHeight="1">
       <c r="A97" s="2" t="inlineStr">
@@ -53566,6 +54516,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;As you may have concluded so far, genetic information is used to direct protein synthesis that takes place in the cell's ribosomes. The sequence of bases in a DNA strand is the code to create a protein (just like a recipe book contains the recipe for making your favorite food!). The genetic code consists of codons, meaning that every three bases correspond to an amino acid. A gene is a sequence of bases encoding a particular protein.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="98" ht="85" customHeight="1">
       <c r="A98" s="2" t="inlineStr">
@@ -53589,6 +54549,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;The laboratory below depicts two DNA strands in the nucleus of a cell. Press the 'Prepare for transcription' button and then select the correct nitrogenous bases according to the Base Pairing Rule.&lt;/p&gt;&lt;p&gt;Note: The U symbol you find in the lab is the nitrogenous base uracil, which is found in the RNA molecule, which we will talk about later. Uracil pairs with adenine.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="99" ht="73" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -53612,6 +54582,16 @@
           <t>&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;Once created, the mRNA molecules move from the nucleus to the cytoplasm and carry the 'message' for protein synthesis to the ribosomes.&lt;/p&gt;&lt;p&gt;In the virtual lab that follows, click the 'Translate' button to carefully follow up the process.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -53635,6 +54615,16 @@
         </is>
       </c>
       <c r="E100" s="3" t="n"/>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="157" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -53658,6 +54648,16 @@
           <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;&lt;p&gt;The process you watched in the second virtual lab is called the translation of DNA, during which the nucleotide codons are 'translated' into amino acids. The molecules depicted in green in the lab are called transfer RNA or tRNA. Each tRNA molecule transfers an amino acid to the ribosome, while at its other end there is an anti-codon recognized by the complementary codon of the mRNA. In this way the tRNAs bring the appropriate amino acids to the ribosome, where they are bonded to form proteins with a specific amino acid sequence.&lt;/p&gt;&lt;p&gt;Another type of RNA molecules are the ribosomal RNAs or rRNAs, which bind to specific proteins and form ribosomes.&lt;/p&gt;&lt;p&gt;You are now ready to proceed to the next phase of the course.&lt;/p&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="102" ht="97" customHeight="1">
       <c r="A102" s="2" t="inlineStr">
@@ -53681,6 +54681,16 @@
         </is>
       </c>
       <c r="E102" s="3" t="n"/>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="103" ht="409.5" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -53704,6 +54714,16 @@
         </is>
       </c>
       <c r="E103" s="3" t="n"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -53727,6 +54747,16 @@
         </is>
       </c>
       <c r="E104" s="3" t="n"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="105" ht="169" customHeight="1">
       <c r="A105" s="2" t="inlineStr">
@@ -53750,6 +54780,16 @@
         </is>
       </c>
       <c r="E105" s="3" t="n"/>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="106" ht="37" customHeight="1">
       <c r="A106" s="2" t="inlineStr">
@@ -53773,6 +54813,16 @@
         </is>
       </c>
       <c r="E106" s="3" t="n"/>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="107" ht="25" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -53796,6 +54846,16 @@
         </is>
       </c>
       <c r="E107" s="3" t="n"/>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="108" ht="169" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -53819,6 +54879,16 @@
         </is>
       </c>
       <c r="E108" s="3" t="n"/>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="109" ht="49" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -53842,6 +54912,16 @@
         </is>
       </c>
       <c r="E109" s="3" t="n"/>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="110" ht="25" customHeight="1">
       <c r="A110" s="2" t="inlineStr">
@@ -53865,6 +54945,16 @@
         </is>
       </c>
       <c r="E110" s="3" t="n"/>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="111" ht="193" customHeight="1">
       <c r="A111" s="2" t="inlineStr">
@@ -53888,6 +54978,16 @@
           <t>Hello Scientists!! We already know about the property of rectilinear propagation of light, that is, light travels in a straight line. Formation of shadows and eclipses are direct consequences of rectilinear propagation of light. Similarly, formation of day and night suggests that light travels in a straight line (see the figure below). If it was not so, the light would have curved around the earth and there would have been sunlight during night. When a beam of sunlight enters a dark room through a small hole, we can see a beam of light travelling in a straight line. Watch the demonstration of the rectilinear propagation of light below. Here, three cardboards are taken (A,B and C) with fine holes at their centres. A lighted candle is placed on one side and boards are arranged such that the holes are in the straight line. Viewing from the other side, it is found that light from the candle is seen only if all the three holes are in the straight line. If one of the cardboard is displaced sideways, light is no longer seen. This clearly shows that light travels in a straight line.</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -53911,6 +55011,16 @@
         </is>
       </c>
       <c r="E112" s="3" t="n"/>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="113" ht="49" customHeight="1">
       <c r="A113" s="2" t="inlineStr">
@@ -53934,6 +55044,16 @@
         </is>
       </c>
       <c r="E113" s="3" t="n"/>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="114" ht="25" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -53957,6 +55077,16 @@
         </is>
       </c>
       <c r="E114" s="3" t="n"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="115" ht="25" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -53980,6 +55110,16 @@
           <t>&lt;p&gt;Today we will be learning Quadratic Equation &lt;/p&gt;&lt;p&gt;using the quadratic  formula.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="25" customHeight="1">
       <c r="A116" s="2" t="inlineStr">
@@ -54003,6 +55143,16 @@
         </is>
       </c>
       <c r="E116" s="3" t="n"/>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="61" customHeight="1">
       <c r="A117" s="2" t="inlineStr">
@@ -54026,6 +55176,16 @@
         </is>
       </c>
       <c r="E117" s="3" t="n"/>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="25" customHeight="1">
       <c r="A118" s="2" t="inlineStr">
@@ -54049,6 +55209,16 @@
           <t>&lt;p&gt;ALl quadratic equations could be solved using graphical formular method.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -54072,6 +55242,16 @@
           <t>&lt;p&gt;if y=0 and a,b,c are known then we can get values for x.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -54095,6 +55275,16 @@
           <t>&lt;p&gt;Both methods give the same values for x.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="25" customHeight="1">
       <c r="A121" s="2" t="inlineStr">
@@ -54118,6 +55308,16 @@
         </is>
       </c>
       <c r="E121" s="3" t="n"/>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="229" customHeight="1">
       <c r="A122" s="2" t="inlineStr">
@@ -54141,6 +55341,16 @@
         </is>
       </c>
       <c r="E122" s="3" t="n"/>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="25" customHeight="1">
       <c r="A123" s="2" t="inlineStr">
@@ -54164,6 +55374,16 @@
         </is>
       </c>
       <c r="E123" s="3" t="n"/>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="25" customHeight="1">
       <c r="A124" s="2" t="inlineStr">
@@ -54187,6 +55407,16 @@
         </is>
       </c>
       <c r="E124" s="3" t="n"/>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -54210,6 +55440,16 @@
         </is>
       </c>
       <c r="E125" s="3" t="n"/>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="157" customHeight="1">
       <c r="A126" s="2" t="inlineStr">
@@ -54233,6 +55473,16 @@
         </is>
       </c>
       <c r="E126" s="3" t="n"/>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="25" customHeight="1">
       <c r="A127" s="2" t="inlineStr">
@@ -54256,6 +55506,16 @@
           <t>&lt;p&gt;predict the colour changes.&lt;/p&gt;&lt;p&gt;what happens if water is add to the solution?&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="73" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -54279,6 +55539,16 @@
         </is>
       </c>
       <c r="E128" s="3" t="n"/>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="37" customHeight="1">
       <c r="A129" s="2" t="inlineStr">
@@ -54302,6 +55572,16 @@
         </is>
       </c>
       <c r="E129" s="3" t="n"/>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="37" customHeight="1">
       <c r="A130" s="2" t="inlineStr">
@@ -54325,6 +55605,16 @@
         </is>
       </c>
       <c r="E130" s="3" t="n"/>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="61" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -54348,6 +55638,16 @@
         </is>
       </c>
       <c r="E131" s="3" t="n"/>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="25" customHeight="1">
       <c r="A132" s="2" t="inlineStr">
@@ -54371,6 +55671,16 @@
         </is>
       </c>
       <c r="E132" s="3" t="n"/>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="145" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -54394,6 +55704,16 @@
         </is>
       </c>
       <c r="E133" s="3" t="n"/>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="49" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -54417,6 +55737,16 @@
         </is>
       </c>
       <c r="E134" s="3" t="n"/>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="37" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -54440,6 +55770,16 @@
         </is>
       </c>
       <c r="E135" s="3" t="n"/>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="409.5" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -54463,6 +55803,16 @@
         </is>
       </c>
       <c r="E136" s="3" t="n"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="49" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
@@ -54486,6 +55836,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Step 2: Informative Video&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;According to evolutionary theory many animals, including humans, are attracted to certain physical characteristics. Let's watch a video from Hank's Science Show about Why Sexy is Sexy.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="169" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -54509,6 +55869,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Step 4: Background Information on Guppies&lt;/strong&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;Our inquiry investigation about natural and sexual selection will use the online virtual laboratory Sexual Selection in Guppies. The guppy is a fascinating type of fish. Please read the introduction about &lt;a href="http://en.wikipedia.org/wiki/Guppy" target="_blank"&gt;guppies in the Wikipedia article&lt;/a&gt; to acquire background information about them.&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Have you finished reading about guppies? If so you can now move on to the next phase by clicking on the Conceptualization tab at the top of your screen.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="73" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -54532,6 +55902,16 @@
           <t>&lt;p&gt;Figure 1. Three plots (A, B and C) of long-term trends in the average number of spots per male guppy.&lt;/p&gt;&lt;p&gt;In order to determine which variables are responsible for the trends in plots A, B and C you should familiarize yourself with the descriptions of important variables that can be varied in the virtual laboratory. Table 1 shows these variables and their descriptions.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="193" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -54555,6 +55935,16 @@
           <t>&lt;!DOCTYPE HTML&gt; &lt;html&gt; &lt;head&gt; &lt;meta charset="utf-8"&gt; &lt;title&gt;Sexual Selection in Guppies&lt;/title&gt;    &lt;style&gt; body {  font-family: Helvetica; } table {  width:100%; } table, th, td {  border: 1px solid black;  border-collapse: collapse; } th, td {  padding: 5px;  text-align:left; } table#tguppy tr:nth-child(even) {  background-color: #eee; } table#tguppy tr:nth-child(odd) {  background-color:#fff; } table#tguppy th {  background-color: #5050d2;  color: white; } &lt;/style&gt; &lt;/head&gt;   &lt;body&gt;  &lt;h3&gt;Table 1. Variables and their descriptions in the virtual laboratory &lt;i&gt;Sexual Selection in Guppies.&lt;/i&gt; &lt;/h3&gt;  &lt;table id="tguppy"&gt;  &lt;tr&gt;   &lt;th&gt;Variable&lt;/th&gt;   &lt;th&gt;Description&lt;/th&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Number of guppies&lt;/td&gt;   &lt;td&gt;The starting population size of guppies&lt;/td&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Female preference&lt;/td&gt;   &lt;td&gt;The likelihood that a female guppy will reject a male with less than the average number of spots&lt;/td&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Number of predators&lt;/td&gt;   &lt;td&gt;The number of pike predators in the environment&lt;/td&gt;  &lt;/tr&gt; &lt;/table&gt;  &lt;/body&gt; &lt;/html&gt;</t>
         </is>
       </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="141" ht="181" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
@@ -54578,6 +55968,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Congratulations! &lt;/strong&gt;&lt;/p&gt;&lt;p&gt;You have now completed your inquiry learning experience. &lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Additional information:&lt;/strong&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;The original research article by John Endler on natural selection in guppies is entitled &lt;a href="http://www.mhhe.com/biosci/genbio/raven6/lab6/labs/lab6/resources/original.pdf" target="_blank"&gt;"Natural selection on color patterns in Poecillia reticulata"&lt;/a&gt; and was published in 1980 in the journal Evolution.&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="142" ht="73" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -54605,6 +56005,16 @@
           <t>&lt;p&gt;A. Geometrical properties of common solids&lt;/p&gt;&lt;p&gt;&lt;br&gt;B.  Skew lines and projection of a line onto a plane &lt;/p&gt;&lt;p&gt;&lt;br&gt;C.  Length of a line in 3 - dimensional geometry &lt;/p&gt;&lt;p&gt;&lt;br&gt;D.  The angle between&lt;/p&gt;&lt;p&gt;(a)   a line and a line &lt;br&gt;(b)  a line and a plane    &lt;br&gt;(c)   a plane and a plane  &lt;/p&gt;&lt;p&gt;    &lt;br&gt;E. Angles between skew lines&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="143" ht="37" customHeight="1">
       <c r="A143" s="2" t="inlineStr">
@@ -54628,6 +56038,16 @@
         </is>
       </c>
       <c r="E143" s="3" t="n"/>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -54651,6 +56071,16 @@
         </is>
       </c>
       <c r="E144" s="3" t="n"/>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="145" ht="133" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -54674,6 +56104,16 @@
           <t>&lt;p&gt;Do you know that you can collaborate with students from other parts of the world? See this cool project below where you can  measure the UV levels in your town and study the level of awareness of your family, and then compare it with the results from other students!&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Before you begin you will need the following materials:&lt;/p&gt;&lt;p&gt; - UV light sensitive beads - your teacher can find them &lt;a href="https://www.teachersource.com/product/purple-uv-beads/light-ultraviolet" target="_blank"&gt;here&lt;/a&gt; (or in Amazon with the keywords "UV beads"&lt;/p&gt;&lt;p&gt;- The UV radiation scale - you can find it &lt;a href="https://idiverse.eu/wp-content/uploads/2019/04/UV-light-scale.pdf" target="_blank"&gt;here&lt;/a&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="146" ht="37" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -54697,6 +56137,16 @@
         </is>
       </c>
       <c r="E146" s="3" t="n"/>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="147" ht="181" customHeight="1">
       <c r="A147" s="2" t="inlineStr">
@@ -54720,6 +56170,16 @@
           <t>&lt;p&gt;Great Job. Now you can move to the next phase&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Note:&lt;/strong&gt; In this exercise we use a standardized UV scale, to allow for the comparison of results measures by different students in different locations.&lt;/p&gt;&lt;p&gt;The UV Index is an internationally standardised open ended numerical scale developed by the World Health Organization that measures the amount of UV radiation reaching the earth’s surface. It begins at zero and has no upper limit.  The UV Index is often represented as a number line with accompanying action statements and descriptive words which convey UV intensity. (&lt;a href="https://www.myuv.com.au/about-uv/" target="_blank"&gt;https://www.myuv.com.au/about-uv/&lt;/a&gt;)&lt;br&gt;You  can check the value of the level of UV radiation around the world in &lt;a href="https://www.uvlens.com/" target="_blank"&gt;https://www.uvlens.com/&lt;/a&gt; or  use a mobile app.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="148" ht="157" customHeight="1">
       <c r="A148" s="2" t="inlineStr">
@@ -54743,6 +56203,16 @@
           <t>&lt;p&gt;Now, let's make an experiment to see if your predictions are correct. Our goal? To test the different ways of protecting the skin you mentioned above (the effective and non-effective) and see how they work in blocking UV radiation.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Materials you will need:&lt;/p&gt;&lt;p&gt; - UV sensitive beads (as in previous phase)&lt;br&gt;&lt;/p&gt;&lt;p&gt; - UV level scale (as in previous phase)&lt;br&gt; - Sunscreen bottles of different protective factors (ex. 10, 30 and 50)&lt;br&gt; - Creativity to come up with all other important materials&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Optional:&lt;/p&gt;&lt;p&gt; - UV lantern to replace direct sun light (in case you have a cloudy day)&lt;/p&gt;&lt;p&gt;Tips: you might want to bring a Tanner, for example, to your experiment ;)&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Make a list with all your materials and make sure you bring them to your experiment.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="49" customHeight="1">
       <c r="A149" s="2" t="inlineStr">
@@ -54766,6 +56236,16 @@
           <t>&lt;p&gt;Make sure you have made all the experiments you wanted to make. Don't worry if something went wrong, you can always repeat your experiment.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;When you finish, go to the "conclusion" phase&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="85" customHeight="1">
       <c r="A150" s="2" t="inlineStr">
@@ -54789,6 +56269,16 @@
           <t>&lt;p&gt;Great work dear scientist!&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Now, here is a challenge for you and for your colleagues:&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;In this activity you have learned about the benefits and the dangers of UV rays, you have evaluated the level of awareness of your community, you have learned about the different UV levels throughout the day and in other places of the world and you have learned about the effective ways of protecting the skin against UV damage.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="61" customHeight="1">
       <c r="A151" s="2" t="inlineStr">
@@ -54812,6 +56302,16 @@
         </is>
       </c>
       <c r="E151" s="3" t="n"/>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -54835,6 +56335,16 @@
         </is>
       </c>
       <c r="E152" s="3" t="n"/>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="25" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -54858,6 +56368,16 @@
         </is>
       </c>
       <c r="E153" s="3" t="n"/>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="25" customHeight="1">
       <c r="A154" s="2" t="inlineStr">
@@ -54881,6 +56401,16 @@
           <t>&lt;p&gt;Use the app to investigate some substances to see whether they are acidic or basic...enjoy.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="25" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
@@ -54904,6 +56434,16 @@
           <t>&lt;p&gt;When you understand what an acid or a base is,  review the video on the chemical reaction of HCl on CaCO3.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="37" customHeight="1">
       <c r="A156" s="2" t="inlineStr">
@@ -54927,6 +56467,16 @@
         </is>
       </c>
       <c r="E156" s="3" t="n"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="252" customHeight="1">
       <c r="A157" s="2" t="inlineStr">
@@ -54950,6 +56500,16 @@
           <t>&lt;p&gt;In order for a bulb to light up, we need to have a wire, a battery, and a bulb connected in a proper way to create a close circuit. This arrangement is called a “&lt;strong&gt;simple electrical circuit&lt;/strong&gt;". Each of the three electrical elements of the simple electric circuit (namely, the wire, the battery, and the bulb) has two electrical ends, which are called “&lt;strong&gt;conductive parts&lt;/strong&gt;". Conductive parts must connect in series in a closed circular arrangement. This means that one of the conductive parts of the battery needs to connect to a conductive part of the bulb. The free part of the bulb connects to an end of the wire and the free end of the wire connects to the free part of the battery. The battery creates a&lt;strong&gt; potential difference&lt;/strong&gt;, which is called “&lt;strong&gt;voltage&lt;/strong&gt;", and forces electrons to flow from the negative to the positive side of the battery. More specifically, the chemical reactions in a battery cause a buildup of electrons at the negative pole of the battery and thus there is an electrical difference between the two sides (the negative and the positive). The electrons want to move to a place with fewer electrons, but this cannot be done through the battery. When a circuit is closed (that means the two sides of a battery are connected with a conductive material) electrons find a way to move from the negative to the positive side.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="37" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -54973,6 +56533,16 @@
         </is>
       </c>
       <c r="E158" s="3" t="n"/>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="159" ht="121" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
@@ -54996,6 +56566,16 @@
           <t>&lt;ul&gt;&lt;li&gt;A good hypothesis can be formulated in the form of an "&lt;strong&gt;If ... then...&lt;/strong&gt;" statement, which will include &lt;strong&gt;one independent variable&lt;/strong&gt; and &lt;strong&gt;at least one dependent variable&lt;/strong&gt;. This is an example of how variables are linked in a hypothesis: "&lt;strong&gt;If the independent variable increases, then the dependent variable decreases.&lt;/strong&gt;"&lt;/li&gt;&lt;li&gt;Remember that a hypothesis might not be confirmed after the experimentation. This is not a problem. Many scientific experiments have led to valuable knowledge because they resulted in the rejection of a hypothesis.&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="160" ht="37" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -55019,6 +56599,16 @@
           <t>&lt;p style="text-align: center;"&gt;&lt;strong&gt;If the relation between the variables that you have investigated is clear, you can move to the next phase.&lt;/strong&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="161" ht="97" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -55042,6 +56632,16 @@
           <t>&lt;ul&gt;&lt;li&gt;What was your expert’s hypothesis?&lt;/li&gt;&lt;li&gt;What was the experimental procedure that you have followed to test your expert’s hypothesis?&lt;ul&gt;&lt;li&gt;Which was the independent variable? &lt;/li&gt;&lt;li&gt;Which was the dependent variable?&lt;/li&gt;&lt;li&gt;What other variables were involved in your experiment and how did you treat them?&lt;/li&gt;&lt;/ul&gt;&lt;/li&gt;&lt;li&gt;Did your experimental data support your expert’s hypothesis?&lt;/li&gt;&lt;li&gt;What is the relation between the dependent and the independent variable?&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="162" ht="49" customHeight="1">
       <c r="A162" s="2" t="inlineStr">
@@ -55065,6 +56665,16 @@
         </is>
       </c>
       <c r="E162" s="3" t="n"/>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="163" ht="25" customHeight="1">
       <c r="A163" s="2" t="inlineStr">
@@ -55088,6 +56698,16 @@
         </is>
       </c>
       <c r="E163" s="3" t="n"/>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="164" ht="49" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -55111,6 +56731,16 @@
         </is>
       </c>
       <c r="E164" s="3" t="n"/>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="165" ht="49" customHeight="1">
       <c r="A165" s="2" t="inlineStr">
@@ -55134,6 +56764,16 @@
         </is>
       </c>
       <c r="E165" s="3" t="n"/>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="166" ht="97" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -55157,6 +56797,16 @@
         </is>
       </c>
       <c r="E166" s="3" t="n"/>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="49" customHeight="1">
       <c r="A167" s="2" t="inlineStr">
@@ -55184,6 +56834,16 @@
           <t>Mitochondria Intermediate fi lament Plasma membrane Riboscmes Rough endoplasmic Microlubule reticulum Centrosome Nucleolus Microlilament Chromatin Golgi apparatus Smooth endoplasmic reticulum Secrelory vesicle Golgi vesicle Peroxiscme Cytoplasm</t>
         </is>
       </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="25" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -55211,6 +56871,16 @@
           <t>The Cell Nucleus Muclur Envelope Chmmosomes Cnmnmln</t>
         </is>
       </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="37" customHeight="1">
       <c r="A169" s="2" t="inlineStr">
@@ -55234,6 +56904,16 @@
         </is>
       </c>
       <c r="E169" s="3" t="n"/>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="85" customHeight="1">
       <c r="A170" s="2" t="inlineStr">
@@ -55261,6 +56941,16 @@
           <t>Prukuruall: cell Eukuruouc cell</t>
         </is>
       </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="49" customHeight="1">
       <c r="A171" s="2" t="inlineStr">
@@ -55284,6 +56974,16 @@
         </is>
       </c>
       <c r="E171" s="3" t="n"/>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="145" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -55307,6 +57007,16 @@
         </is>
       </c>
       <c r="E172" s="3" t="n"/>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="61" customHeight="1">
       <c r="A173" s="2" t="inlineStr">
@@ -55330,6 +57040,16 @@
         </is>
       </c>
       <c r="E173" s="3" t="n"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="49" customHeight="1">
       <c r="A174" s="2" t="inlineStr">
@@ -55353,6 +57073,16 @@
         </is>
       </c>
       <c r="E174" s="3" t="n"/>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="37" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -55376,6 +57106,16 @@
         </is>
       </c>
       <c r="E175" s="3" t="n"/>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="49" customHeight="1">
       <c r="A176" s="2" t="inlineStr">
@@ -55399,6 +57139,16 @@
         </is>
       </c>
       <c r="E176" s="3" t="n"/>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="61" customHeight="1">
       <c r="A177" s="2" t="inlineStr">
@@ -55422,6 +57172,16 @@
         </is>
       </c>
       <c r="E177" s="3" t="n"/>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="61" customHeight="1">
       <c r="A178" s="2" t="inlineStr">
@@ -55445,6 +57205,16 @@
         </is>
       </c>
       <c r="E178" s="3" t="n"/>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="37" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
@@ -55468,6 +57238,16 @@
         </is>
       </c>
       <c r="E179" s="3" t="n"/>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -55491,6 +57271,16 @@
         </is>
       </c>
       <c r="E180" s="3" t="n"/>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="169" customHeight="1">
       <c r="A181" s="2" t="inlineStr">
@@ -55514,6 +57304,16 @@
           <t>&lt;p&gt;&lt;strong&gt;DNA...What is next?&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Population genetics is a subfield of genetics that deals with genetic differences within and between populations, and is a part of evolutionary biology. &lt;br&gt;Studies in this branch of biology examine such phenomena as adaptation, speciation, and population structure.&lt;/p&gt;&lt;p&gt;Evolution and Genetics&lt;/p&gt;&lt;p&gt;&lt;br&gt;When Darwin first published his seminal work “On the Origin of Species By Means of Natural Selection” in 1859, Mendel’s work on heredity was largely unknown. Since then, the study of &lt;br&gt;evolution has moved into the “modern synthesis” combining evolutionary theory with current understanding of genetics. &lt;/p&gt;&lt;p&gt;In fact, biological evolution is now defined as: changes in allele proportions within a population over time. Models in this section explore various mechanisms that affect allele proportions in populations.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="157" customHeight="1">
       <c r="A182" s="2" t="inlineStr">
@@ -55537,6 +57337,16 @@
           <t>&lt;p&gt;Natural selection and other components of evolutionary theory are known to be particularly &lt;br&gt;challenging concepts for students to understand. To help illustrate these concepts, you will investigate a simulation model of microevolutionary processes. The model features all the components of Hardy-Weinberg theory, with population size, selection, gene flow, nonrandom mating, and mutation all being demonstrated in the simulations. &lt;/p&gt;&lt;p&gt;By using this freely available computer model, students can develop and test hypotheses with replicated virtual experiments. Because the model is an agent-based simulation, there is biologically realistic variability in the results. Students using the model see results both numerically and graphically and these are reinforced by an animation of the virtual fish&lt;br&gt; in the simulated experiment.&lt;br&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="73" customHeight="1">
       <c r="A183" s="2" t="inlineStr">
@@ -55560,6 +57370,16 @@
         </is>
       </c>
       <c r="E183" s="3" t="n"/>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="217" customHeight="1">
       <c r="A184" s="2" t="inlineStr">
@@ -55583,6 +57403,16 @@
           <t>&lt;p&gt;Random  genetic  drif tis  the  accumulation  of  changes  in  allele  proportions in  populations &lt;br&gt;over generations.    It  is  the  effect  of  sampling  error  in  the  sense  that  an  individual’s  genotype  is essentially a ‘random draw’ from the gene pool of the previous generation.  &lt;br&gt;Thus, over time the proportion of an allele can ‘drift’ up or down over time. &lt;/p&gt;&lt;p&gt;It is important to note that this is not due to any advantage or disadvantage associated with the allele (selection).   Just as statistical error is greater with small sample sizes, genetic drift particularly affects small populations.&lt;br&gt;This  model  is  an  adaptation  of the  classic experiment  conducted  by  Peter  Buri  (1956), which documented genetic drift in laboratory populations of  Drosophila.&lt;/p&gt;&lt;p&gt;In this model, there are  two  alleles for  a  gene  coding  for  eye  color:  the  dominant  wild  type  allele  (+)  codes  for  red  eye color, while the recessive mutant allele (bw) codes for brown eye  color.  In the model, ten  vials (populations)  of  flies are held  at  a  constant  population  size and&lt;br&gt;the  proportions of  the bw allele  are tracked over generations (Figure 1).  The population size and the initial allele proportion can be manipulated.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="263" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -55606,6 +57436,16 @@
           <t>&lt;p style="margin-left: 120px;"&gt;&lt;strong&gt;Directions for using Experimental Design Tool &lt;/strong&gt;&lt;em&gt;&lt;br&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;Setup Resets the model to the parameters shown&lt;br&gt;Go Sets the model in motion, individuals breeding and dying&lt;br&gt;Speed Slider Above the world view, adjusts the simulation speed&lt;br&gt;Mainland-K The stable population size of the mainland&lt;br&gt;Stop-at-Fixation Stops the simulation if a mainland allele proportion hits 1.0&lt;br&gt;Bottleneck-Size The number that will survive a bottleneck event&lt;br&gt;Bottleneck Culls the mainland population to the Bottleneck-Size&lt;br&gt;Colonize-(1 &amp; 2)&lt;br&gt;Seeds the an island from a founding population&lt;br&gt;Isle-1 is founded from the mainland, and Isle-2 from Isle-1&lt;br&gt;(note: there must be enough individuals in the source population to seed the new&lt;br&gt;population&lt;br&gt;Founding-N-(1 &amp; 2) The number of founding individuals&lt;br&gt;Isle-(1 &amp; 2)-K The stable population sizes of the islands&lt;br&gt;Clear (1 &amp; 2) Removes all individuals from the associated island&lt;br&gt;Reporter Description&lt;br&gt;Mainland Allele Props. Proportion of the Yellow, Blue, and Red alleles on mainland&lt;br&gt;Mainland Allele Graph Graph of the allele proportions over time&lt;br&gt;N The current mainland population size&lt;br&gt;Generation The number of generations since the start of the simulation&lt;br&gt;Island Allele Props. Proportion of the Yellow, Blue, and Red alleles on the islands&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="61" customHeight="1">
       <c r="A186" s="2" t="inlineStr">
@@ -55629,6 +57469,16 @@
         </is>
       </c>
       <c r="E186" s="3" t="n"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="285" customHeight="1">
       <c r="A187" s="2" t="inlineStr">
@@ -55652,6 +57502,16 @@
           <t>&lt;p class="MsoNormal"&gt;&lt;em&gt;When the biologist John Endler observed wild guppies in Trinidad in the 1970s, he was puzzled by the fact that male guppies exhibited a wide variation in physical appearance depending on which part of a stream they lived in. Male guppies in one part of a stream had many colourful spots on their sides, whereas male guppies in another location were relatively dull and showed only a few spots. Something must have been responsible for causing these variations.&lt;/em&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;br&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;&lt;strong&gt;Step 1: Introduction to Guppy Experiments&lt;/strong&gt;&lt;/p&gt;&lt;p class="MsoNormal"&gt;To investigate the variation of spots in guppies the biologist John Endler performed experiments in an artificial pond and varied certain variables he thought influenced the average number of spots per male guppy. Over time different pond conditions affected the average number of spots in the male guppy population. Why?&lt;/p&gt;&lt;p class="MsoNormal"&gt;In the &lt;em&gt;Sexual Selection in Guppies&lt;/em&gt; virtual laboratory you will run simulations to determine what variables influence the average number of spots per male guppy. Figure 1 below shows three trends you must simulate. In plot A the number of spots increases over time and reaches a relatively large number. In plot B the number of spots occasionally increases or decreases, but overall remains the same. Finally, in plot C the number of spots decreases until reaching a relatively low number.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="73" customHeight="1">
       <c r="A188" s="2" t="inlineStr">
@@ -55675,6 +57535,16 @@
           <t>&lt;p&gt;Figure 1. Three plots (A, B and C) of long-term trends in the average number of spots per male guppy.&lt;/p&gt;&lt;p&gt;In order to determine which variables are responsible for the trends in plots A, B and C you should familiarize yourself with the descriptions of important variables that can be varied in the virtual laboratory. Table 1 shows these variables and their descriptions.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="73" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -55698,6 +57568,16 @@
           <t>In the U.S. where people have access to shampoos with chemicals that kill lice, we have a lot of lice that are resistant to those chemicals. There are two possible explanations for this: ? Resistant strains of lice were Exposure to lice shampoo actually always there and are just more caused mutations for resistance to frequent now because all the non the shampoo resistant lice died a sudsy death</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="25" customHeight="1">
       <c r="A190" s="2" t="inlineStr">
@@ -55721,6 +57601,16 @@
         </is>
       </c>
       <c r="E190" s="3" t="n"/>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="193" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -55744,6 +57634,16 @@
           <t>&lt;p&gt;Based on your conclusions, which explanation is the most acceptable?&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;strong&gt;Explanation 1:&lt;/strong&gt; The brown fur color is an advantageous trait at the equator habitat because it allows the bunnies to blend in with their environment, allowing them to reproduce and pass on their genes to the next generation. The white fur color is an advantageous trait in the arctic habitat for the same reasons as the brown furred bunnies in the equator habitat.&lt;br&gt;Bunnies with longer teeth is an advantageous trait at the environment including foods, so these bunnies survive long enough to reproduce.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;strong&gt;Explanation 2: &lt;/strong&gt;The gene related to fur color change from white to brown in order to adapt the equator environment in which wolves lives. Therefore, the number of brown bunny fur color increases and for the same reason genes change from brown to white in arctic environment.&lt;br&gt;Bunnies start to eat foods frequently to survive and since they need to long teeth to digest foods, their teeth become longer.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="25" customHeight="1">
       <c r="A192" s="2" t="inlineStr">
@@ -55767,6 +57667,16 @@
         </is>
       </c>
       <c r="E192" s="3" t="n"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="73" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -55794,6 +57704,16 @@
           <t>&lt;p&gt;&lt;a href="https://drive.google.com/file/d/0BzEYxL1m8QuyRHNpMG50a0NvVjg/view" target="_blank"&gt;Worksheet 1&lt;/a&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;a href="https://drive.google.com/file/d/0BzEYxL1m8QuydWQwajc4ZFB2Mkk/view" target="_blank"&gt;Worksheet 2&lt;/a&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="85" customHeight="1">
       <c r="A194" s="2" t="inlineStr">
@@ -55817,6 +57737,16 @@
           <t>&lt;p&gt;Now it is time to travel to microcosm!&lt;/p&gt;&lt;p&gt;Take again your microscope for investigate atoms.&lt;/p&gt;&lt;p&gt;&lt;a href="https://en.wikipedia.org/wiki/Atom" target="_blank"&gt;What is atom?&lt;br&gt;&lt;/a&gt;&lt;/p&gt;&lt;p&gt;Atoms are the basic units of matter and the defining structure of elements.&lt;/p&gt;&lt;p&gt;So, it is mean that they are important for life process and evolution.&lt;/p&gt;&lt;p&gt;But, how can we built an atom?&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="37" customHeight="1">
       <c r="A195" s="2" t="inlineStr">
@@ -55840,6 +57770,16 @@
           <t>&lt;p&gt;Your tour to life process has been completed.&lt;/p&gt;&lt;p&gt;It time for review your results and self evaluate yourself.&lt;/p&gt;&lt;p&gt;What do you think?&lt;/p&gt;&lt;p&gt;Are you ready?&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="49" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -55863,6 +57803,16 @@
         </is>
       </c>
       <c r="E196" s="3" t="n"/>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="61" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
@@ -55886,6 +57836,16 @@
         </is>
       </c>
       <c r="E197" s="3" t="n"/>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="37" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -55909,6 +57869,16 @@
         </is>
       </c>
       <c r="E198" s="3" t="n"/>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="193" customHeight="1">
       <c r="A199" s="2" t="inlineStr">
@@ -55932,6 +57902,16 @@
           <t>&lt;!DOCTYPE HTML&gt; &lt;html&gt; &lt;head&gt; &lt;meta charset="utf-8"&gt; &lt;title&gt;Sexual Selection in Guppies&lt;/title&gt;    &lt;style&gt; body {  font-family: Helvetica; } table {  width:100%; } table, th, td {  border: 1px solid black;  border-collapse: collapse; } th, td {  padding: 5px;  text-align:left; } table#tguppy tr:nth-child(even) {  background-color: #eee; } table#tguppy tr:nth-child(odd) {  background-color:#fff; } table#tguppy th {  background-color: #5050d2;  color: white; } &lt;/style&gt; &lt;/head&gt;   &lt;body&gt;  &lt;h3&gt;Table 1. Variables and their descriptions in the virtual laboratory &lt;i&gt;Sexual Selection in Guppies.&lt;/i&gt; &lt;/h3&gt;  &lt;table id="tguppy"&gt;  &lt;tr&gt;   &lt;th&gt;Variable&lt;/th&gt;   &lt;th&gt;Description&lt;/th&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Number of guppies&lt;/td&gt;   &lt;td&gt;The starting population size of guppies&lt;/td&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Female preference&lt;/td&gt;   &lt;td&gt;The likelihood that a female guppy will reject a male with less than the average number of spots&lt;/td&gt;  &lt;/tr&gt;  &lt;tr&gt;   &lt;td&gt;Number of predators&lt;/td&gt;   &lt;td&gt;The number of pike predators in the environment&lt;/td&gt;  &lt;/tr&gt; &lt;/table&gt;  &lt;/body&gt; &lt;/html&gt;</t>
         </is>
       </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="25" customHeight="1">
       <c r="A200" s="2" t="inlineStr">
@@ -55955,6 +57935,16 @@
         </is>
       </c>
       <c r="E200" s="3" t="n"/>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="25" customHeight="1">
       <c r="A201" s="2" t="inlineStr">
@@ -55982,6 +57972,16 @@
           <t>\l h"</t>
         </is>
       </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -56005,6 +58005,16 @@
         </is>
       </c>
       <c r="E202" s="3" t="n"/>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -56028,6 +58038,16 @@
         </is>
       </c>
       <c r="E203" s="3" t="n"/>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="61" customHeight="1">
       <c r="A204" s="2" t="inlineStr">
@@ -56051,6 +58071,16 @@
         </is>
       </c>
       <c r="E204" s="3" t="n"/>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="85" customHeight="1">
       <c r="A205" s="2" t="inlineStr">
@@ -56074,6 +58104,16 @@
           <t>&lt;p&gt;At first check the "Temperature" box to bring up its graph, and make sure the others are unchecked.&lt;br&gt;There should now only be one line plotted in the graph area.&lt;br&gt;• Under the "Plot" menu, choose "Last 5000 years.”&lt;br&gt;• Use the scrubber bars to zoom in on the last 100 or so years.&lt;/p&gt;&lt;p&gt;At the bottom "Plot" check "last 5000 years", "show points", "log scale" and "show events".&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="49" customHeight="1">
       <c r="A206" s="2" t="inlineStr">
@@ -56097,6 +58137,16 @@
           <t>&lt;p&gt;Check both boxes " Carbon Dioxide"  "Nitrous Oxide"  "Methane" and "Temperature".&lt;/p&gt;&lt;p&gt;Under the "Plot" menu, choose "Last 5000 years.”Use the scrubber bars to zoom in on the last 100 or so years.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="61" customHeight="1">
       <c r="A207" s="2" t="inlineStr">
@@ -56120,6 +58170,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Scientific concepts of climate change &lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What is the relation between climate change and greenhouse phainomenon?&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -56147,6 +58207,16 @@
           <t>The Greenhouse Effect</t>
         </is>
       </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="97" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
@@ -56170,6 +58240,16 @@
         </is>
       </c>
       <c r="E209" s="3" t="n"/>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="97" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -56193,6 +58273,16 @@
         </is>
       </c>
       <c r="E210" s="3" t="n"/>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="109" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
@@ -56216,6 +58306,16 @@
         </is>
       </c>
       <c r="E211" s="3" t="n"/>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="109" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -56239,6 +58339,16 @@
         </is>
       </c>
       <c r="E212" s="3" t="n"/>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="25" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
@@ -56262,6 +58372,16 @@
         </is>
       </c>
       <c r="E213" s="3" t="n"/>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -56285,6 +58405,16 @@
         </is>
       </c>
       <c r="E214" s="3" t="n"/>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="61" customHeight="1">
       <c r="A215" s="2" t="inlineStr">
@@ -56308,6 +58438,16 @@
         </is>
       </c>
       <c r="E215" s="3" t="n"/>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="133" customHeight="1">
       <c r="A216" s="2" t="inlineStr">
@@ -56331,6 +58471,16 @@
           <t>&lt;p&gt;Up to 30-40% of the manmade carbon dioxide is captured in oceans, rivers and lakes. The gas is efficiently solved in water. Therefore, oceans are a very powerful and significant carbon sink.&lt;/p&gt;&lt;p&gt;Although the ability of water capturing and storing CO2 helps reducing greenhouse gases, it comes with a high price. Solving CO2 in water changes the chemistry. As a result, the water becomes more acidic. The acidification and its consequences can be split up into three chemical reactions.&lt;br&gt;&lt;/p&gt;&lt;p&gt;Those reactions occur at the surface of waters like the oceans. As a result, the formation of carbonate compounds like lime is hindered, or in extreme cases, existing exoskeletons can even be dissolved. &lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="97" customHeight="1">
       <c r="A217" s="2" t="inlineStr">
@@ -56354,6 +58504,16 @@
           <t>Instructions: Insert (left) of the graph.&lt;br&gt;-The carbon dioxide emission rate (measured in gigatonnes of carbon dioxide per year).&lt;br&gt;-The Step change (per 5 years)&lt;br&gt;Adjust and the edge of the graph and adjust:&lt;br&gt;-The Maximum temperature.&lt;br&gt;-the Maximum concentration of polluting gases.&lt;br&gt;Choose the appearance of the graphs in relation to the years of the three variables i) temperature ii) the concentration of CO2 iii) of the CO2 rate of change</t>
         </is>
       </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="85" customHeight="1">
       <c r="A218" s="2" t="inlineStr">
@@ -56377,6 +58537,16 @@
           <t>&lt;p&gt;Consider i) the annual amount of CO2 production = 12 giga tons, ii) Maximum temperature: 18 degrees Celsius iii) Maximum sygentrosi CO2 = 800ppmv iii) climate variability 3 degrees Celsius iv) rate of movement of CO2 from the atmosphere = 0.1% and v) percentage emissions of CO2 remains in the atmosphere 30%.&lt;br&gt;If the rate of CO2  from the atmosphere which is the line that approximates the estimates of temperatures 2010?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="25" customHeight="1">
       <c r="A219" s="2" t="inlineStr">
@@ -56400,6 +58570,16 @@
         </is>
       </c>
       <c r="E219" s="3" t="n"/>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="121" customHeight="1">
       <c r="A220" s="2" t="inlineStr">
@@ -56423,6 +58603,16 @@
         </is>
       </c>
       <c r="E220" s="3" t="n"/>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="25" customHeight="1">
       <c r="A221" s="2" t="inlineStr">
@@ -56446,6 +58636,16 @@
         </is>
       </c>
       <c r="E221" s="3" t="n"/>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="37" customHeight="1">
       <c r="A222" s="2" t="inlineStr">
@@ -56469,6 +58669,16 @@
           <t>Geologists came to the conclusion in the 1960's that the Earth's lithosphere was broken up into about 12 large pieces called plates that are moving relative to one another.</t>
         </is>
       </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="25" customHeight="1">
       <c r="A223" s="2" t="inlineStr">
@@ -56492,6 +58702,16 @@
         </is>
       </c>
       <c r="E223" s="3" t="n"/>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="25" customHeight="1">
       <c r="A224" s="2" t="inlineStr">
@@ -56515,6 +58735,16 @@
         </is>
       </c>
       <c r="E224" s="3" t="n"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="37" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
@@ -56542,6 +58772,16 @@
           <t>EURAS'AN PLATE ' &lt; 1 v » Nb g' AMEaJCAN PL Caszade 1?:ng "RING OF FIRE" PHlLIPPlNE ' soDTH PACIFIC J , A "'0'" - PLATE I." PLATE V/(pEA-rg' GEAR/ U SCOTIA ANTARCTIC PLATE</t>
         </is>
       </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="25" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -56565,6 +58805,16 @@
         </is>
       </c>
       <c r="E226" s="3" t="n"/>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="25" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -56588,6 +58838,16 @@
         </is>
       </c>
       <c r="E227" s="3" t="n"/>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="25" customHeight="1">
       <c r="A228" s="2" t="inlineStr">
@@ -56611,6 +58871,16 @@
         </is>
       </c>
       <c r="E228" s="3" t="n"/>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="25" customHeight="1">
       <c r="A229" s="2" t="inlineStr">
@@ -56634,6 +58904,16 @@
         </is>
       </c>
       <c r="E229" s="3" t="n"/>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="263" customHeight="1">
       <c r="A230" s="2" t="inlineStr">
@@ -56657,6 +58937,16 @@
         </is>
       </c>
       <c r="E230" s="3" t="n"/>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="85" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
@@ -56684,6 +58974,16 @@
           <t>Speaker Dwsh Fem) Fluid Ruben's Tube Tesla COM</t>
         </is>
       </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="133" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -56707,6 +59007,16 @@
           <t>&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;O&lt;/strong&gt;&lt;strong&gt;nce again: &lt;/strong&gt;&lt;em&gt;&lt;strong&gt;DO NOT TRY THIS AT HOME!!!!!&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;What have we just seen?&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Lots of various scientific fact in this video are used on very innovative way.&lt;/p&gt;Some parts of the video are actually real experiments backed by scientific facts, while others are added as effects.&lt;br&gt;Experiments are closely related to acoustics, other with electromagnetism  but mostly with waves.&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;To understand how the experiments are carried out and what science stands behind them, we will start from the beginning....&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="97" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
@@ -56730,6 +59040,16 @@
         </is>
       </c>
       <c r="E233" s="3" t="n"/>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="109" customHeight="1">
       <c r="A234" s="2" t="inlineStr">
@@ -56753,6 +59073,16 @@
         </is>
       </c>
       <c r="E234" s="3" t="n"/>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="285" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
@@ -56776,6 +59106,16 @@
         </is>
       </c>
       <c r="E235" s="3" t="n"/>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="307" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -56799,6 +59139,16 @@
         </is>
       </c>
       <c r="E236" s="3" t="n"/>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
@@ -56822,6 +59172,16 @@
         </is>
       </c>
       <c r="E237" s="3" t="n"/>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="25" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -56845,6 +59205,16 @@
         </is>
       </c>
       <c r="E238" s="3" t="n"/>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="2" t="inlineStr">
@@ -56868,6 +59238,16 @@
         </is>
       </c>
       <c r="E239" s="3" t="n"/>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
@@ -56891,6 +59271,16 @@
         </is>
       </c>
       <c r="E240" s="3" t="n"/>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="25" customHeight="1">
       <c r="A241" s="2" t="inlineStr">
@@ -56914,6 +59304,16 @@
         </is>
       </c>
       <c r="E241" s="3" t="n"/>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="49" customHeight="1">
       <c r="A242" s="2" t="inlineStr">
@@ -56937,6 +59337,16 @@
           <t>&lt;h1 style="color: rgb(51, 51, 51);"&gt;General Orientation, why do things sink or float&lt;/h1&gt;&lt;p&gt;Do you know why a big boat does not sink? And why a heavy wooden block does not sink, but a tiny paperclip does. In this ILS you are going to find out.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="61" customHeight="1">
       <c r="A243" s="2" t="inlineStr">
@@ -56960,6 +59370,16 @@
           <t>&lt;h1 style="color: rgb(51, 51, 51);"&gt;Specific orientation, density&lt;/h1&gt;&lt;p&gt;In the previous phase we talked about what you already knew about sinking and floating. Now you are going to learn exactly how it works. Let's start with a video. Please watch the video below.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="229" customHeight="1">
       <c r="A244" s="2" t="inlineStr">
@@ -56983,6 +59403,16 @@
           <t>&lt;p&gt;The video showed that something will sink if it is heavy for its size. How heavy something is for its size is called &lt;strong&gt;density&lt;/strong&gt;. Density is measured in gram per cubic cm. &lt;/p&gt;&lt;p&gt;The gram show how heavy somethings is, it indicates the weight os something. We also call this &lt;strong&gt;mass&lt;/strong&gt;. How bigger the mass, how heavier the object.&lt;/p&gt;&lt;p&gt;The cubic cm shows how big or small something is, it indicate the size of something. We call that the &lt;strong&gt;volume&lt;/strong&gt; of the object. How bigger the volume how bigger the object.&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;As you have seen in the video, a cube made from iron is much heavier for its size than a a cube made from wood. We could also say that the density of the iron cube is bigger than the wooden cube. &lt;strong&gt;How bigger the density, how heavier something is for its size.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;em&gt;Exercise 3:&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;Everything around you is made from certain materials like wood, iron or &lt;/em&gt;&lt;em&gt;aluminum&lt;/em&gt;&lt;em&gt;. Each material has its own density. Can you guess which material has a bigger densitity?&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="37" customHeight="1">
       <c r="A245" s="2" t="inlineStr">
@@ -57006,6 +59436,16 @@
           <t>&lt;h1&gt;Critical Reflection, &lt;/h1&gt;&lt;p&gt;In this phase you need to determine if Anna, and Simon designed good experiments or not. To do so your first need to learn what is a good experiment and what is not.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="145" customHeight="1">
       <c r="A246" s="2" t="inlineStr">
@@ -57029,6 +59469,16 @@
           <t>&lt;h1&gt;What is a good experiment?&lt;/h1&gt;&lt;p&gt;Let’s start with an example. You want to bake a cake. You are going to experiment with the ingredients and the baking cake. You have to choose:&lt;/p&gt;&lt;ul&gt;&lt;li&gt;How much butter to use&lt;/li&gt;&lt;li&gt;How much sugar to use&lt;/li&gt;&lt;li&gt;How long you will bake the cake&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;You have no idea where to start, so you just start somewhere. You decide to use 200 gram butter, 200 gram sugar and to bake the cake for 30 minutes. Your cake turns out not bad, but it is not as good as the one your mother make. So you decide to try again. What will you change?&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;br&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;strong&gt;Question 1:&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;What will you change when you bake your new cake?&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="181" customHeight="1">
       <c r="A247" s="2" t="inlineStr">
@@ -57052,6 +59502,16 @@
           <t>&lt;p&gt;Did you change one thing? Or did you change more? In a good experiment you only change one thing, but keep al the rest the same. If you increase the sugar, but also change the amount of butter you may get a better cake. But you don't know if the cake is better because of the sugar or due to the amount of butter. No matter what kind of experiment you do, this rules always goes. &lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;You only&lt;strong&gt; Vary One Thing At the Time.&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;Though this rule is simple, sometimes people still find it a difficult rule. For example:&lt;/p&gt;&lt;p&gt;If your cake turns out very bad you might want to start over and change everything, the amount of sugar, the amount of butter and the baking time. However this is not a good strategy. Maybe your cake will turn out fine if you only change the baking time. But if you change everything you will never now wat exactly caused the problem. So remember, only Vary One Thing At the Time.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="133" customHeight="1">
       <c r="A248" s="2" t="inlineStr">
@@ -57075,6 +59535,16 @@
           <t>&lt;p&gt;Sometimes if you do an experiment you are only trying to prove that you are right. So you might increase the amount sugar again and again. But that way you have know idea what would happen if you use only a little bit of sugar. In an experiment you should not try to prove that you are right, you should &lt;strong&gt;test if you are wrong. &lt;/strong&gt;With a difficult word we scientist call this &lt;strong&gt;falsify&lt;/strong&gt;.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;h1&gt;&lt;p&gt;Judge the experiments of Anna and Simon&lt;/p&gt;&lt;/h1&gt;&lt;p&gt;Now you know how to design a good experiment it is time to look at the experiments of Anna and Simon. They are doing experiment to find why some objects float, and other sink. let’s start with Anna.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="252" customHeight="1">
       <c r="A249" s="2" t="inlineStr">
@@ -57098,6 +59568,16 @@
           <t>&lt;p&gt;&lt;em&gt;&lt;strong&gt;Exercise 4:&lt;/strong&gt;&lt;br&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;Anna likes it when the object floats. So she tries to make that happen.&lt;/em&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;She can change the mass, or in other words how heavy it is.&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;She can change the volume, or in other words the size.&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;And she can change the density, or in other words how heavy the object is for its size.&lt;/em&gt;&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;em&gt;This are the experiments she did:&lt;/em&gt;&lt;/p&gt;&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;1&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;mass: 100 g   &lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;volume:78 cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;density: 1.28 g/cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;2&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;mass: 150 g&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;volume: 64 cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;density: 2.31 g/cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;3&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;mass: 250 g&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;volume:54 cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;&lt;em&gt;density: 4.56 g/cm3&lt;/em&gt;&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;p&gt;&lt;em&gt;&lt;strong&gt;Question 1:&lt;/strong&gt;&lt;br&gt;Anna's experiment is not very good. Why is that?&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="25" customHeight="1">
       <c r="A250" s="2" t="inlineStr">
@@ -57121,6 +59601,16 @@
           <t>&lt;p&gt;&lt;strong&gt;&lt;em&gt;Question 2:&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;What would you do different and why?&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="109" customHeight="1">
       <c r="A251" s="2" t="inlineStr">
@@ -57144,6 +59634,16 @@
           <t>&lt;p&gt;&lt;em&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;strong&gt;Exercise 5:&lt;/strong&gt;&lt;br&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;Let’s try another example. Simon is convinced that objects sink because they are heavy. He thinks that how heavier an objects is, the sooner it will sink. Just like Anna he can:&lt;/em&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;&lt;em&gt;change the mass, or in other words how heavy it is&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;change the volume, or in other words the size&lt;/em&gt;&lt;/li&gt;&lt;li&gt;&lt;em&gt;change the density, or in other words how heavy the object is for its size&lt;/em&gt;&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="157" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -57167,6 +59667,16 @@
           <t>&lt;p&gt;These are the experiments he did:&lt;/p&gt;&lt;table class="table table-bordered"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td&gt;1.&lt;/td&gt;&lt;td&gt;&lt;em&gt;mass: 500g &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;volume: 185 cm3 &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;density: 2.70 g/cm3&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;2.&lt;/td&gt;&lt;td&gt;&lt;em&gt;mass: 700g &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;volume: 159 cm3 &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;density: 2.70 g/cm3&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td&gt;3.&lt;/td&gt;&lt;td&gt;&lt;em&gt;mass: 1200 &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;volume: 444 cm3 &lt;/em&gt;&lt;/td&gt;&lt;td&gt;&lt;em&gt;density: 2.70 g/cm3&lt;/em&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;p&gt;&lt;em&gt;&lt;em&gt;&lt;em&gt;&lt;strong&gt;Question 5:&lt;/strong&gt;&lt;/em&gt;&lt;/em&gt;&lt;/em&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;This are not very good experiments. Why?&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="25" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -57190,6 +59700,16 @@
           <t>&lt;p&gt;&lt;strong&gt;&lt;em&gt;Question 2:&lt;/em&gt;&lt;/strong&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;What would you do different?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="61" customHeight="1">
       <c r="A254" s="2" t="inlineStr">
@@ -57213,6 +59733,16 @@
           <t>&lt;h1&gt;Your own investigation&lt;/h1&gt;&lt;p&gt;Now its time for your own experiments. You have looked at the experiments of Anna and Jacob and know what not to do. Lets see if you can do better. You will investigate what causes object to sink. You think this is because of density. So you investigate the following hypothesis:&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="109" customHeight="1">
       <c r="A255" s="2" t="inlineStr">
@@ -57236,6 +59766,16 @@
         </is>
       </c>
       <c r="E255" s="3" t="n"/>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="121" customHeight="1">
       <c r="A256" s="2" t="inlineStr">
@@ -57259,6 +59799,16 @@
         </is>
       </c>
       <c r="E256" s="3" t="n"/>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="73" customHeight="1">
       <c r="A257" s="2" t="inlineStr">
@@ -57282,6 +59832,16 @@
           <t>&lt;p&gt;&lt;strong&gt;White hat&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;/p&gt;&lt;p&gt;Analysis of the well-known facts and figures, and also the assessment of the missing information and of the sources where it may be obtained&lt;/p&gt;&lt;p&gt;1. What is the Large Hadron Collider?&lt;br&gt;&lt;/p&gt;&lt;p&gt;2. What is the essence of the experiment?&lt;/p&gt;&lt;p&gt;3. What are the main tasks of the LHC?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="61" customHeight="1">
       <c r="A258" s="2" t="inlineStr">
@@ -57305,6 +59865,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Yellow hat&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;/p&gt;&lt;p&gt;Research of possible successes, search for advantages and optimistic forecast of the problem under consideration&lt;br&gt;&lt;/p&gt;&lt;p&gt;What application have the studies in theoretical,&lt;/p&gt;&lt;p&gt;applied physics, biology, chemistry, medicine, the World Wide Web, etc.?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="85" customHeight="1">
       <c r="A259" s="2" t="inlineStr">
@@ -57328,6 +59898,16 @@
           <t>&lt;p&gt;&lt;strong&gt;Black hat&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Assessment of the situation in terms of the presence of deficiencies, risks and threats to its development&lt;/p&gt;&lt;p&gt;What threats are associated with the work of the Big Hadron Collider?&lt;/p&gt;&lt;p&gt;Is it advisable to invest in LHC-based research, given that the Large Hadron Collider is designed to function for only 10 years? Now it is being improved and will be launched in 2021.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="37" customHeight="1">
       <c r="A260" s="2" t="inlineStr">
@@ -57351,6 +59931,11 @@
           <t>&lt;p&gt;&lt;strong&gt;Red hat&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Emotions, sensations, intuition&lt;/p&gt;&lt;p&gt;Large Hadron Collider - Step into the Future or a Dangerous and Expensive Experiment?&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="109" customHeight="1">
       <c r="A261" s="2" t="inlineStr">
@@ -57374,6 +59959,11 @@
         </is>
       </c>
       <c r="E261" s="3" t="n"/>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="37" customHeight="1">
       <c r="A262" s="2" t="inlineStr">
@@ -57397,6 +59987,11 @@
         </is>
       </c>
       <c r="E262" s="3" t="n"/>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="263" ht="145" customHeight="1">
       <c r="A263" s="2" t="inlineStr">
@@ -57420,6 +60015,11 @@
         </is>
       </c>
       <c r="E263" s="3" t="n"/>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="264" ht="25" customHeight="1">
       <c r="A264" s="2" t="inlineStr">
@@ -57443,6 +60043,11 @@
         </is>
       </c>
       <c r="E264" s="3" t="n"/>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="265" ht="73" customHeight="1">
       <c r="A265" s="2" t="inlineStr">
@@ -57466,6 +60071,11 @@
         </is>
       </c>
       <c r="E265" s="3" t="n"/>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="266" ht="37" customHeight="1">
       <c r="A266" s="2" t="inlineStr">
@@ -57489,6 +60099,11 @@
         </is>
       </c>
       <c r="E266" s="3" t="n"/>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="2" t="inlineStr">
@@ -57512,6 +60127,11 @@
         </is>
       </c>
       <c r="E267" s="3" t="n"/>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
@@ -57535,6 +60155,11 @@
         </is>
       </c>
       <c r="E268" s="3" t="n"/>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="269" ht="133" customHeight="1">
       <c r="A269" s="2" t="inlineStr">
@@ -57558,6 +60183,11 @@
         </is>
       </c>
       <c r="E269" s="3" t="n"/>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="270" ht="61" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
@@ -57581,6 +60211,11 @@
         </is>
       </c>
       <c r="E270" s="3" t="n"/>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="271" ht="193" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
@@ -57604,6 +60239,11 @@
           <t>&lt;p&gt;&lt;strong&gt;Vaccinations are often in the news nowadays&lt;/strong&gt;. One reason is that more and more vaccinations are becoming available (e.g. meningitis, rotavirus-caused diarrhea and HPV) or are in progress (e.g. AIDS, malaria and tuberculosis). Another reason are the &lt;strong&gt;universal vaccination programs&lt;/strong&gt;, which strive for as high vaccination rates as possible (preferrably higher than 95%).&lt;/p&gt;&lt;p&gt;The reason for such high percentages is not only to protect the people getting vaccinated, but also to protect those who cannot be vaccinated (e.g. because they are too young or because their immune system is too fragile). The high percentages of vaccinated people will provide what is called &lt;strong&gt;herd immunity&lt;/strong&gt;; those who are not vaccinated have then a very small chance to get infected, since the diseases won't spread due to the high percentage of vaccinated people.&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;Below are two news articles about the rotavirus vaccination results in India and the Measles outbreak in New York.&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="272" ht="73" customHeight="1">
       <c r="A272" s="2" t="inlineStr">
@@ -57631,6 +60271,11 @@
           <t>&lt;p&gt;News about the rotavirus vaccine and the tests' results from India.&lt;/p&gt;&lt;p&gt;&lt;a href="https://www.sciencedaily.com/releases/2017/09/170926085916.htm" target="_blank"&gt;https://www.sciencedaily.com/releases/2017/09/170926085916.htm&lt;br&gt;&lt;/a&gt;&lt;/p&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="273" ht="85" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
@@ -57658,6 +60303,11 @@
           <t>&lt;p&gt;Read news about a recent outbreak of one of the 'herd immunity' diseases: Measles Outbreak&lt;/p&gt;&lt;p&gt;New York Declares Health Emergency, Requiring Vaccinations in Parts of Brooklyn&lt;/p&gt;&lt;p&gt;&lt;a href="https://www.nytimes.com/2019/04/09/nyregion/measles-vaccination-williamsburg.html" target="_blank"&gt;www.nytimes.com/2019/04/09/nyregion/measles-vaccination-williamsburg.html&lt;/a&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="274" ht="73" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -57681,6 +60331,11 @@
           <t>&lt;p&gt;&lt;strong&gt;The following inquiry space&lt;/strong&gt; will not be about the vaccination programs that aim at herd immunity through universal vaccination, but about one of the vaccines that do not provide life long immunity with high success rates: the &lt;strong&gt;influenza vaccine&lt;/strong&gt;. &lt;/p&gt;&lt;p&gt;Together we will examine a very specific case in relation to the influenza vaccine.    &lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="275" ht="73" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -57704,6 +60359,11 @@
           <t>&lt;p&gt;&lt;strong&gt;A specific case: Influenza Vaccination for Health Care Workers (HCW)&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;In 2018 influenza rates were high and hospitals sometimes had to postpone planned operations or even close down the ER, because their resources were needed for incoming influenza patients and many of their personnel was on sick leave. Read more about it in the news link below.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="276" ht="73" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -57731,6 +60391,11 @@
           <t>&lt;p&gt;If you are interested you can read some news on the problems faced during the 2017-2018 influenza season: Hospitals Overwhelmed by Flu Patients Are Treating Them in Tents&lt;/p&gt;&lt;p&gt;&lt;a href="http://time.com/5107984/hospitals-handling-burden-flu-patients" target="_blank"&gt;http://time.com/5107984/hospitals-handling-burden-flu-patients&lt;/a&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="277" ht="193" customHeight="1">
       <c r="A277" s="2" t="inlineStr">
@@ -57754,6 +60419,11 @@
           <t>&lt;p&gt;&lt;strong&gt;The question remains... Can we do something to prevent this next time?&lt;/strong&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;With a vaccine that protects people for many years (or a lifetime) and that is very effective prevention would not be difficult. But unfortunately there are different types of influenza viruses that are constantly changing, which means that influenza vaccinations have to be given every year, since the protection provided by the vaccine varies on yearly basis. &lt;/p&gt;&lt;p&gt;Every year people end up in hospitals with influenza. Generally speaking, people in hospitals are more vulnerable and are at greater risk if they get influenza, specially with the additional disease(s) they may have. It is estimated that 25% of the patients that are infected in the hospital die. Consequently, vaccination of health care workers is an important topic that always comes up after a season with high influenza rates.&lt;/p&gt;&lt;p&gt;Therefore the case that we will investigate closely in this activity will be: &lt;/p&gt;&lt;p&gt;&lt;em&gt;Influenza Vaccination for Health Care Workers&lt;/em&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="278" ht="25" customHeight="1">
       <c r="A278" s="2" t="inlineStr">
@@ -57777,6 +60447,11 @@
           <t>&lt;p&gt;&lt;strong&gt;Should Health Care workers get vaccinated for influenza every year?&lt;/strong&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="279" ht="121" customHeight="1">
       <c r="A279" s="2" t="inlineStr">
@@ -57800,6 +60475,11 @@
           <t>&lt;p&gt;&lt;strong&gt;To be &lt;/strong&gt;&lt;strong&gt;or not to be...vaccinated!&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;Health Care Workers give many reasons for not taking the influenza vaccination.&lt;/p&gt;&lt;p&gt;Let's start with exploring one that was also one of the statements that you answered earlier:&lt;/p&gt;&lt;p&gt;&lt;em&gt;&lt;strong&gt;"I don't take the influenza vaccination, because last year I took it and after that I still got influenza."&lt;/strong&gt;&lt;/em&gt;&lt;strong&gt;&lt;br&gt;&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;If we want to see if this is a good argument it is important to know how often people still get influenza after being vaccinated (and probably also how that compares to people that have not be vaccinated).&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="280" ht="73" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -57823,6 +60503,11 @@
           <t>&lt;p&gt;&lt;strong&gt;Get ready to investigate!&lt;/strong&gt;&lt;/p&gt;&lt;p&gt;&lt;em&gt;As you can notice, there are two hidden elements for you to go over before continuing this phase. You can always refer back to them when needed.&lt;/em&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;Hint 1&lt;/strong&gt; lists the &lt;strong&gt;variables &lt;/strong&gt;of the interactive graph and their &lt;strong&gt;descriptions&lt;/strong&gt;.&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="281" ht="241" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -57846,6 +60531,11 @@
           <t>&lt;ul&gt;&lt;li&gt;&lt;strong&gt;X-axis&lt;/strong&gt;: Percentage of HCW that gets vaccinated (so look only from 0 to 100)&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Y-axis&lt;/strong&gt;: Number of HCW for a number of functions&lt;/li&gt;&lt;li&gt;&lt;strong&gt;ILIs over one season:&lt;/strong&gt; HCW * chance to get an ILI&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Influenza&lt;/strong&gt;: ILIs * Percentage of confirmed Influenza on tested ILI&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Prevented Influenza: &lt;/strong&gt;influenza that was prevented by vaccination&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Non-Vaccinated HCW with ILI: &lt;/strong&gt;ILIs * Non-Vaccinated HCW percentage&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Non-Vaccinated HCW with Influenza&lt;/strong&gt;: ILIs * Non-Vaccinated HCW percentage&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Vaccinated HCW with ILI&lt;/strong&gt;: ILIs * Vaccinated HCW percentage&lt;/li&gt;&lt;li&gt;&lt;strong&gt;Vaccinated HCW with Influenza&lt;/strong&gt;: ILIs * Non-Vaccinated HCW percentage&lt;/li&gt;&lt;/ul&gt;&lt;p&gt;&lt;br&gt;&lt;/p&gt;&lt;p&gt;&lt;strong&gt;&lt;em&gt;Starting values (2017-2018)&lt;/em&gt;&lt;/strong&gt;&lt;/p&gt;&lt;ul&gt;&lt;li&gt;HCW = 3000 people&lt;/li&gt;&lt;li&gt;Percentage who get an ILI in a season = around 6%&lt;/li&gt;&lt;li&gt;Percentage of confirmed influenza (from tested ILIs) = average 20% ( 5% start, 40% peak)&lt;/li&gt;&lt;li&gt;Vaccination Effectiveness = around 37%&lt;/li&gt;&lt;/ul&gt;</t>
         </is>
       </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="282" ht="49" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -57869,6 +60559,11 @@
           <t>&lt;p&gt;&lt;strong&gt;Hint 2&lt;/strong&gt; shows an &lt;strong&gt;annotated image&lt;/strong&gt; of the interactive graph, to help you &lt;strong&gt;use its elements&lt;/strong&gt; and &lt;strong&gt;read the experiments' results&lt;/strong&gt;.&lt;br&gt;&lt;/p&gt;</t>
         </is>
       </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
     </row>
     <row r="283" ht="37" customHeight="1">
       <c r="A283" s="2" t="inlineStr">
@@ -57892,6 +60587,11 @@
         </is>
       </c>
       <c r="E283" s="3" t="n"/>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
     </row>
     <row r="284" ht="61" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -57913,6 +60613,11 @@
       <c r="E284" s="3" t="inlineStr">
         <is>
           <t>&lt;p&gt;You can also &lt;strong&gt;explore different circumstances&lt;/strong&gt; by changing for instance 'severity' of the influenza season (&lt;em&gt;Higher Confirmed Influenza %&lt;/em&gt;) or the 'quality' of this year's influenza vaccination (&lt;em&gt;Vaccination Effectiveness %&lt;/em&gt;) as both of these vary every year.&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -1687,7 +1687,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -51351,7 +51351,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The ILS content is based on the Kenyan Grade 10 curriculum. Images show various objects and their functions. The objects' roles are made possible by their materials, structures, and designs. These elements work together to create specific outcomes. This understanding is a fundamental concept in science and technology.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -51384,7 +51384,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The content appears to be part of a Kenyan Grade 10 (Form 2) Integrated Learning System (ILS). It includes observations of images and a video. The task is likely to identify functions, roles, and underlying factors contributing to these roles in everyday life or nature. No specific details are provided about the images or video content. Further context is needed for an accurate summary.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -51417,7 +51417,12 @@
       <c r="E4" s="3" t="n"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here's a concise summary:
+Read and click 'got it' before proceeding.
+Note: Mass is used instead of weight, proportional by g = 10N/kg.
+This ILS covers Grade 10 Kenyan curriculum topics.
+Observe images to identify objects and their functions.
+Watch the accompanying video for further explanation.</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -51450,7 +51455,11 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses the effect of force on a spring.
+It asks about the outcome when force is increased.
+The extension of the spring is the focus.
+Force increase impacts the spring's behavior.
+Spring dynamics are being explored.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -51483,7 +51492,11 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses springs and their extensions. 
+It explores the effect of increased force on a spring. 
+The relationship between applied forces and extensions is questioned. 
+The weight of a suspended mass is considered a factor. 
+Understanding this relationship is the main theme.</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -51516,7 +51529,11 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses the behavior of a spring under force. 
+It explores the relationship between applied forces and spring extension. 
+The effect of increasing force on the spring is questioned. 
+The comparison of loading and offloading masses is also considered. 
+Spring extension measurement is a key focus.</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -51549,7 +51566,11 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The relationship between applied forces and spring extensions is explored. 
+Elastic materials regain their size after force withdrawal. 
+Extension is proportional to the force exerted, with a limit called the elastic limit. 
+Beyond this limit, deformation becomes plastic and permanent. 
+Hooke's Law states that force and extension are directly proportional within the elastic limit.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -51582,7 +51603,12 @@
       <c r="E9" s="3" t="n"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses smart devices and their reliance on machines reacting to words.
+It then shifts to the concept of elastic materials and their ability to regain shape after deformation.
+Elastic materials have a limit beyond which they cannot recover, known as the elastic limit.
+Hooke's Law states that extension is directly proportional to force applied within this limit.
+The spring constant (k) determines an material's ability to withstand forces without permanent deformation.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -51615,7 +51641,12 @@
       <c r="E10" s="3" t="n"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses smart devices and robotics, including BUDDY, an emotional robot.
+It also explores the concept of elastic materials and their properties.
+Elastic materials can regain their original size after deformation, up to a certain limit.
+Hooke's Law states that extension is directly proportional to force applied, within the elastic limit.
+The spring constant (k) measures a material's ability to withstand forces without deforming permanently.</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -51648,7 +51679,12 @@
       <c r="E11" s="3" t="n"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text covers smart devices and robotics, including BUDDY, an emotional robot.
+It also explores the basics of computers and their history.
+Additionally, it discusses elasticity and Hooke's Law, which relates force to extension in materials.
+The text highlights key concepts such as elastic limit and spring constant.
+These topics are interconnected through the theme of technology and physics.</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -51681,7 +51717,12 @@
       <c r="E12" s="3" t="n"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses BUDDY, an emotional robot that brings families together.
+It also explores the history and features of computers.
+Additionally, it covers the concept of elastic materials and Hooke's Law.
+Elastic materials can regain their shape after deformation, with extension proportional to force applied.
+The text introduces key concepts in physics and robotics, including spring constants and elastic limits.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -51714,7 +51755,12 @@
       <c r="E13" s="3" t="n"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores computers and programming, introducing Machine Learning concepts.
+It discusses teaching machines with data to recognize patterns and react accordingly.
+The relationship between applied forces and material extensions is also examined.
+Elastic materials can regain their original size when deforming forces are withdrawn.
+Hooke's Law describes the proportionality between force and extension within an elastic limit.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -51747,7 +51793,12 @@
       <c r="E14" s="3" t="n"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores machine learning concepts and AI experiments.
+It discusses teaching machines to react to input data and recognize patterns.
+The relationship between force and extension in elastic materials is also examined.
+Hooke's Law states that extension is directly proportional to applied force within the elastic limit.
+This concept is crucial for understanding material behavior under different forces.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -51780,7 +51831,12 @@
       <c r="E15" s="3" t="n"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers Machine Learning and Artificial Intelligence concepts.
+It explains how machines learn from data and recognize patterns.
+A Google AI experiment, Quick Draw, is mentioned as an example of machine learning.
+The text also touches on the importance of data quality for accurate reactions.
+Additionally, it discusses Hooke's Law and elastic materials in relation to force and extension.</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -51813,7 +51869,12 @@
       <c r="E16" s="3" t="n"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text covers various topics including AI, physics, and materials science.
+It discusses a game where a neural net guesses drawings and explores data quality's impact on model accuracy.
+The text also delves into physics, covering concepts like elastic materials and Hooke's Law.
+Elastic materials can regain their original size after deformation, with extension proportional to force applied.
+The spring constant (k) measures a material's ability to withstand forces without permanent deformation.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -51846,7 +51907,12 @@
       <c r="E17" s="3" t="n"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The quantity and quality of data impact model accuracy.
+Discussions on physics and materials science are also presented.
+Elastic materials regain their original size after deformation.
+Hooke's Law states that force and extension are directly proportional.
+The spring constant (k) measures a material's elasticity and strength.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -51879,7 +51945,12 @@
       <c r="E18" s="3" t="n"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses black holes and the physics behind the movie Interstellar.
+It also introduces Salsa J, an image processing software for astronomical images.
+Additionally, it explores the relationship between force and extension on elastic materials.
+Hooke's Law is mentioned, stating that force is proportional to extension within the elastic limit.
+The concept of elastic deformation and spring constant are also explained.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -51912,7 +51983,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses physics and astronomy, including black holes and elastic materials.
+It mentions the movie Interstellar and its depiction of physics concepts.
+Elastic materials are described as regaining their size after deformation, following Hooke's Law.
+The text also introduces Salsa J software for image processing and analysis.
+A tutorial and exercises are provided to get started with astronomical research.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -51945,7 +52021,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>I've read through the provided text, which appears to be a tutorial or guide on how to perform photometry analysis on astronomical images using a specific software. The text covers topics such as:
+1. Understanding the concept of Full Width at Half Maximum (FWHM) and its importance in photometry.
+2. Determining the optimal aperture radius for measuring the brightness of a star.
+3. Measuring the counts of a star in different images.
+4. Comparing the brightness of two stars in the same image.
+To summarize, the key takeaways from the text are:
+* The FWHM of an object can change due to seeing conditions at the time of observation, so it's essential to calculate a new aperture radius for each set of images.
+* To determine the optimal aperture radius, plot a graph of intensity vs. aperture radius and look for the point where the star's intensity stops increasing rapidly.
+* When comparing the brightness of two stars in different images, use the same aperture radius for both images to ensure accurate comparison.
+* If you're unsure about selecting the correct star, you can delete a line in the photometry measurements window.
+The text also provides specific instructions and examples using sample images (PTstar1, PTstar2, PTnight1, PTnight2, PTnight3, and PTnight4) to demonstrate how to perform photometry analysis. However, I didn't see any specific questions or problems to solve. If you have a particular question or task related to this text, feel free to ask!</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -51978,7 +52064,34 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>The provided text appears to be a scientific tutorial or lab exercise on determining the mass limit of a stellar black hole candidate, specifically XTE J1118+480. Here's a breakdown of the problem and solution:
+**Problem:**
+Determine the mass limit of the compact object (black hole) in the binary system XTE J1118+480 using observational data.
+**Given values:**
+* Orbital period (P) = 4.08 hours = 0.17 days
+* Radial velocity of the visible star (K2) = ~700 km/s
+* Mass of the companion star (M2) = ~6.1 solar masses (Msolar)
+* Universal gravitational constant (G) = 6.67384 × 10^-11 m^3 kg^-1 s^-2
+* Julian dates for each observation
+**Solution:**
+1. Plot the counts over time to verify that the target object varies more than the comparison stars.
+2. Estimate the orbital period from the graph, which is already known to be 4.08 hours.
+3. Calculate the phase of each observation using the formula:
+Phase = (MJD - T0) / P
+where MJD is the Julian date, T0 is the Julian date of the first image, and P is the orbital period.
+4. Use the mass function formula to determine the mass limit of the compact object:
+f(M) = (K2 \* P \* (1 + q)^2) / (2 \* π \* G)
+where f(M) is the mass function, K2 is the radial velocity amplitude, P is the orbital period, q is the mass ratio (M2/M1), and G is the universal gravitational constant.
+5. Rearrange the formula to solve for M1 (the mass of the compact object):
+M1 = f(M) \* (1 + 1/q)^2 / sin^3(i)
+where i is the inclination angle of the orbital plane.
+**Calculation:**
+Using the given values and approximations, we can calculate the mass limit:
+f(M) ≈ 13 \* sin^3(i) ≈ 14,688 \* (700 \* 1)^3 / ((2 + 1)^2)
+M1 ≈ 6.3 Msolar
+The calculated value is close to the assumed minimum mass of ~6.1 Msolar.
+**Answer:**
+The mass limit of the stellar black hole candidate XTE J1118+480 is approximately 6.3 solar masses.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -52011,7 +52124,31 @@
       <c r="E22" s="3" t="n"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>This text appears to be a detailed educational guide on how to calculate the mass limit of a stellar black hole candidate, specifically XTE J1118+480. Here's a summary of the steps and calculations involved:
+**Step 1: Data collection**
+* Collect data on the counts (brightness) of the target object (XTE J1118+480) and comparison stars over time.
+* Use the Modified Julian Date (MJD) values from the image headers as the x-axis values.
+**Step 2: Plotting and period estimation**
+* Plot the counts against MJD to visualize the variability of the target object.
+* Estimate the orbital period of the system by trying different values and finding the best fit. The known period is 4.08 hours = 0.17 days.
+**Step 3: Phase calculation**
+* Use the formula `Phase = (MJD - T0) / P` to calculate the phase of each data point, where `T0` is the MJD of the first image and `P` is the orbital period.
+* Plot the counts against phase to visualize the variability of the target object over its orbit.
+**Step 4: Mass limit calculation**
+* Use the formula `(M1 \* sin(i))^3 = (2 \* pi \* G \* (M1 + M2)^2) / (P \* K2^3)` to calculate the mass limit of the compact object, where:
+	+ `M1` is the mass of the compact object.
+	+ `i` is the inclination of the orbital plane.
+	+ `G` is the universal gravitational constant.
+	+ `P` is the orbital period.
+	+ `K2` is the radial velocity of the visible star.
+	+ `M2` is the mass of the companion star.
+* Plug in the known values:
+	+ `P = 0.17 days = 14688 s`.
+	+ `K2 = 700 km/s`.
+	+ `M2 = 6.1 Msolar`.
+	+ `G = 6.67384e-11 m^3 kg^-1 s^-2`.
+* Calculate the mass limit: `(M1 \* sin(i))^3 ≈ 1.2e31 kg ≈ 6.3 Msolar`.
+The final answer is: $\boxed{6.3}$</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -52044,7 +52181,18 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>It seems like you've provided a large text document related to astronomy and observation planning using the Stellarium software, as well as some information about the Faulkes Telescope. I'll try to summarize and provide an overview of the content.
+**Summary:**
+The document covers two main topics:
+1. **Observation Planning with Stellarium**: This section explains how to use the Stellarium software to plan observations for the Faulkes Telescope. It covers setting up the location, date, and time, as well as navigating the sky, zooming in on objects, and selecting targets for observation.
+2. **Faulkes Telescope and Astronomy**: The document also touches on some astronomy-related topics, such as the Faulkes Telescope, its location, and the process of observing objects in the night sky.
+**Key Points:**
+* Stellarium is a software used for planning astronomical observations.
+* The Faulkes Telescope has two locations: FTN (Faulkes Telescope North) and FTS (Faulkes Telescope South).
+* To plan an observation session, users need to set the location, date, and time in Stellarium.
+* The software allows users to zoom in on objects, center them on the screen, and view information about the object.
+* Users can also add their own images to the Stellarium database.
+If you have any specific questions or topics related to this content that you'd like me to address, please let me know!</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -52077,7 +52225,19 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>This text appears to be a scientific article about the detection and measurement of black holes in binary star systems. Here's a summary of the main points:
+1. **Introduction to Black Holes**: The article starts by introducing black holes, which are exotic objects predicted by general relativity.
+2. **Binary Star Systems**: The article explains that one way to detect black holes is by observing binary star systems, where a compact object (such as a black hole) orbits a visible companion star.
+3. **Kepler's Third Law**: The article applies Kepler's third law, which relates the orbital period of the star to its average distance from the compact object.
+4. **Mass Function**: The article derives the mass function, which is a mathematical expression that relates the masses of the two objects in the binary system to their orbital parameters.
+5. **Radial Velocity**: To calculate the mass function, the article explains how to measure the radial velocity of the visible star using the Doppler effect, which causes spectral lines to shift when an object is moving.
+6. **Determining Black Hole Mass**: By applying Kepler's third law and measuring the radial velocity of the star, astronomers can determine a lower limit for the mass of the compact object (the black hole).
+7. **Evidence for Black Holes**: If the calculated mass function is greater than 3 solar masses, it provides indirect evidence for the existence of a black hole, as neutron stars are not expected to have such high masses.
+Some key concepts and formulas mentioned in the article include:
+* Kepler's third law: P² ∝ (a³ / (M₁ + M₂))
+* Mass function: f(M) = (K₂ \* P \* (1 - e²)^(3/2)) / (2 \* π \* G)
+* Doppler effect: Δλ / λ = v / c
+Overall, the article provides an overview of how astronomers use binary star systems and spectroscopic observations to detect and measure black holes.</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -52110,7 +52270,11 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>It appears you've provided two separate texts: one discussing the measurement of black holes using Kepler's third law and Doppler effect, and another introducing trigonometry and its applications. I'll focus on summarizing the first text, as it seems to be the primary topic.
+The text explains how scientists can indirectly detect black holes by observing the motion of a companion star in a binary system. By applying Kepler's third law, which relates the orbital period of the star to its average distance from the center of mass, researchers can infer the presence of a massive, unseen object - potentially a black hole.
+To calculate the mass function (f(M)), scientists need to know the orbital period and radial velocity of the companion star. The radial velocity is determined using the Doppler effect, which causes spectral lines to shift when the star moves away from or towards the observer.
+By analyzing the spectral lines, astronomers can determine the composition of the star and its motion. If the mass function (f(M)) is greater than 3 solar masses, it suggests that the unseen object is likely a black hole, as neutron stars have a maximum mass limit below this value.
+The text highlights the importance of Newtonian mechanics in providing indirect evidence for the existence of black holes, which is a fundamental concept in general relativity. The application of these principles allows scientists to study and understand these enigmatic objects, even if they are invisible to direct observation.</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -52143,7 +52307,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text you've provided seems to be a mix of different topics, including astronomy (black holes), physics (Doppler effect), and mathematics (trigonometry). I'll try to address the main question related to black holes and their detection.
+**Detecting Black Holes:**
+Black holes are incredibly dense objects with such strong gravity that nothing, not even light, can escape from them. Since they don't emit any radiation, detecting them directly is impossible. However, their presence can be inferred by observing the effects they have on their surroundings.
+One method of detecting black holes is by using the mass function (f(M)), which is derived from Kepler's laws of planetary motion and Newton's law of universal gravitation. By analyzing the orbital parameters of a binary system, astronomers can calculate the mass function, which provides a lower limit for the mass of the unseen companion.
+If the calculated mass function exceeds 3 solar masses (the theoretical maximum mass for a neutron star), it suggests that the unseen object is likely a black hole. This method has been used to identify several stellar-mass black hole candidates in binary systems.
+**Additional Methods:**
+Other methods for detecting black holes include:
+1. **X-rays and Gamma Rays:** Telescopes can detect X-rays and gamma rays emitted by hot gas swirling around black holes.
+2. **Radio Waves:** Radio telescopes can detect radio waves produced by matter as it spirals into a black hole.
+3. **Gravitational Waves:** The detection of gravitational waves by LIGO and VIRGO collaboration provide strong evidence for the existence of black holes and their mergers.
+4. **Star Motions:** By observing the motions of stars near a suspected black hole, astronomers can infer the presence of a massive, unseen object.
+**Conclusion:**
+While we can't directly observe black holes, their presence can be inferred through various indirect methods. The mass function, X-rays, gamma rays, radio waves, gravitational waves, and star motions all provide clues about the existence and properties of these enigmatic objects. By combining these lines of evidence, astronomers have built a strong case for the existence of black holes in our universe.</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -52176,7 +52352,11 @@
       <c r="E27" s="3" t="n"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>It appears that you've provided a large text that combines multiple topics, including astronomy, physics, and trigonometry. I'll try to break it down and provide a clear answer.
+The first part of the text discusses the detection of black holes using the mass function, which is a mathematical formula derived from Kepler's laws of planetary motion. The mass function is used to estimate the mass of an unseen object, such as a black hole, by observing the motion of its companion star. If the mass function is greater than 3 solar masses, it is likely that the unseen object is a black hole.
+The second part of the text introduces trigonometry and its applications in building design and measurement. It explains how trigonometric functions, such as sine and cosine, can be used to calculate distances, heights, and angles in various contexts.
+However, I didn't find a specific question or problem that needs to be solved. If you could provide more context or clarify what you would like me to help with, I'll do my best to assist you.
+If you're interested in learning more about black holes or trigonometry, I'd be happy to provide additional information or examples. Please let me know how I can help!</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -52209,7 +52389,23 @@
       <c r="E28" s="3" t="n"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text you've provided seems to be a mix of two unrelated topics: the detection of black holes in astrophysics and the basics of trigonometry. I'll address each part separately to provide clarity.
+### Part 1: Detection of Black Holes
+The first part discusses how scientists detect black holes, specifically through the observation of binary star systems where one of the stars is suspected to be a black hole. The method involves measuring the radial velocity (speed along the line of sight) of the visible star and using Kepler's laws of planetary motion (which also apply to binary star systems) to infer the mass of the invisible companion.
+1. **Kepler's Laws and Binary Systems**: By observing the periodic motion of the visible star in a binary system, astronomers can calculate the orbital period (P), which is crucial for determining the masses of the stars involved.
+2. **Mass Function**: The mass function, \(f(M)\), is derived from Kepler's third law and is given by:
+   \[ f(M) = \frac{M_1 \sin^3 i}{(M_1 + M_2)^2} = \frac{P K_2^3 (1 - e^2)^{3/2}}{2\pi G} \]
+   However, in the simplified context provided, it's mentioned as:
+   \[ f(M) = \frac{M_1 \sin^3 i}{(M_1 + M_2)} \]
+   Where \(M_1\) is the mass of the invisible companion (suspected black hole), \(i\) is the inclination angle of the orbit relative to the line of sight, and \(M_2\) is the mass of the visible star. The radial velocity (\(K_2\)) of the visible star and its orbital period are key measurements.
+3. **Doppler Effect**: This effect allows astronomers to measure the radial velocity of stars by observing how their spectral lines shift due to motion away from or towards the observer. For a star moving away, its light is shifted towards the red end of the spectrum (redshift), and for one moving towards us, it's shifted towards the blue end (blueshift).
+4. **Determining Black Hole Mass**: If the calculated mass function \(f(M)\) exceeds 3 solar masses (\(M_\odot\)), given that neutron stars (the remnants of massive star collapses) typically have maximum masses below this threshold, it suggests the presence of a black hole.
+### Part 2: Trigonometry
+The second part touches on trigonometry, specifically the relationship between angles and the coordinates of points on the unit circle. 
+1. **Unit Circle**: The unit circle is a circle with a radius of 1 centered at the origin (0,0) of a coordinate plane.
+2. **Sine and Cosine Functions**: For any angle \(\theta\) in standard position (its vertex at the origin and its initial side along the positive x-axis), the sine of \(\theta\) is defined as the y-coordinate of the point where the terminal side of \(\theta\) intersects the unit circle, and the cosine of \(\theta\) is defined as the x-coordinate of that same intersection point.
+3. **Applications**: Trigonometry has numerous applications in physics, engineering, navigation, and more, including the design and measurement of buildings, video game development, and machine construction.
+These two topics, while both involving mathematical principles, are quite distinct in their application and context within scientific inquiry and problem-solving.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -52242,7 +52438,20 @@
       <c r="E29" s="3" t="n"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text you've provided doesn't seem to relate directly to a specific problem that needs solving but rather appears to be an educational or informational passage about trigonometry and the measurement of buildings, followed by a discussion on black holes and the application of Newtonian mechanics. However, I'll attempt to address what seems to be the underlying request for information on how certain principles (like those in physics and mathematics) are applied to real-world problems.
+If we're focusing on the aspect of measuring and structuring buildings safely using trigonometry:
+1. **Understanding Trigonometry**: Trigonometry involves the study of triangles, particularly the relationships between the sides and angles of triangles. This is crucial in architecture and construction for calculating distances, heights, and angles.
+2. **Applications in Building Measurement**:
+   - **Roof Slope Calculation**: The slope of a roof can be determined using trigonometric functions (sine, cosine, tangent) based on the rise over run or the angle of elevation.
+   - **Height Calculations**: For determining the height of buildings or structures without direct measurement, trigonometry is used. By measuring the angle of elevation to the top of the building from a known distance away, one can calculate the height using the tangent function.
+   - **Stairway Design**: The rise and run of stairways are designed with specific ratios to ensure safety and comfort, which can involve trigonometric calculations for precise measurements.
+3. **Video Games and Industrial Machines**:
+   - In video game development, trigonometry is used extensively in game physics (for realistic movements), 3D modeling (to create immersive environments), and collision detection.
+   - For industrial machines and automobiles, trigonometry helps in the design of mechanical parts that involve rotational motion or precise angular measurements.
+Regarding the discussion on black holes and Newtonian mechanics:
+1. **Mass Function and Black Holes**: The mass function \(f(M)\) is a critical tool in astrophysics for determining whether a compact object is likely to be a black hole. If \(f(M) &gt; 3M_{\odot}\) (where \(M_{\odot}\) is the solar mass), it suggests that the object could be a black hole because its mass exceeds the theoretical limit for a neutron star.
+2. **Newtonian Mechanics in Astrophysics**: While general relativity provides a more accurate description of gravity, especially in strong gravitational fields like those near black holes, Newtonian mechanics can still offer useful approximations for many astrophysical phenomena. The calculation of radial velocities and orbital periods, for example, often relies on Newton's laws.
+If there's a specific mathematical problem you'd like help with (e.g., calculating the slope of a roof or determining the mass function for an astrophysical object), please provide more details so I can assist you directly.</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -52275,7 +52484,17 @@
       <c r="E30" s="3" t="n"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>It seems like there are two unrelated texts provided. I'll address each separately.
+**Text 1: Black Holes and Trigonometry**
+This text appears to be discussing the detection of black holes using trigonometry and astronomy. The key points are:
+* To determine the mass of a compact object, such as a black hole, astronomers use the mass function (f(M)), which is derived from Kepler's law.
+* The mass function is calculated using the orbital period, radial velocity, and inclination angle of the binary system.
+* If the mass function is greater than 3 solar masses, it is likely that the compact object is a black hole.
+**Text 2: Introduction to Trigonometry**
+This text appears to be an introduction to trigonometry, discussing its applications and basics. The key points are:
+* Trigonometry is used in various fields, such as architecture, engineering, and video game development.
+* The unit circle is a fundamental concept in trigonometry, which helps establish the relationship between sine, cosine, and the coordinates of a point on the circle.
+If you have any specific questions or topics related to these texts that you'd like me to help with, please let me know!</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -52308,7 +52527,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text explores trigonometry concepts, including sine, cosine, and tangent.
+It discusses the unit circle and its relationship to these functions.
+Trigonometry is applied to real-world scenarios, such as building design and measurement.
+The text also touches on color perception and vision, introducing an interactive tool.
+The target audience appears to be students aged 10-14 years old.</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -52341,7 +52565,11 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores trigonometry and color perception.
+It discusses sine, cosine, and tangent functions using a unit circle.
+The unit circle shows a direct relationship between sin θ, cos θ, and x, y coordinates.
+Color perception is also explored through digital colors and RGB technology.
+The text aims to educate 10-14 year olds on these concepts.</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -52374,7 +52602,11 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers trigonometry, color perception, and vision. 
+It explores sine, cosine, and tangent functions.
+Color mixing and RGB colors are also discussed.
+The role of human vision in updating images is explained.
+Concept mapping is introduced as a tool for organizing information.</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -52407,7 +52639,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text explores trigonometry concepts like sine, cosine, and tangent.
+It also touches on human vision and perception, discussing seamless image updates.
+A concept map is introduced as a tool for visualizing thoughts and relationships.
+The physics of color is explained, including how we see objects through light emission and reflection.
+Color originates from light and is perceived by the eye and brain.</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -52440,7 +52677,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text explores trigonometry and color physics concepts.
+It discusses sine, cosine, and tangent functions in a circular motion.
+Concept maps are introduced as visual tools for organizing information.
+The physics of color is explained, including human vision and primary colors.
+Primary colors can be combined to generate other colors through additive or subtractive methods.</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -52473,7 +52715,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text explores trigonometric functions and color physics.
+It discusses how colors are perceived by the human eye and brain.
+Primary colors and their combinations are explained in detail.
+The visible spectrum and electromagnetic radiation are also covered.
+The text concludes with tips for setting up experiments to test theories related to color and light.</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -52506,7 +52753,11 @@
       <c r="E37" s="3" t="n"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers color theory, human vision, and experimentation.
+It discusses how colors are perceived and combined to create new hues.
+Primary colors and their combinations are also explored.
+The role of light and its wavelengths in color perception is explained.
+Experiments with RGB LED lights demonstrate color mixing principles.</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -52539,7 +52790,11 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores color theory and vision. 
+It discusses primary colors and their combinations. 
+The human eye can distinguish 10 million colors. 
+Experiments with RGB LED laboratories demonstrate color mixing. 
+Color perception is influenced by wavelength and intensity.</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -52572,7 +52827,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers experiments and research methods. 
+It discusses trigonometry and RGB LED laboratory experiments. 
+Key tips include designing simple experiments and varying one thing at a time. 
+Conclusions should summarize how results answer the research question. 
+Experiments help learn about something through observation and testing.</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -52605,7 +52864,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores interactive experiments with trigonometry and RGB LED lights. 
+It discusses observing effects of moving sliders and adjusting values.
+The goal is to learn about cause-and-effect relationships.
+A research question guides the experiment, aiming to draw conclusions.
+The text provides tips for designing effective experiments and writing conclusions.</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -52638,7 +52901,11 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores trigonometry and light experiments.
+It discusses observing cosine and tangent values as a dot moves around a circle.
+An RGB LED lab allows adjusting color values to observe effects.
+The text also touches on designing experiments and asking research questions.
+Rainbows and their causes are briefly mentioned.</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -52671,7 +52938,11 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers trigonometric functions and light experiments.
+It explores the behavior of COS and TAN theta values in a circle.
+An RGB LED laboratory is introduced for color adjustment experiments.
+Rainbows and their causes are also discussed as a topic of discovery.
+The lesson aims to uncover more about these concepts through interactive experiments.</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -52704,7 +52975,12 @@
       <c r="E43" s="3" t="n"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text explores light and color concepts.
+It mentions experiments with TAN values and RGB LED lights.
+The order of adjusting colors can affect results.
+White light is a mixture of colors with different wavelengths.
+The lesson aims to discover more about light and rainbows.</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -52737,7 +53013,12 @@
       <c r="E44" s="3" t="n"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text discusses an experiment with RGB LED lights and color mixing.
+It references previous lessons about the composition of white light and light waves.
+Students are guided through interactive activities to learn more about colors and wavelengths.
+The topic of rainbows and their causes is introduced for further exploration.
+The lesson aims to help students discover and confirm their understanding of light and colors.</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -52770,7 +53051,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+Experimenting with RGB LED and light properties.
+Understanding color mixture and wavelength.
+Exploring prisms and rainbow formation.
+Discovering how colors interact with light.
+Learning about the science of light and color.</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -52803,7 +53089,12 @@
       <c r="E46" s="3" t="n"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text reviews concepts about light and color.
+It covers white light as a mixture of colors with different wavelengths.
+Refraction separates colors at different angles, making them visible.
+This phenomenon can create rainbows, which will be explored further.
+The lesson invites interaction and discovery through a program.</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -52836,7 +53127,12 @@
       <c r="E47" s="3" t="n"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses the properties of light and color.
+White light is a mixture of colors with different wavelengths.
+Refraction causes each color to bend at a different angle.
+This phenomenon creates colorful events like rainbows.
+The lesson invites exploration and discovery about light and color.</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -52869,7 +53165,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses light and its properties.
+It explains how white light refracts into different colors.
+The behavior of light creates colorful events like rainbows.
+An interactive program allows users to explore light refraction.
+The topic is part of a lesson on the properties of light.</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -52902,7 +53203,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text explores light refraction and rainbows.
+It describes an interactive program to demonstrate this concept.
+White light is a mixture of colors with different wavelengths.
+Refraction separates these colors, creating a rainbow effect.
+The text also mentions the École polytechnique fédérale de Lausanne (EPFL) university.</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -52935,7 +53241,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary of the text:
+The text discusses light refraction and rainbows.
+It explains how white light is refracted at different angles.
+The École polytechnique fédérale de Lausanne (EPFL) is introduced as a research institute.
+The university's history and growth are outlined, from 11 students to 14,000 people.
+The EPFL has become a highly international institution with a strong focus on natural sciences and engineering.</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -52968,7 +53279,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers light refraction and rainbows.
+It also discusses the history and development of EPFL (École polytechnique fédérale de Lausanne).
+EPFL has grown rapidly since its inception in 1853.
+The university has a highly international environment with students from over 125 countries.
+EPFL encourages entrepreneurship and has a strong start-up culture among its students.</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -53001,7 +53317,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary of the text:
+The text discusses light refraction and rainbows.
+It also covers the history and growth of EPFL, a Swiss university.
+EPFL has become a top international university, attracting students from over 125 countries.
+The university has a selective admission process for international students and a high failure rate for first-year students.
+EPFL is ranked among the world's best universities in various rankings, including QS and Times Higher Education.</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -53034,7 +53355,12 @@
       <c r="E53" s="3" t="n"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses the properties of light and its refraction, creating rainbows. 
+It also covers the history and growth of EPFL, a Swiss university.
+EPFL has become highly international, attracting students and researchers worldwide.
+The university has a selective admission process for international students.
+EPFL ranks high in various global university rankings, particularly in engineering and technology.</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -53067,7 +53393,12 @@
       <c r="E54" s="3" t="n"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+EPFL is a top-ranked university with a strong focus on engineering and technology.
+The university has grown rapidly since its founding in 1969, with over 14,000 students and staff from 125 countries.
+Admission to EPFL is selective for international students, but not for Swiss residents who hold a maturité certificate.
+EPFL ranks highly in international university rankings, including QS World University Rankings and Times Higher Education.
+The university is known for its strong scientific impact, international outlook, and faculty-to-student ratio.</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -53100,7 +53431,15 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text appears to be a humorous article about giving cats an annual performance review. The author provides tongue-in-cheek guidelines on how to evaluate a cat's performance, including setting standards based on age and breed, focusing on impact, and providing specific feedback.
+Some of the key points from the article include:
+1. Evaluating a cat's performance against a standard that takes into account their age and breed.
+2. Using the situation-behavior-impact (SBI) model to provide specific and actionable feedback.
+3. Creating a performance improvement plan (PIP) when a cat is not meeting expectations.
+4. Providing regular individual feedback and acknowledging positive behaviors.
+5. Being aware of one's own role in a cat's performance, such as providing adequate space and toys.
+The article is written in a lighthearted and satirical tone, with the author using humorous examples and anecdotes to illustrate their points. It is not meant to be taken seriously, but rather as an entertaining and playful take on the idea of giving cats a performance review.
+In contrast, the first part of the text appears to be about a university or academic institution, specifically École polytechnique fédérale de Lausanne (EPFL), and its admission requirements and procedures. It seems unrelated to the rest of the text, which is about cat performance reviews.</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -53137,7 +53476,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses university rankings, specifically EPFL's rankings in Engineering and Technology.
+EPFL is ranked highly in various categories, including faculty to student ratio and scientific impact.
+The university also ranks well in international outlook and citation index.
+In contrast, the text also includes a satirical piece about giving cats their annual performance review.
+The two topics seem unrelated, with the first discussing academic rankings and the second being a humorous take on cat ownership.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -53174,7 +53518,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The article humorously discusses giving annual performance reviews to cats.
+It outlines guidelines for evaluating cat performance, including setting standards and goals.
+Feedback should be specific, actionable, and focused on impact.
+A performance improvement plan may be necessary for underperforming cats.
+The article uses satire to poke fun at management techniques and cat ownership.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -53207,7 +53556,11 @@
       <c r="E58" s="3" t="n"/>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The article satirically discusses giving annual performance reviews to cats. 
+It outlines guidelines for evaluating a cat's performance, including setting standards and focusing on impact.
+The article uses humor to convey the importance of constructive feedback and appreciation.
+Regular individual feedback sessions are recommended to address negative behaviors and praise positive ones.
+The tone is lighthearted and comedic, using satire to poke fun at management and leadership techniques.</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -53244,7 +53597,11 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses functional modeling for estimating power.
+It provides a model to evaluate and estimate power usage.
+The example given is an electric car with a battery and motor.
+The goal is to assess if the model is useful for estimation.
+Functional modeling helps understand how systems work.</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -53277,7 +53634,11 @@
       <c r="E60" s="3" t="n"/>
       <c r="F60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses functional modeling for estimating power.
+It provides a model to evaluate and estimate power usage.
+The topic of electric cars is introduced as an example.
+A basic explanation of how an electric car works is given.
+Functional modeling is used to understand and reflect on the process.</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -53314,7 +53675,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+Electric cars run on batteries that power electric motors.
+They have no tailpipe or gas tank, reducing emissions and maintenance needs.
+The motor and controller work together to regulate energy use.
+Regenerative braking recharges the battery using the car's momentum.
+Overall, electric cars offer an efficient and environmentally friendly alternative.</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -53351,7 +53717,12 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text describes how an electric car works, highlighting its key components. 
+It explains the role of the battery and electric motor in powering the vehicle.
+The electric car's structure is similar to fossil fuel-powered cars but lacks a tailpipe and gas tank.
+Regenerative braking allows the car to recharge its battery using the motor's momentum.
+Overall, the text provides an overview of electric car technology and its advantages.</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -53388,7 +53759,11 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Electric cars have a similar structure to fossil fuel-powered cars but lack a tailpipe and gas tank. 
+They are powered by an electric motor and battery, which supplies energy for acceleration. 
+The electric motor requires no oil or tune-ups and produces no emissions. 
+Regenerative braking is used to recharge the battery when the brakes are applied. 
+Overall, electric cars have several advantages over traditional fossil fuel-powered vehicles.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -53425,7 +53800,8 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+Electric cars have a similar structure to fossil fuel-powered cars but lack a tailpipe and gas tank. They are powered by an electric motor and battery, which supplies energy for acceleration. The controller regulates power to prevent the motor from burning out. Regenerative braking recharges the battery using the motor's momentum when brakes are applied. Electric cars have several advantages, including no oil or tune-ups required and reduced emissions.</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -53462,7 +53838,11 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Electric cars have a similar structure to fossil fuel-powered cars but lack a tailpipe and gas tank. 
+They are powered by an electric motor and battery, which provides acceleration and energy. 
+The electric motor requires no oil or tune-ups and produces no emissions. 
+Regenerative braking allows the car to recharge its battery using the motor's momentum. 
+Overall, electric cars offer a sustainable and efficient alternative to traditional vehicles.</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -53495,7 +53875,12 @@
       <c r="E66" s="3" t="n"/>
       <c r="F66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+Electric cars have a similar structure to fossil fuel-powered cars.
+They are powered by an electric motor and battery, with no tailpipe or gas tank.
+The electric motor provides acceleration and requires no oil or tune-ups.
+Regenerative braking allows the car to recharge its battery using momentum.
+This makes electric vehicles efficient and environmentally friendly.</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -53528,7 +53913,11 @@
       <c r="E67" s="3" t="n"/>
       <c r="F67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Electric cars have a similar structure to fossil fuel-powered cars but lack a tailpipe and gas tank. 
+They are powered by an electric motor and battery, which supplies energy for movement.
+The controller regulates power to prevent the motor from burning out.
+Regenerative braking recharges the battery using the motor's momentum when brakes are applied.
+Electric cars offer advantages like reduced emissions and lower maintenance needs.</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -53561,7 +53950,11 @@
       <c r="E68" s="3" t="n"/>
       <c r="F68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Electric cars have a similar structure to fossil fuel-powered cars but with an electric motor and battery. 
+The electric motor requires no oil or tune-ups and produces no emissions. 
+The battery powers the motor and electronic devices, providing acceleration and energy efficiency. 
+Regenerative braking allows the car to recharge its battery using the motor's momentum. 
+Overall, electric cars offer a sustainable and efficient alternative to traditional vehicles.</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -53594,7 +53987,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses electric cars and their components. 
+Electric cars have an electric motor, controller, and battery as the power source.
+Regenerative braking is used to recharge the battery when the car brakes.
+The text also touches on quantitative modeling and evaluation of electric car parameters.
+It relates to the topic of particulate nature of matter and rate of diffusion.</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -53627,7 +54025,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses electric cars and their components. 
+Electric cars have an electric motor, controller, and battery as the power source. 
+Regenerative braking allows the car to recharge its battery using momentum. 
+The overall structure of an electric car is similar to a fossil fuel-powered car. 
+The text also mentions diffusion and factors affecting its rate.</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -53660,7 +54063,11 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses the topic of diffusion in the context of particulate matter.
+It explores factors affecting the rate of diffusion, including temperature.
+The objective is to determine these factors and understand their impact.
+The text also touches on estimation problems related to calculating power.
+Diffusion and its relationship with temperature are key themes.</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -53693,7 +54100,11 @@
       <c r="E72" s="3" t="n"/>
       <c r="F72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses lab experiments and predictions.
+It covers the topic of particulate nature of matter, specifically rate of diffusion.
+The objective is to determine factors affecting rate of diffusion.
+Temperature's effect on rate of diffusion is a key point of inquiry.
+Lab work involves predicting outcomes and testing hypotheses.</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -53726,7 +54137,11 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers lab experimentation and prediction.
+It involves understanding diffusion and its factors.
+Temperature and molecular mass affect the rate of diffusion.
+An experiment is outlined with steps to regulate temperature and molecular mass.
+The goal is to test predictions and observe molecular interactions.</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -53759,7 +54174,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses experimentation and prediction in a lab setting.
+It also explores the effect of temperature on the rate of diffusion.
+Additionally, it touches on the process of photosynthesis in plants.
+Photosynthesis is crucial for plant survival, using light energy to produce food.
+The experiment involves regulating temperature and molecular mass to observe molecule interactions.</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -53792,7 +54212,11 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers experiment planning and execution.
+It involves predicting outcomes and testing hypotheses.
+Photosynthesis is introduced as a process by which plants produce food from light energy.
+Plants require light to survive and release oxygen as a byproduct.
+The experiment will explore how light affects photosynthesis in aquarium plants.</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -53825,7 +54249,11 @@
       <c r="E76" s="3" t="n"/>
       <c r="F76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses photosynthesis in plants, specifically in aquarium plants.
+It explores how light intensity affects photosynthesis.
+An experiment is outlined to investigate this relationship.
+Plants use light energy to produce food through photosynthesis, releasing oxygen as a byproduct.
+The process occurs in the green parts of plants and is essential for their survival.</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -53858,7 +54286,12 @@
       <c r="E77" s="3" t="n"/>
       <c r="F77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses photosynthesis in aquarium plants.
+It explores how light intensity affects photosynthesis.
+The experiment also examines seasonal effects on photosynthesis.
+Plants use light energy to produce food through photosynthesis.
+The process releases oxygen as a byproduct.</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -53891,7 +54324,12 @@
       <c r="E78" s="3" t="n"/>
       <c r="F78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+Photosynthesis in plants depends on light intensity and season.
+Plants use light energy to make food through photosynthesis.
+This process occurs in green parts of plants and releases oxygen.
+Aquarium plants' photosynthesis will be explored in relation to light and season.
+The experiment aims to understand how these factors affect plant growth.</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -53924,7 +54362,12 @@
       <c r="E79" s="3" t="n"/>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses photosynthesis in plants, a process using light energy to produce food.
+Plants require light, carbon dioxide, water, nutrients, and minerals for photosynthesis.
+Photosynthesis occurs in green parts of plants and releases oxygen as a byproduct.
+The text also touches on collaborative work and experimental procedures.
+Aquarium plants' photosynthesis is affected by light and the season of the year.</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -53957,7 +54400,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses plant survival and food production through photosynthesis.
+Photosynthesis uses light energy, carbon dioxide, water, and nutrients to produce oxygen.
+It occurs in green parts of plants and is essential for their survival.
+The text also touches on collaborative work and problem-solving strategies.
+Aquarium plants' photosynthesis is explored in relation to seasonal changes.</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -53990,7 +54438,12 @@
       <c r="E81" s="3" t="n"/>
       <c r="F81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses collaborative work challenges.
+It also explores plant photosynthesis and its importance.
+Plants produce oxygen through photosynthesis using light energy.
+The process occurs in green parts of plants.
+Investigations on light and season effects on photosynthesis are also mentioned.</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -54023,7 +54476,11 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers collaborative work challenges and improvements.
+It also explores plant management for ammonia production.
+Photosynthesis in aquarium plants is another topic discussed.
+The Haber process for synthesizing ammonia is introduced.
+Managing variables to optimize production is a key theme.</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -54056,7 +54513,12 @@
       <c r="E83" s="3" t="n"/>
       <c r="F83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text discusses a collaborative task involving ammonia production.
+It requires managing a plant to produce as much ammonia as possible.
+The Haber process is used to synthesize ammonia from nitrogen and hydrogen.
+Independent variables can be adjusted to analyze results and optimize production.
+The goal is to produce the maximum amount of NH3 at the least cost.</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -54089,7 +54551,8 @@
       <c r="E84" s="3" t="n"/>
       <c r="F84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text covers various scientific topics, including plant management and ammonia production. It also touches on biology, specifically the mammalian eye and photosynthesis. Additionally, it mentions transcription and translation concepts. The Haber process for synthesizing ammonia is discussed in detail. Overall, the text explores different scientific investigations and experiments.</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -54122,7 +54585,12 @@
       <c r="E85" s="3" t="n"/>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers various scientific topics, including the mammalian eye and its parts.
+It also explores photosynthesis in aquarium plants and its relation to light and season.
+Additionally, transcription and translation concepts are introduced through a YouTube video.
+The Haber process for synthesizing ammonia is discussed with a focus on optimization.
+These topics aim to provide interactive learning experiences through labs and simulations.</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -54155,7 +54623,11 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers the structure and function of the mammalian eye. 
+It explains the role of parts like cornea, lens, and retina in sight perception.
+The text also touches on a lab investigation about light reflection and iris control.
+Additionally, it mentions the Haber process for ammonia synthesis.
+The overall theme is biology and chemistry concepts.</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -54188,7 +54660,11 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers the structure and function of the mammalian eye. 
+It explains how different parts work together to enable sight. 
+The eye is compared to a camera with similar components. 
+Light perception and conversion to electrochemical impulses are key functions. 
+The text also touches on the Haber process for ammonia synthesis.</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -54221,7 +54697,11 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The mammalian eye is a sensory organ with parts adapted for sight.
+It has photo receptors that perceive light as a stimulus.
+The eye's components work like a camera to provide clear vision.
+The cornea, lens, retina, and iris all play vital roles in focusing light.
+The human eye converts light into electrochemical impulses, allowing us to see.</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -54254,7 +54734,11 @@
       <c r="E89" s="3" t="n"/>
       <c r="F89" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The mammalian eye is a sensory organ with parts adapted for perception of light. 
+It has cornea, lens, retina, and iris that work together for clear vision. 
+The eye functions like a camera, focusing light onto the retina. 
+Rod and cone cells in the retina convert light to electrochemical impulses. 
+The human eye accommodates changing lighting conditions and focuses light rays for sharp vision.</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -54287,7 +54771,11 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The mammalian eye has various parts adapted for perception of sight.
+It includes the cornea, lens, retina, and iris, each playing a vital role.
+The eye works similarly to a camera, with each part contributing to clear vision.
+The retina converts light into electrical impulses sent to the brain.
+The human eye accommodates changing lighting conditions and focuses light rays.</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -54320,7 +54808,11 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The mammalian eye is a sensory organ with photo receptors.
+It has various parts, including cornea, lens, and retina, adapted to their functions.
+The retina converts light rays into electrical impulses sent to the brain.
+The eye accommodates changing lighting conditions and focuses light rays from varying distances.
+The proper functioning of all components allows for image perception.</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -54353,7 +54845,12 @@
       <c r="E92" s="3" t="n"/>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The mammalian eye has multiple parts that work together for sight perception.
+Key components include the cornea, lens, retina, and iris, which control light entry.
+The retina converts light rays into electrical impulses sent to the brain.
+The macula enables sharp vision, while the peripheral retina handles peripheral vision.
+Proper functioning of these components allows the eye to focus and perceive images.</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -54386,7 +54883,11 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers the structure of the mammalian eye and its parts. 
+It mentions the cornea, lens, retina, and iris and their roles. 
+The text also briefly touches on DNA and nucleotides. 
+It describes the components of a nucleotide, including nitrogenous base and phosphate group. 
+The topic seems to be a transition between biology lessons on vision and molecular biology.</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -54419,7 +54920,12 @@
       <c r="E94" s="3" t="n"/>
       <c r="F94" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text reviews DNA structure and nucleotides.
+It reminds readers of key components: nitrogenous bases, sugar, and phosphate groups.
+Concentrated and dilute solutions are also defined.
+The lesson is entering its second phase, Conceptualization.
+Readers are encouraged to recall prior knowledge before moving forward.</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -54452,7 +54958,11 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text reviews DNA structure and nucleotides.
+It covers the components of nucleotides, including nitrogenous bases.
+The concept of dilute solutions is also mentioned briefly.
+The text prepares for a lesson phase focused on conceptualization.
+Key concepts include DNA, nucleotides, and proteins.</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -54485,7 +54995,11 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text reviews DNA structure and nucleotides.
+It covers nitrogenous bases, sugar, and phosphate groups.
+The lesson is in its second phase, Conceptualization.
+The goal is to reinforce prior knowledge before moving forward.
+Key concepts include DNA, nucleotides, and amino acids.</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -54518,7 +55032,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text reviews DNA structure and nucleotides.
+It also covers proteins and amino acids.
+Genetic information directs protein synthesis in ribosomes.
+The genetic code consists of codons, with three bases per amino acid.
+A gene encodes a specific protein through its sequence of bases.</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -54551,7 +55070,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text reviews DNA structure and nucleotides.
+It discusses the concept of genetic information directing protein synthesis.
+The sequence of bases in DNA encodes a protein like a recipe book.
+A gene is a sequence of bases encoding a particular protein.
+The laboratory simulation demonstrates transcription with base pairing rules.</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -54584,7 +55108,12 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text reviews DNA structure and nucleotides.
+It discusses genetic information directing protein synthesis in cells.
+The sequence of bases in DNA codes for protein creation.
+A gene encodes a specific protein through codons and base pairing.
+The process involves transcription, mRNA formation, and translation to ribosomes.</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -54617,7 +55146,12 @@
       <c r="E100" s="3" t="n"/>
       <c r="F100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The structure of DNA and nucleotides is reviewed.
+Genetic information directs protein synthesis in cell ribosomes.
+The sequence of bases in DNA codes for protein creation.
+A gene is a sequence of bases encoding a particular protein.
+The process involves transcription and translation to create proteins.</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -54650,7 +55184,12 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text reviews DNA structure and nucleotides.
+It discusses transcription and translation processes in cells.
+mRNA molecules carry genetic information from the nucleus to the cytoplasm.
+Translation occurs at ribosomes, where tRNA brings amino acids to form proteins.
+The process results in protein synthesis with specific amino acid sequences.</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -54683,7 +55222,11 @@
       <c r="E102" s="3" t="n"/>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers scientific concepts, including DNA and RNA.
+It references a historical story about Archimedes and a golden crown.
+The laboratory section explores DNA transcription and translation.
+The process of protein synthesis is described, involving mRNA and tRNA molecules.
+Key biological concepts are introduced, preparing students for the next course phase.</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -54716,7 +55259,12 @@
       <c r="E103" s="3" t="n"/>
       <c r="F103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text covers various topics including Archimedes' discovery of fraud in a golden crown.
+It also features a personal story of buying a dream car, an AM General Hummer H1.
+Additionally, the text discusses DNA transcription and translation processes.
+It includes interactive lab simulations for learning about base pairing rules and protein synthesis.
+The topics appear to be unrelated, covering history, cars, and molecular biology.</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -54749,7 +55297,13 @@
       <c r="E104" s="3" t="n"/>
       <c r="F104" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text covers three unrelated topics: 
+Archimedes and Vitruvius' story about a golden crown.
+A car enthusiast's video about buying and testing an AM General Hummer H1.
+A biology lesson on DNA transcription and translation, including RNA and protein synthesis. 
+These topics are distinct and separate from one another.
+The text includes various links and disclaimers related to the car video.</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -54782,7 +55336,11 @@
       <c r="E105" s="3" t="n"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers various topics including buying a dream car, off-roading, and car-related content. 
+It also mentions robotic arm geometry and DNA transcription. 
+Additionally, it touches on protein synthesis and translation. 
+The content is from different YouTube videos and sources. 
+Overall, it's a mix of automotive and scientific topics.</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -54815,7 +55373,12 @@
       <c r="E106" s="3" t="n"/>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers robotic arm geometry and types. 
+It explains rectangular, cylindrical, spherical, and jointed spherical arms.
+Additionally, it touches on DNA transcription and translation processes.
+mRNA molecules carry genetic information from the nucleus to the cytoplasm.
+The process involves tRNA and rRNA molecules in protein synthesis.</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -54848,7 +55411,11 @@
       <c r="E107" s="3" t="n"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers robotic arm geometry and DNA transcription. 
+It explains four types of robotic arms and their movements.
+It also discusses DNA transcription and translation processes.
+The role of RNA molecules, including tRNA and rRNA, is highlighted.
+Key concepts in biology and engineering technology are explored.</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -54881,7 +55448,12 @@
       <c r="E108" s="3" t="n"/>
       <c r="F108" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text covers various unrelated topics. 
+It touches on robotics, racism, and molecular biology.
+Racism is discussed from a social learning perspective.
+Molecular biology concepts, such as DNA transcription and translation, are also explored.
+These topics seem to be unrelated and lack a cohesive theme.</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -54914,7 +55486,11 @@
       <c r="E109" s="3" t="n"/>
       <c r="F109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers racism and its effects on society. 
+It examines the root causes from a social learning perspective.
+Additionally, it touches on DNA transcription and translation.
+The process of creating mRNA molecules is described.
+Racism and molecular biology are the two main topics discussed.</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -54947,7 +55523,12 @@
       <c r="E110" s="3" t="n"/>
       <c r="F110" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+Racism is prejudice based on the belief of racial superiority.
+It has a profound impact on humanity, degrading our future.
+The root causes and effects of racism will be examined from a social learning perspective.
+The text also touches on DNA transcription and translation in a virtual lab setting.
+Understanding these concepts will lead to further discussion and exploration in the course.</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -54980,7 +55561,12 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses racism and its impact on society.
+It explores the root causes of racism from a social learning perspective.
+However, the text also abruptly changes topic to discuss molecular biology and genetics.
+Additionally, it covers the rectilinear propagation of light and its properties.
+Overall, the text touches on three unrelated topics: racism, molecular biology, and physics.</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -55013,7 +55599,12 @@
       <c r="E112" s="3" t="n"/>
       <c r="F112" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers two main topics: racism and molecular biology.
+It discusses protein synthesis and translation of DNA.
+RNA molecules, including tRNA and rRNA, play a crucial role in this process.
+The text also explores the property of rectilinear propagation of light.
+Light travels in a straight line, forming shadows and day-night cycles.</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -55046,7 +55637,13 @@
       <c r="E113" s="3" t="n"/>
       <c r="F113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers two main topics: 
+Racism and molecular biology experiments.
+It explains protein synthesis and translation of DNA.
+Transfer RNA (tRNA) and ribosomal RNA (rRNA) are discussed.
+The second part shifts to physics, discussing light propagation.
+Rectilinear propagation of light is demonstrated through an experiment.</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
@@ -55079,7 +55676,12 @@
       <c r="E114" s="3" t="n"/>
       <c r="F114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text covers lab experiments and scientific concepts.
+It discusses DNA translation and protein synthesis.
+The role of mRNA, tRNA, and rRNA molecules is explained.
+The rectilinear propagation of light is demonstrated through experiments.
+Light travels in a straight line, forming shadows and day-night cycles.</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -55112,7 +55714,12 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers lab experiments and scientific concepts.
+It introduces the Experiment Lab and Bending Light Lab for hands-on learning.
+DNA translation, tRNA, and rRNA are explained in the context of protein formation.
+The rectilinear propagation of light is demonstrated through experiments and examples.
+The topics range from biology to physics and mathematics, including quadratic equations.</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -55145,7 +55752,12 @@
       <c r="E116" s="3" t="n"/>
       <c r="F116" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers lab experiments and equipment usage.
+It discusses translation of DNA and RNA molecules' roles.
+Rectilinear propagation of light is also explored with demonstrations.
+The formation of shadows, eclipses, and day/night cycles are explained.
+Quadratic equations and algebra topics are mentioned as additional learning material.</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -55178,7 +55790,12 @@
       <c r="E117" s="3" t="n"/>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers various science topics, including light propagation and genetics.
+It discusses rectilinear propagation of light and its consequences.
+The translation of DNA into amino acids is also explained.
+Quadratic equations and algebra are mentioned as additional topics.
+These subjects are covered through labs, videos, and demonstrations.</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
@@ -55211,7 +55828,13 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text covers two main topics: 
+Light propagation and quadratic equations.
+It discusses rectilinear propagation of light and its examples.
+Quadratic equations are also introduced with a focus on graphical solutions.
+The quadratic formula is mentioned as a tool for solving equations.
+Key concepts include light traveling in straight lines and algebraic problem-solving.</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -55244,7 +55867,12 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses solving quadratic equations.
+It mentions using the quadratic formula and graphical methods.
+The quadratic formula is used to find values of x.
+Resources are provided for further learning, including videos and websites.
+Quadratic equations can be solved when y=0 and a, b, c are known.</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -55277,7 +55905,11 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses solving quadratic equations.
+It mentions using graphical methods to find solutions.
+A website, MathMeeting.com, offers free algebra videos.
+Quadratic equations can be solved when y=0 and a, b, c are known.
+Graphical and formula methods yield the same results for x.</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -55310,7 +55942,11 @@
       <c r="E121" s="3" t="n"/>
       <c r="F121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses solving quadratic equations using graphs.
+It provides examples and resources, including free videos.
+The graphical method involves setting y=0 to find x values.
+This approach yields the same results as other methods.
+Quadratic equations can be solved graphically with known coefficients a, b, and c.</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -55343,7 +55979,11 @@
       <c r="E122" s="3" t="n"/>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers solving quadratic equations using graphs.
+It discusses two methods for solving quadratic equations.
+Both methods yield the same results for x values.
+Leadership qualities and self-motivation are also briefly mentioned.
+Quadratic equations can be solved graphically with known coefficients.</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -55376,7 +56016,11 @@
       <c r="E123" s="3" t="n"/>
       <c r="F123" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses achieving success in life through leadership qualities. 
+It touches on solving quadratic equations using two methods. 
+Both methods yield the same results for x when y=0 and a, b, c are known.
+Leadership is analyzed as a key factor in goal achievement.
+Success requires endurance, self-motivation, and strong character traits.</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -55409,7 +56053,12 @@
       <c r="E124" s="3" t="n"/>
       <c r="F124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses finding purpose in life and achieving success.
+It highlights the importance of leadership qualities, endurance, and self-motivation.
+The topic of leadership and its variations is introduced for analysis.
+A quote suggests that leadership is about action and example, not just position or title.
+The text also briefly mentions solving quadratic equations, but this seems unrelated to the main theme.</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -55442,7 +56091,11 @@
       <c r="E125" s="3" t="n"/>
       <c r="F125" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses leadership and its true meaning. 
+It emphasizes that leadership is about action, not title. 
+The conversation then shifts to quadratic equations. 
+Graphical and formula methods can solve these equations. 
+Both methods yield the same results for x.</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
@@ -55475,7 +56128,12 @@
       <c r="E126" s="3" t="n"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores leadership and its true meaning.
+It discusses what leadership in Utopia would look like.
+Lars Sudmann shares strategies on self-leadership to develop into a "Utopia leader".
+The talk highlights personal journeys of great leaders and lessons from the golden age of leadership.
+Leadership is about action and example, not just position or title.</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -55508,7 +56166,12 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The concept of leadership is discussed, emphasizing action and example.
+A TEDxUtopia talk explores what leadership in Utopia would look like.
+Lars Sudmann shares strategies for self-leadership development.
+He draws from personal journeys of great leaders and historical lessons.
+The goal is to develop into a "Utopia leader" with effective leadership skills.</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -55541,7 +56204,12 @@
       <c r="E128" s="3" t="n"/>
       <c r="F128" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses leadership in Utopia and strategies for self-leadership.
+It references a TEDx talk by Lars Sudmann on overcoming the "leadership formula of doom".
+Practical tasks are also mentioned, including testing pH levels of coffee and soap.
+Additionally, mathematical concepts, such as solving for x, are touched upon.
+The text covers various topics, including leadership, chemistry, and problem-solving.</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -55574,7 +56242,12 @@
       <c r="E129" s="3" t="n"/>
       <c r="F129" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses leadership in Utopia and strategies for self-leadership.
+It explores the "leadership formula of doom" and how great leaders overcome it.
+Additionally, the text touches on chemistry concepts, including pH levels and acid-base reactions.
+It also mentions procedures for testing pH levels and predicting color changes.
+Overall, the text covers leadership development and basic chemistry principles.</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -55607,7 +56280,12 @@
       <c r="E130" s="3" t="n"/>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers experiments with pH levels of coffee and soap.
+It explores how volume changes affect acidity and basicity.
+Acids have a pH of 1-6, while bases have a pH of 8-14.
+A brief mention of the Digital Divide is made, but not elaborated on.
+The text also touches on solving equations and predicting color changes in solutions.</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -55640,7 +56318,12 @@
       <c r="E131" s="3" t="n"/>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text covers multiple topics, including chemistry and digital divide.
+Acids and bases react to form neutral solutions with specific pH levels.
+The digital divide lesson aims to educate students on its meaning and effects.
+It also explores old and new economies and their features.
+Chemistry and math concepts are also briefly mentioned.</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
@@ -55673,7 +56356,11 @@
       <c r="E132" s="3" t="n"/>
       <c r="F132" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The lesson covers the concept of Digital Divide.
+It aims to explain the meaning and features of old and new economies.
+The impact of Digital Divide on people's lives is also discussed.
+A video is provided for better understanding.
+The topic focuses on digital inequality and its effects.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -55706,7 +56393,12 @@
       <c r="E133" s="3" t="n"/>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The digital divide refers to unequal access to information technology.
+It affects people's lives and can be classified by gender, income, and location.
+Global digital divide occurs between countries with differing technological access.
+The concept describes the gap between those with and without effective access to ICT.
+Understanding the digital divide is crucial for explaining its impact on society.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -55739,7 +56431,11 @@
       <c r="E134" s="3" t="n"/>
       <c r="F134" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to unequal access to ICT.
+It affects people based on gender, income, and location.
+Global digital divide occurs between countries.
+This gap limits access to information and technology.
+It's a societal issue with significant implications.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -55772,7 +56468,11 @@
       <c r="E135" s="3" t="n"/>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to unequal access to technology.
+It affects people based on gender, income, and location.
+Global digital divide exists between countries with varying technological access.
+This gap separates those with internet access from those without.
+The digital divide highlights societal disparities in ICT access.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -55805,7 +56505,11 @@
       <c r="E136" s="3" t="n"/>
       <c r="F136" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap in internet access between demographics and regions.
+Half of the world's population remains offline, with Africa having the highest percentage without connection.
+The digital divide affects not only access but also quality of infrastructure and digital literacy.
+Digital technologies can boost economic growth and education, but benefits are unevenly distributed.
+Closing the gap in internet access is critical for global participation in the digital economy.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -55838,7 +56542,11 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap between those with internet access and those without.
+Half of the world's population remains offline, with Africa having 88% without connection.
+The divide also encompasses disparities in digital infrastructure and skills.
+Digital technologies bring numerous benefits, but unevenly distributed due to limited connectivity.
+Closing the internet access gap is critical for global participation in the digital economy.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -55871,7 +56579,11 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap between those with internet access and those without. 
+Half of the world's population remains offline, with Africa having 88% without connection.
+The divide also includes discrepancies in digital infrastructure and skills.
+Closing the gap is crucial for global participation in the digital economy.
+Innovative solutions are needed to deploy technology sustainably and affordably.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -55904,7 +56616,11 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap between those with access to modern technology and those without. 
+Half of the world's population lacks internet access, with Africa having the highest percentage. 
+The digital divide encompasses not only access but also quality and skills. 
+Digital technologies can boost economic growth and education, but benefits are unevenly distributed. 
+Closing the gap in internet access is critical for global prosperity.</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -55937,7 +56653,11 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap between those with internet access and those without. 
+Half of the world's population remains offline, with Africa having the highest percentage.
+The digital divide affects not only access but also quality of infrastructure and digital literacy.
+Closing this gap is critical for global prosperity and economic growth.
+Innovative solutions are needed to address the digital divide and promote equitable use of technology.</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -55970,7 +56690,11 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to the gap in internet access between demographics and regions. 
+Half of the world's population remains offline, with Africa having the highest percentage without connection. 
+The digital divide encompasses not only access but also quality of infrastructure and digital literacy. 
+Digital technologies can bring economic growth and opportunities, but benefits are unevenly distributed. 
+Closing the gap in internet access is critical for global prosperity and participation in the digital economy.</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -56007,7 +56731,11 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The digital divide refers to unequal internet access globally.
+Half of the world's population remains offline, with Africa at 88% disconnected.
+The gap affects not only access but also quality and skills.
+Digital technologies can boost economies and education, but benefits are unevenly distributed.
+Closing the gap is critical for global prosperity and digital equality.</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -56040,7 +56768,12 @@
       <c r="E143" s="3" t="n"/>
       <c r="F143" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The world faces a digital divide, with half the population offline.
+Asia has the most people without internet, while Africa has the highest percentage.
+Male internet users outnumber females in every region.
+Digital technologies can boost economies and improve education, but benefits are unevenly distributed.
+Closing the gap in internet access is critical for global prosperity.</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
@@ -56073,7 +56806,8 @@
       <c r="E144" s="3" t="n"/>
       <c r="F144" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text covers various topics, including three-dimensional geometry and sexual selection in guppies. It mentions objectives of 3D geometry and variables in a virtual laboratory. The text also references a research article on natural selection in guppies. Additionally, it lists geometrical properties and angles between lines and planes. Key concepts include skew lines and projection of a line onto a plane.</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -56106,7 +56840,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text covers objectives of Three Dimensional Geometry.
+It includes topics such as geometrical properties and angles between lines and planes.
+Natural selection and UV radiation are also mentioned in separate contexts.
+The text references a research article on natural selection in guppies.
+It concludes with an invitation to collaborate on a project measuring UV levels.</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -56139,7 +56878,12 @@
       <c r="E146" s="3" t="n"/>
       <c r="F146" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses ultraviolet radiation and its effects on humans.
+It touches on the importance of protection from UV radiation.
+A project is mentioned where students measure UV levels in their town.
+The project also studies awareness of UV radiation among family members.
+Students can collaborate globally to compare their results.</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -56172,7 +56916,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses ultraviolet radiation and its effects on humans.
+It highlights the importance of protection from UV radiation.
+A project is mentioned where students measure UV levels and awareness in their town.
+The project uses UV light sensitive beads and a standardized UV scale.
+Students can compare results with others worldwide using online resources.</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -56205,7 +56954,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses the effects of ultraviolet radiation on the skin.
+It highlights the importance of protection from UV radiation worldwide.
+A project is introduced where students measure UV levels and study awareness in their community.
+The project uses UV-sensitive beads and a standardized UV scale for comparison.
+Students can experiment with different sunscreens to test their effectiveness in blocking UV radiation.</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -56238,7 +56992,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses ultraviolet radiation and its effects on the skin.
+It introduces the UV Index, a standardized scale measuring UV radiation levels worldwide.
+An experiment is proposed to test different methods of protecting skin from UV radiation.
+Materials needed include UV sensitive beads, sunscreen, and a UV level scale.
+The goal is to determine effective ways to block UV radiation and protect the skin.</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -56271,7 +57030,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses ultraviolet radiation and its effects on skin.
+An experiment is proposed to test methods of protection from UV radiation.
+Materials needed include UV sensitive beads, sunscreen, and a UV level scale.
+The goal is to evaluate effective and non-effective ways to block UV radiation.
+The activity aims to raise awareness about UV rays and their dangers.</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -56304,7 +57068,12 @@
       <c r="E151" s="3" t="n"/>
       <c r="F151" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses ultraviolet radiation and its effects on the skin.
+It encourages readers to develop an hypothesis on how to protect themselves from UV radiation.
+An experiment is proposed to test different methods of protection, including sunscreen with various protective factors.
+The goal is to determine which methods are effective in blocking UV radiation.
+The activity aims to educate readers about UV rays and promote awareness of skin protection.</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -56337,7 +57106,12 @@
       <c r="E152" s="3" t="n"/>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses ultraviolet radiation and its effects on skin.
+It encourages readers to develop an hypothesis on how to protect themselves from UV radiation.
+An experiment is proposed to test different methods of blocking UV radiation.
+Materials such as UV sensitive beads, sunscreen, and a UV level scale are needed for the experiment.
+The goal is to learn about effective ways to protect skin against UV damage.</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -56370,7 +57144,12 @@
       <c r="E153" s="3" t="n"/>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers an experiment to test sunscreen protection against UV radiation.
+Students develop a hypothesis and test various protective factors.
+Materials include UV sensitive beads, sunscreen, and a UV level scale.
+The goal is to evaluate effective ways to block UV radiation.
+The activity teaches about UV benefits, dangers, and skin protection methods.</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -56403,7 +57182,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses an interactive science activity involving acids, bases, and UV rays.
+Students develop hypotheses and conduct experiments to learn about these concepts.
+They evaluate their community's awareness of UV risks and explore protective measures.
+The activity involves using an app to investigate substances and their acidity or basicity.
+It aims to educate students about the benefits and dangers of UV rays.</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -56436,7 +57220,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text covers science activities and experiments. 
+It involves exploring acids and bases, UV rays, and their effects.
+Students develop hypotheses and investigate substances using an app.
+They learn about protecting skin from UV damage and chemical reactions.
+The goal is to educate students about science concepts in a interactive way.</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -56469,7 +57258,11 @@
       <c r="E156" s="3" t="n"/>
       <c r="F156" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers acids and bases, including their dangers.
+It mentions a reaction between hydrochloric acid and calcium carbonate.
+The topic of UV rays and skin protection is also introduced.
+An interactive activity is suggested to investigate acidic and basic substances.
+Chemical reactions and safety are key themes in the text.</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -56502,7 +57295,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers acids and bases, including their reactions.
+Marble reacts with hydrochloric acid due to its calcium carbonate composition.
+A simple electrical circuit consists of a wire, battery, and bulb connected in series.
+Conductive parts must connect in a closed circular arrangement for the circuit to work.
+The battery creates voltage, forcing electrons to flow from negative to positive.</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -56535,7 +57333,12 @@
       <c r="E158" s="3" t="n"/>
       <c r="F158" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers acids and bases, including their reaction with calcium carbonate.
+It also discusses electrical circuits and their components, such as wires and batteries.
+A simple electrical circuit requires a closed circular arrangement of conductive parts.
+The battery creates a potential difference, or voltage, that forces electrons to flow.
+Electrical circuits and chemical reactions are the main topics explored in the text.</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -56568,7 +57371,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text covers acids and bases, electrical circuits, and scientific hypotheses.
+It explains how calcium carbonate reacts with hydrochloric acid.
+A simple electrical circuit requires a wire, battery, and bulb connected in series.
+Conductive parts must connect in a closed circular arrangement to create voltage.
+The text also discusses formulating hypotheses using independent and dependent variables.</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -56601,7 +57409,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers topics in chemistry and physics.
+It discusses acids and bases, as well as electrical circuits.
+A simple electrical circuit requires a wire, battery, and bulb connected in series.
+Conductive parts must connect in a closed circular arrangement to create voltage.
+Hypothesis formulation and experimentation are also briefly introduced.</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -56634,7 +57447,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses acids, bases, and chemical reactions.
+It also covers electrical circuits and hypothesis formulation.
+A good hypothesis includes an independent and dependent variable.
+The text emphasizes that hypotheses may not be confirmed after experimentation.
+Scientific experiments can lead to valuable knowledge even if the hypothesis is rejected.</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -56667,7 +57485,12 @@
       <c r="E162" s="3" t="n"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text covers various scientific topics, including geology and biology.
+It discusses the composition of marble and its reaction with acid.
+A hypothesis is defined as an "If...then..." statement with variables.
+The text also touches on experimental procedures and variable identification.
+Scientific experiments and hypothesis testing are emphasized throughout.</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -56700,7 +57523,12 @@
       <c r="E163" s="3" t="n"/>
       <c r="F163" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers biology basics and scientific experimentation.
+It discusses forming hypotheses with independent and dependent variables.
+A good hypothesis uses an "If...then..." statement to link variables.
+Experimentation may lead to rejection of a hypothesis, still providing valuable knowledge.
+The text also touches on electrical circuits and microscope images of lung cells.</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -56733,7 +57561,12 @@
       <c r="E164" s="3" t="n"/>
       <c r="F164" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses basic biology concepts and definitions.
+It explores the diversity of organisms and cells that make up life.
+A hypothesis is introduced as a statement linking independent and dependent variables.
+The text explains how to formulate and test a hypothesis through experimentation.
+It emphasizes the importance of understanding variable relationships in scientific inquiry.</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -56766,7 +57599,12 @@
       <c r="E165" s="3" t="n"/>
       <c r="F165" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses cells and their diversity.
+It highlights the discovery of the nucleus in plant and animal cells, showing unity in life.
+A hypothesis is formulated with variables to test a theory.
+Experiments may confirm or reject a hypothesis, leading to valuable knowledge.
+The text guides readers through testing a hypothesis and analyzing experimental data.</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
@@ -56799,7 +57637,12 @@
       <c r="E166" s="3" t="n"/>
       <c r="F166" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses cells, organisms, and biology concepts.
+It covers cell structures, including nuclei, organelles, and membranes.
+A hypothesis can be formulated to test relationships between variables.
+Experiments may confirm or reject hypotheses, leading to valuable knowledge.
+The text also guides readers through testing a hypothesis and analyzing results.</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
@@ -56836,7 +57679,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The discovery of the nucleus in cells reveals a unity in life.
+Plant and animal cells share common design and functions.
+The text describes cell components, including organelles and molecules.
+It also covers experimental procedures and variables in scientific investigations.
+Cell biology concepts are explained for middle school and high school students.</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
@@ -56873,7 +57721,11 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers cell biology for middle and high school students. 
+It discusses plant and animal cells, including organelles and their functions. 
+Key components like the nucleus, mitochondria, and cell membrane are highlighted. 
+The text also touches on experimental procedures and variables in cell biology experiments. 
+It provides an overview of cellular structure and function.</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
@@ -56906,7 +57758,11 @@
       <c r="E169" s="3" t="n"/>
       <c r="F169" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers cell components and their importance. 
+It discusses the nucleus, mitochondria, and other organelles.
+The role of these components in biological development is highlighted.
+Experimental procedures and variables are also mentioned.
+Cell structure and function are the main themes.</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
@@ -56943,7 +57799,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The cell nucleus contains genetic material, namely DNA.
+Genes determine biological development and are inherited from parents.
+Characteristics pass from parent to child through genes in DNA.
+Cells have various components, including mitochondria and ribosomes.
+These components work together to support cellular function.</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
@@ -56976,7 +57837,11 @@
       <c r="E171" s="3" t="n"/>
       <c r="F171" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The cell nucleus is crucial as it contains genetic material, namely DNA. 
+Genes determine biological development and are inherited from parents. 
+Proteins and amino acids play a significant role in this process. 
+The cell's structure, including organelles, is essential for its function. 
+Genetic material is passed down through generations, influencing characteristics.</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
@@ -57009,7 +57874,12 @@
       <c r="E172" s="3" t="n"/>
       <c r="F172" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The cell contains genetic material, namely DNA, which passes characteristics from parent to child.
+Genes are specific parts of DNA that determine inherited traits.
+DNA is composed of nucleotides with four different nitrogen bases: A, T, C, and G.
+These bases pair in a complementary manner, forming a double-stranded chain.
+The text also covers cell structure, including organelles and proteins made from amino acid chains.</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
@@ -57042,7 +57912,12 @@
       <c r="E173" s="3" t="n"/>
       <c r="F173" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers proteins, amino acids, and nucleic acids.
+It explains the structure of DNA and its building blocks, nucleotides.
+There are 20 amino acids and 4 types of nucleotides in DNA.
+The central doctrine of biology involves protein synthesis and genetic information flow.
+The text also touches on cell components and structures, including organelles and chromosomes.</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -57075,7 +57950,12 @@
       <c r="E174" s="3" t="n"/>
       <c r="F174" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The structure of nucleic acids, specifically DNA, is composed of nucleotides.
+Nucleotides consist of a nitrogen base, sugar, and phosphate group.
+There are four types of nucleotides in DNA, differing only in their nitrogen base.
+The flow of genetic information is fundamental to molecular biology and genetics.
+Cellular components, including the nucleus and organelles, play a crucial role in this process.</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -57108,7 +57988,7 @@
       <c r="E175" s="3" t="n"/>
       <c r="F175" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers the central doctrine of biology, focusing on protein synthesis and genetic information. It introduces key cellular components and structures. The flow of genetic information is emphasized as a basis for molecular biology. The text invites readers to take on a researcher role and explore hypotheses. It provides an overview of cell structure and biology concepts.</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
@@ -57141,7 +58021,12 @@
       <c r="E176" s="3" t="n"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text introduces a biology research scenario, exploring protein synthesis and DNA's role. 
+It invites readers to investigate cellular components and their functions. 
+Key topics include cell structure and biology concepts, such as mitochondria and ribosomes. 
+The text aims to engage readers in an interactive learning experience. 
+Cellular biology and investigation are the primary themes covered.</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -57174,7 +58059,12 @@
       <c r="E177" s="3" t="n"/>
       <c r="F177" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text explores the world of biology, focusing on cellular components.
+It invites investigation into DNA's role in protein synthesis.
+Key biological processes like replication, transcription, and translation are mentioned.
+Cellular structures such as mitochondria, ribosomes, and the nucleus are listed.
+The text appears to be an introduction to a biology-themed game or educational resource.</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
@@ -57207,7 +58097,12 @@
       <c r="E178" s="3" t="n"/>
       <c r="F178" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text explores protein synthesis and DNA's role in it.
+It investigates replication, transcription, and translation processes.
+Variations in DNA sequences and their effects on phenotypes are discussed.
+Cell structure components such as mitochondria and ribosomes are listed.
+The text appears to be an educational game or lesson on cell biology and genetics.</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -57240,7 +58135,12 @@
       <c r="E179" s="3" t="n"/>
       <c r="F179" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses DNA, RNA, and protein synthesis.
+It covers transcription, translation, and replication processes.
+Variations in DNA sequences and their effects on phenotypes are explored.
+Cell structure and organelles, such as mitochondria and ribosomes, are mentioned.
+The text appears to be a study guide or educational resource for cell biology.</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -57273,7 +58173,11 @@
       <c r="E180" s="3" t="n"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores DNA's role in transcription and translation. 
+It discusses how DNA variations affect phenotypes. 
+Cellular components are listed, including organelles and structures. 
+The process of protein generation is mentioned as complex. 
+Cell types, such as prokaryotic and eukaryotic cells, are referenced.</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -57306,7 +58210,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores DNA and its role in transcription and translation.
+It discusses how variations in DNA sequences produce different phenotypes.
+Population genetics studies genetic differences within and between populations.
+Evolutionary biology examines adaptation, speciation, and population structure.
+The study of evolution combines with genetics to understand changes in allele proportions over time.</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -57339,7 +58248,11 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers DNA, transcription, and translation.
+It explores variations in DNA sequences and their effects on phenotypes.
+Population genetics and evolutionary biology are also discussed.
+The role of natural selection and other mechanisms in evolution is examined.
+Evolutionary concepts are illustrated through simulation models and virtual experiments.</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -57372,7 +58285,11 @@
       <c r="E183" s="3" t="n"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Population genetics studies genetic differences within populations.
+It's a part of evolutionary biology, examining adaptation and speciation.
+The field combines evolutionary theory with genetics understanding.
+Simulations like the agent-based model help illustrate concepts.
+Evolution is defined as changes in allele proportions over time.</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -57405,7 +58322,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+Population genetics studies genetic differences within and between populations.
+It's a part of evolutionary biology, examining adaptation, speciation, and population structure.
+The text discusses Hardy-Weinberg theory and its assumptions, including small population, selection, mutation, and non-random mating.
+A simulation model is used to demonstrate microevolutionary processes, including genetic drift and natural selection.
+The model helps students understand complex concepts in evolutionary biology through virtual experiments.</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -57438,7 +58360,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses an agent-based population genetics simulation model.
+It explores microevolutionary processes, including natural selection and genetic drift.
+The model allows students to conduct virtual experiments and test hypotheses.
+It features tools to demonstrate Hardy-Weinberg theory and its assumptions.
+The simulation helps students understand evolutionary concepts through interactive and graphical results.</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -57471,7 +58398,12 @@
       <c r="E186" s="3" t="n"/>
       <c r="F186" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses an agent-based population genetics simulation model.
+It explores concepts like Hardy-Weinberg theory, natural selection, and genetic drift.
+The model simulates microevolutionary processes with factors like population size and mutation.
+Students can use the model to develop and test hypotheses through virtual experiments.
+The simulation helps illustrate challenging evolutionary concepts in a biologically realistic way.</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
@@ -57504,7 +58436,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses evolutionary theory and population genetics.
+It introduces an agent-based simulation model to study genetic drift and selection.
+The model explores how random events affect allele proportions in small populations.
+The text also references real-world experiments, such as John Endler's guppy study, to illustrate variations in physical characteristics.
+These concepts are used to investigate the influence of variables on evolutionary changes.</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
@@ -57537,7 +58474,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses population genetics simulation and evolutionary theory.
+It introduces an agent-based model to conduct virtual experiments on Hardy-Weinberg theory assumptions.
+A case study on guppies and their varying physical characteristics is presented.
+The Sexual Selection in Guppies virtual laboratory allows users to run simulations to determine variables influencing spot variation.
+The goal is to understand the factors responsible for trends in spot numbers over time.</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -57570,7 +58512,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses population genetics and evolutionary theory.
+It introduces an agent-based simulation model and a virtual lab on guppy experiments.
+The goal is to investigate variables influencing physical characteristics, such as spots in male guppies.
+Sexual selection and other factors like mutation and migration are explored.
+The text also touches on real-world examples, including lice resistance to shampoo chemicals.</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -57603,7 +58550,12 @@
       <c r="E190" s="3" t="n"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses evolutionary theory and population genetics.
+It explores natural selection and variation in species, such as guppies.
+Simulations and experiments are used to investigate factors influencing traits.
+Variables like environment, mutation, and selection are analyzed.
+The goal is to understand how these factors shape the evolution of species.</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
@@ -57636,7 +58588,11 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses population genetics simulations and evolutionary theory. 
+It explores natural selection through virtual experiments with bunnies. 
+Variables such as mutation, migration, and non-random mating are examined. 
+The text also touches on adaptation and advantageous traits in different environments. 
+Evolutionary changes, like fur color and tooth length, are used as examples.</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
@@ -57669,7 +58625,12 @@
       <c r="E192" s="3" t="n"/>
       <c r="F192" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text explores evolutionary theory and natural selection.
+It discusses physical characteristics and attraction in humans and animals.
+Virtual laboratory experiments with bunnies investigate environmental adaptations.
+The text also touches on the development of resistance in lice to shampoos.
+Evolutionary advantages and trait changes are key themes throughout.</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
@@ -57706,7 +58667,11 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores natural selection and evolution.
+It discusses bunnies adapting to environments through mutations.
+The connection between star lightness and age is also investigated.
+Resistant lice strains in the US are attributed to chemical shampoo use.
+Evolutionary advantages and trait changes are examined in various habitats.</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
@@ -57739,7 +58704,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores natural selection and evolution through examples with bunnies.
+It discusses adaptations such as fur color and teeth length in different environments.
+Two explanations are provided to explain these adaptations.
+The text also touches on the life cycle of stars and their connection to age and lightness.
+Finally, it introduces atoms as the basic units of matter and their importance for life processes.</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
@@ -57772,7 +58742,11 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores natural selection and evolution.
+It discusses the connection between stars' lightness and age.
+The topic then shifts to atoms, their importance, and structure.
+Investigations and worksheets are provided for further learning.
+The text concludes with a review of life processes and self-evaluation.</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -57805,7 +58779,11 @@
       <c r="E196" s="3" t="n"/>
       <c r="F196" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores the connection between stars and their ages. 
+It also discusses investigating the life of stars using worksheets.
+The topic then shifts to atoms, the basic units of matter.
+Atoms are crucial for life processes and evolution.
+The text concludes with a call for self-evaluation and review.</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -57838,7 +58816,12 @@
       <c r="E197" s="3" t="n"/>
       <c r="F197" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses investigating star life and atomic structure.
+It mentions using worksheets and apps to facilitate learning.
+Reflecting on time spent in different phases is also encouraged.
+The text then shifts to exploring atoms, their importance, and composition.
+The goal is to complete a tour of life processes and self-evaluate understanding.</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -57871,7 +58854,12 @@
       <c r="E198" s="3" t="n"/>
       <c r="F198" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses an Interactive Learning System (ILS) that tracks time spent on each phase.
+It provides tools to reflect on time management and phase switching.
+The system displays content from other apps and shows time spent on each activity.
+The topic shifts to atoms, their importance in life processes, and building atomic structures.
+The text concludes with a review and self-evaluation of the learning process.</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
@@ -57904,7 +58892,12 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses an Interactive Learning System (ILS) and its features.
+It tracks time spent on each phase and provides a chart for reflection.
+The ILS also explores scientific topics, such as atoms and life processes.
+A virtual laboratory on Sexual Selection in Guppies is introduced.
+Variables and their descriptions are provided for the virtual lab experiment.</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
@@ -57937,7 +58930,12 @@
       <c r="E200" s="3" t="n"/>
       <c r="F200" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers various topics including time management and phase tracking.
+It also touches on environmental changes and atomic structure.
+A tour of life processes is mentioned, with a call to review results.
+Sexual selection in guppies is another topic, with variables described.
+These themes seem unrelated, suggesting a collection of disparate ideas.</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
@@ -57974,7 +58972,12 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers various topics, including environmental changes and conservation. 
+It mentions a lake in Bolivia drying up due to environmental issues.
+A virtual laboratory on sexual selection in guppies is also discussed.
+Variables such as population size and predator numbers are considered.
+The text concludes with a prompt for self-evaluation and review.</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
@@ -58007,7 +59010,12 @@
       <c r="E202" s="3" t="n"/>
       <c r="F202" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses environmental changes and their impacts.
+Bolivia's second-largest lake is drying up, affecting Earth's water.
+A virtual lab on sexual selection in guppies is introduced.
+Variables such as population size and predator presence are considered.
+The text concludes with a prompt for self-evaluation.</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -58040,7 +59048,12 @@
       <c r="E203" s="3" t="n"/>
       <c r="F203" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses environmental changes, such as a drying lake in Bolivia.
+It touches on impacts on water and icebergs.
+A virtual laboratory on sexual selection in guppies is also mentioned.
+Variables like population size and predator numbers are considered.
+The text appears to be a mix of ecology and biology topics.</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
@@ -58073,7 +59086,11 @@
       <c r="E204" s="3" t="n"/>
       <c r="F204" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers climate trends and impacts on Earth. 
+It mentions temperature, carbon dioxide, and greenhouse gases. 
+A virtual lab on sexual selection in guppies is also discussed. 
+Variables such as population size and predator numbers are examined. 
+The text concludes with a call for self-evaluation and review.</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -58106,7 +59123,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text covers climate trends and impacts on Earth's water and ice. 
+It mentions historical temperature and greenhouse gas trends.
+A virtual lab on sexual selection in guppies is also described.
+Variables such as population size and predator numbers are discussed.
+Climate data visualization using graphs and plot menus is explained.</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
@@ -58139,7 +59161,12 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text discusses climate trends and impacts on Earth's water and ice. 
+It covers temperature, carbon dioxide, methane, and nitrous oxide levels.
+Historical data is explored over hundreds of thousands of years.
+Graphs are used to visualize the changing trends.
+The focus is on the last 5000 years, particularly the last 100 years.</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
@@ -58172,7 +59199,11 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text covers impacts of climate change on water and ice. 
+It explores historical climate trends over thousands of years. 
+Temperature, carbon dioxide, methane, and nitrous oxide levels are analyzed. 
+The relationship between climate change and greenhouse phenomena is discussed. 
+Climate trends are visualized through graphs and plots.</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -58209,7 +59240,11 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses climate change and its impacts.
+It explores historical climate trends over thousands of years.
+Key factors include temperature, carbon dioxide, methane, and nitrous oxide.
+The Greenhouse Effect is also examined in relation to climate change.
+Climate trends are visualized over the last 5000 years.</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
@@ -58242,7 +59277,12 @@
       <c r="E209" s="3" t="n"/>
       <c r="F209" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text explores historical climate trends over thousands of years.
+It covers temperature, carbon dioxide, methane, and nitrous oxide levels.
+Solar radiation's interaction with Earth's atmosphere causes global warming.
+Greenhouse gases like carbon dioxide contribute to the greenhouse effect.
+Climate change is linked to the greenhouse phenomenon.</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
@@ -58275,7 +59315,11 @@
       <c r="E210" s="3" t="n"/>
       <c r="F210" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores the interaction between solar radiation and the Earth's atmosphere.
+It discusses how greenhouse gases, such as carbon dioxide, affect the climate.
+The greenhouse effect and its impact on global warming are key topics.
+The role of atmospheric gases and clouds in climate change is also examined.
+The text aims to explain the scientific concepts of climate change.</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
@@ -58308,7 +59352,12 @@
       <c r="E211" s="3" t="n"/>
       <c r="F211" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text explores the interaction between solar radiation and the Earth's atmosphere, causing global warming.
+Greenhouse gases, such as carbon dioxide, play a significant role in the climate.
+The text also discusses the effects of clouds, glass panes, and atmospheric gases on the greenhouse effect.
+Simulations and experiments are used to understand and stabilize carbon output over time.
+The relationship between climate change and the greenhouse phenomenon is a central scientific concept.</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
@@ -58341,7 +59390,12 @@
       <c r="E212" s="3" t="n"/>
       <c r="F212" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text explores the impact of greenhouse gases on climate.
+It delves into the atmosphere's composition during the ice age and present day.
+The role of clouds, greenhouse gas concentration, and temperature changes are examined.
+The interaction between light and molecules is also discussed.
+The Greenhouse Effect and its relation to climate change are key themes.</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
@@ -58374,7 +59428,12 @@
       <c r="E213" s="3" t="n"/>
       <c r="F213" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text discusses climate change and carbon output.
+It explores strategies to stabilize carbon levels over 50 years.
+The role of greenhouse gases like CO2, methane, and nitrous oxide is examined.
+The interaction between IR photons and these gases is also studied.
+Climate change and the Greenhouse Effect are key scientific concepts covered.</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
@@ -58407,7 +59466,11 @@
       <c r="E214" s="3" t="n"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores the absorption of infrared radiation by CO2.
+It illustrates energy transfer to surrounding molecules, affecting temperature.
+The animation demonstrates vibrational modes of CO2 and temperature rise.
+Climate change and the greenhouse effect are key scientific concepts discussed.
+The relationship between greenhouse phenomena and climate change is examined.</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
@@ -58440,7 +59503,11 @@
       <c r="E215" s="3" t="n"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores ocean acidification and its impacts.
+It delves into climate change and the greenhouse effect.
+Greenhouse gases like CO2, N2O, and methane are discussed.
+The relationship between these gases and temperature is analyzed.
+Climate change concepts are examined through interactive models.</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
@@ -58473,7 +59540,11 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores ocean acidification and its impacts on sea life.
+It discusses climate change and the greenhouse effect.
+Up to 40% of manmade CO2 is captured by oceans, making them a significant carbon sink.
+However, this comes at a cost, as CO2 dissolves in water, increasing acidity.
+Ocean acidification affects marine life, particularly shell-forming organisms like sea urchin larvae.</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
@@ -58506,7 +59577,12 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text explores ocean acidification and its effects on sea life.
+It discusses the Greenhouse Effect and carbon sinks, including oceans.
+Up to 40% of manmade CO2 is captured by oceans, causing acidification.
+This acidification hinders carbonate formation and dissolves exoskeletons.
+The text also mentions interactive models and graph adjustments for climate variables.</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -58539,7 +59615,11 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores ocean acidification and its impacts on marine life.
+It discusses how oceans absorb CO2, becoming a significant carbon sink.
+However, this absorption comes with a cost, making the water more acidic.
+The chemistry of ocean acidification is explained through three chemical reactions.
+This affects the formation of carbonate compounds and can dissolve existing exoskeletons.</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -58572,7 +59652,11 @@
       <c r="E219" s="3" t="n"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores ocean acidification and its impacts on marine life. 
+Up to 40% of manmade CO2 is captured by oceans, rivers, and lakes. 
+This absorption changes water chemistry, making it more acidic. 
+Acidification hinders carbonate formation and can dissolve exoskeletons. 
+The text also discusses modeling climate variables like temperature and CO2 concentration.</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -58605,7 +59689,12 @@
       <c r="E220" s="3" t="n"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers ocean acidification, plate tectonics, and climate change.
+It explores the chemistry of ocean acidification and its impacts on sea life.
+Up to 40% of manmade CO2 is captured by oceans, causing acidification.
+This process affects marine ecosystems and can dissolve existing exoskeletons.
+The text also discusses modeling climate change using graphs and variables.</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -58638,7 +59727,12 @@
       <c r="E221" s="3" t="n"/>
       <c r="F221" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text covers plate tectonics, continental drift, and carbon capture.
+It explains how oceans absorb CO2, becoming more acidic in the process.
+This acidification affects marine life and carbonate formation.
+The text also includes instructions for graphing CO2 emissions and temperature changes.
+Key variables include CO2 production, maximum temperature, and climate variability.</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -58671,7 +59765,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses plate tectonics and continental drift.
+It mentions a documentary on the subject by Isaac Frame.
+The topic also covers climate change and CO2 emissions.
+Graphs are used to illustrate temperature, CO2 concentration, and emission rates.
+Geologists concluded that the Earth's lithosphere is broken into moving plates.</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -58704,7 +59803,12 @@
       <c r="E223" s="3" t="n"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The documentary explores plate tectonics and continental drift.
+It covers processes like subduction and transduction, explaining how continents formed.
+Greece's location on the tectonic plate map is also examined.
+The text also touches on climate change, CO2 emissions, and temperature variability.
+Plate tectonics reveals the Earth's lithosphere is broken into moving plates.</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -58737,7 +59841,12 @@
       <c r="E224" s="3" t="n"/>
       <c r="F224" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses tectonic plates and their motion.
+It mentions the division of the Earth's surface into plates, including Greece's location.
+The text also touches on climate change variables like CO2 emission rates and temperature.
+Geologists concluded that the Earth's lithosphere is broken into moving plates.
+This concept was established in the 1960s with around 12 large plates identified.</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
@@ -58774,7 +59883,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses tectonic plates and their movement.
+It mentions Greece's location on the map of tectonic plates.
+Earthquake activity and climate variability are also touched upon.
+The text references CO2 production, temperature, and emissions rates.
+Geologists' conclusions about the Earth's lithosphere are mentioned.</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
@@ -58807,7 +59921,12 @@
       <c r="E226" s="3" t="n"/>
       <c r="F226" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses tectonic plates and earthquake activity.
+It also touches on climate change and CO2 production.
+Geologists have identified 12 large moving plates in the Earth's lithosphere.
+These plates are responsible for earthquake activity, including the "Ring of Fire".
+The text combines geology and climate change topics.</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -58840,7 +59959,12 @@
       <c r="E227" s="3" t="n"/>
       <c r="F227" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses earthquake activity and data access.
+It also touches on climate change, CO2 production, and temperature variability.
+Geologists' findings on the Earth's lithosphere and moving plates are mentioned.
+The "Ring of Fire" and various tectonic plates are referenced.
+Earthquake and climate data are interconnected topics.</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -58873,7 +59997,12 @@
       <c r="E228" s="3" t="n"/>
       <c r="F228" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers earthquake data and climate change topics. 
+It mentions CO2 production, temperature, and climate variability.
+Geologists discovered the Earth's lithosphere is broken into moving plates.
+The "Ring of Fire" and various tectonic plates are mentioned.
+Earthquake and climate data are provided for analysis and self-assessment.</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
@@ -58906,7 +60035,12 @@
       <c r="E229" s="3" t="n"/>
       <c r="F229" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers earthquakes, climate data, and geology. 
+It mentions CO2 production, temperature, and climate variability.
+Geologists discovered the Earth's lithosphere is broken into moving plates.
+The text references the "Ring of Fire" and various tectonic plates.
+It appears to be a collection of notes on earth sciences and inquiry learning.</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
@@ -58939,7 +60073,12 @@
       <c r="E230" s="3" t="n"/>
       <c r="F230" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text covers various topics, including inquiry learning and Cymatics.
+Cymatics is the science of visualizing audio frequencies through music and science.
+Climate change is also discussed with statistics on CO2 production and temperature.
+Geology is mentioned, highlighting the Earth's lithosphere broken into moving plates.
+These topics seem unrelated, suggesting a collection of notes or resources.</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
@@ -58976,7 +60115,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text explores Cymatics, the science of visualizing audio frequencies.
+A video showcases enthusiastic individuals connecting music and science.
+The experiment uses a Tesla Coil and Plasma Ball to create visual effects.
+The text also briefly mentions plate tectonics and the Earth's lithosphere.
+It highlights an inspiring project that combines art and science.</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
@@ -59009,7 +60153,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text introduces Cymatics, the science of visualizing audio frequencies.
+A video showcases enthusiasts connecting music and science through innovative experiments.
+The experiments involve acoustics, electromagnetism, and waves, with some parts being real and others added for effect.
+The text warns against trying the experiments at home due to safety concerns.
+The topic will be explored further, starting from the basics of the scientific concepts involved.</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
@@ -59042,7 +60191,11 @@
       <c r="E233" s="3" t="n"/>
       <c r="F233" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores Cymatics, a science that visualizes audio frequencies. 
+It features a video showing music and science connection through experiments.
+These experiments involve sound waves, acoustics, and electromagnetism.
+They are presented in an innovative way, combining real experiments with special effects.
+The text warns against trying these experiments at home due to potential risks.</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
@@ -59075,7 +60228,11 @@
       <c r="E234" s="3" t="n"/>
       <c r="F234" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses sound waves and their properties. 
+It covers simple and complex sounds, wave forms, and frequencies. 
+Experiments with Tesla Coils and Plasma Balls are mentioned. 
+The text also touches on scientific concepts like acoustics and electromagnetism. 
+It highlights the innovative use of scientific facts in a video.</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
@@ -59108,7 +60265,12 @@
       <c r="E235" s="3" t="n"/>
       <c r="F235" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses sound and waves, covering topics like frequency and amplitude.
+It explains simple and complex sound waves, as well as transverse and longitudinal waves.
+Waves are defined by quantities such as wavelength, period, and velocity.
+These quantities are related to each other and affect the behavior of waves.
+The text also touches on scientific experiments and innovations related to acoustics and electromagnetism.</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
@@ -59141,7 +60303,12 @@
       <c r="E236" s="3" t="n"/>
       <c r="F236" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary of the text:
+The text discusses types of waves, including transverse and longitudinal waves.
+It covers wave properties such as amplitude, frequency, wavelength, and velocity.
+Mechanical waves are explored in detail, including reflection and superposition.
+Wave interference, including constructive and destructive interference, is also explained.
+The text combines scientific concepts with interactive simulations and experiments.</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
@@ -59174,7 +60341,12 @@
       <c r="E237" s="3" t="n"/>
       <c r="F237" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+Waves have properties like amplitude, frequency, wavelength, and velocity.
+These quantities are related to each other and affect wave behavior.
+Mechanical waves' velocity depends on their environment and wavelength.
+Wave phenomena include reflection, superposition, and interference.
+The text explores various scientific concepts related to acoustics and electromagnetism.</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
@@ -59207,7 +60379,12 @@
       <c r="E238" s="3" t="n"/>
       <c r="F238" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text explores mechanical waves and phenomena like reflection and superposition.
+It discusses wave interference, including constructive and destructive interference.
+The topics are related to acoustics, electromagnetism, and wave propagation.
+Experiments with sound waves and Ruben's Tube are mentioned as examples.
+The text aims to explain the science behind innovative experiments with waves.</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
@@ -59240,7 +60417,11 @@
       <c r="E239" s="3" t="n"/>
       <c r="F239" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores scientific phenomena used in innovative experiments. 
+It mentions Ruben's Tube and acoustic effects.
+Experiments involve acoustics, electromagnetism, and wave dynamics.
+Scientific facts are presented in an engaging and creative way.
+The video features real experiments and added visual effects.</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
@@ -59273,7 +60454,12 @@
       <c r="E240" s="3" t="n"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses Ruben's Tube and its creation.
+It involves scientific phenomena like acoustics and electromagnetism.
+Experiments with sound waves and fluid dynamics are showcased.
+The video features innovative uses of scientific facts and real experiments.
+The topic explores the intersection of sound, light, and physics.</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
@@ -59306,7 +60492,11 @@
       <c r="E241" s="3" t="n"/>
       <c r="F241" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses a video featuring innovative scientific experiments. 
+Experiments involve acoustics, electromagnetism, and waves.
+They include fluid dynamics and Tesla coils.
+Some parts are real, while others are added effects.
+The video showcases unique applications of scientific concepts.</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
@@ -59339,7 +60529,11 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses innovative scientific experiments with fluids and sound.
+It explores concepts related to acoustics, electromagnetism, and waves.
+Experiments include Ruben's Tube and Tesla coil demonstrations.
+These experiments are used to explain scientific facts in an engaging way.
+The text aims to educate on various scientific principles.</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
@@ -59372,7 +60566,11 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses scientific concepts related to acoustics and waves.
+Experiments are used to demonstrate innovative ideas and effects.
+Density is a key topic, explaining why objects sink or float.
+The text warns against attempting experiments at home.
+Scientific facts are presented in an engaging and educational way.</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
@@ -59405,7 +60603,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text explores concepts of sinking and floating.
+It introduces the concept of density and its relation to weight and size.
+Density is measured in grams per cubic centimeter, combining mass and volume.
+A higher density indicates that an object is heavier for its size.
+The text aims to help learners understand why objects sink or float based on their density.</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
@@ -59438,7 +60641,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses sinking and floating concepts.
+It introduces density as a key factor in determining if an object sinks or floats.
+Density is measured by weight (mass) and size (volume).
+Different materials have unique densities, affecting their buoyancy.
+Understanding density is crucial for designing good experiments.</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
@@ -59471,7 +60679,11 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text covers concepts of density and volume. 
+Density is measured in grams per cubic cm, indicating an object's weight and size. 
+A higher density means an object is heavier for its size. 
+The text also introduces experimentation and critical reflection. 
+It discusses designing good experiments, using an example of baking a cake.</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
@@ -59504,7 +60716,11 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses designing good experiments. 
+A good experiment involves changing one variable at a time. 
+This approach helps identify cause-and-effect relationships. 
+Changing multiple variables can lead to unclear results. 
+Only varying one thing at a time is key to a successful experiment.</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
@@ -59537,7 +60753,11 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses designing a good experiment by changing one variable at a time. 
+It uses baking a cake as an example to illustrate this concept.
+The goal is to identify cause-and-effect relationships.
+Changing multiple variables can lead to unclear results.
+A good experiment tests to falsify a hypothesis, not prove it right.</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
@@ -59570,7 +60790,11 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses the principles of designing a good experiment. 
+It emphasizes the importance of varying one thing at a time. 
+This approach helps to identify cause-and-effect relationships.
+A good experiment should test hypotheses, not prove them right.
+It applies these principles to evaluate experiments by Anna and Simon.</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
@@ -59603,7 +60827,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+The text discusses experimental design and the importance of testing hypotheses.
+It highlights common pitfalls, such as trying to prove oneself right.
+A key concept is "falsify," or testing if one is wrong.
+Anna's experiment is critiqued for its flaws in designing a good test.
+Good experimentation involves objective testing and variable manipulation.</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
@@ -59636,7 +60865,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text explores concepts of buoyancy and density.
+Anna conducts experiments changing mass, volume, and density.
+Her goal is to make objects float, but her experiment has flaws.
+Simon also explores buoyancy, believing heavy objects sink faster.
+The exercises aim to understand the relationship between density and buoyancy.</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
@@ -59669,7 +60903,11 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses concepts related to physics and experimentation.
+It touches on ideas about mass, volume, and density.
+A character named Simon conducts experiments to test his theory about sinking objects.
+His experiments involve changing the mass, volume, and density of objects.
+The text questions the validity of Simon's experimental approach.</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
@@ -59702,7 +60940,11 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses experiments on sinking objects and density.
+Simon tests how mass, volume, and density affect an object's ability to sink.
+He conducts three experiments with varying masses and volumes but constant density.
+The experiments are deemed not very good, prompting questions about their flaws.
+Improving the experiment design is suggested as a next step.</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
@@ -59735,7 +60977,11 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses experiments with density and buoyancy.
+It highlights flaws in previous experiments by others.
+A new investigation is proposed to explore what makes objects sink.
+Density is suspected as the key factor.
+The goal is to design better experiments to test this hypothesis.</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
@@ -59768,7 +61014,12 @@
       <c r="E255" s="3" t="n"/>
       <c r="F255" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses CERN and its collider.
+It introduces experiments on density and volume.
+The experiments have flaws, making them "not very good".
+Readers are prompted to design their own investigation.
+The goal is to explore what causes objects to sink or float based on density.</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
@@ -59801,7 +61052,12 @@
       <c r="E256" s="3" t="n"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses CERN and its purpose in nuclear research.
+It explains the structure of matter at smaller scales, from atoms to quarks.
+The Standard Model governs interactions between basic building blocks of matter.
+Experiments on density are presented, with flaws identified.
+The reader is invited to design their own investigation on object density.</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
@@ -59834,7 +61090,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses CERN, a European nuclear research organization.
+It introduces the concept of the Large Hadron Collider and its purpose.
+The Standard Model explains how matter interacts through fundamental forces.
+An experiment investigating object density and sinking is proposed.
+The text encourages readers to learn about CERN and conduct their own investigation.</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
@@ -59867,7 +61128,11 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses CERN and the Large Hadron Collider. 
+It explains the structure of matter and the Standard Model. 
+The text also introduces an experiment on density and object buoyancy. 
+Investigations and research are encouraged to understand physics concepts. 
+Key topics include particle physics, experimentation, and scientific inquiry.</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
@@ -59900,7 +61165,11 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses CERN and the Large Hadron Collider. 
+It explains the structure of matter and the Standard Model.
+The collider's purpose and main tasks are outlined.
+Potential applications in physics, biology, and medicine are explored.
+Risks and threats associated with the collider's work are also assessed.</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
@@ -59933,7 +61202,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses CERN and the Large Hadron Collider.
+It explains the structure of matter and the Standard Model.
+The collider's purpose and potential applications are explored.
+Risks and threats associated with the collider are also assessed.
+The text raises questions about the benefits and dangers of LHC-based research.</t>
         </is>
       </c>
     </row>
@@ -59961,7 +61235,12 @@
       <c r="E261" s="3" t="n"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief summary:
+CERN's Large Hadron Collider is explained through interactive models and animations.
+The Standard Model of physics governs the basic building blocks of matter.
+Research applications include physics, biology, chemistry, and medicine.
+Risks and threats associated with the collider are assessed.
+Investment in LHC-based research is considered amidst its 10-year lifespan.</t>
         </is>
       </c>
     </row>
@@ -59989,7 +61268,11 @@
       <c r="E262" s="3" t="n"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores the structure of matter at smaller scales.
+It introduces the Standard Model and fundamental forces governing interactions.
+The Large Hadron Collider (LHC) is discussed, including its operation and potential applications.
+Various "hats" represent different perspectives: optimistic (Yellow), critical (Black), and emotional (Red).
+The LHC's impact and future are considered, weighing risks and benefits.</t>
         </is>
       </c>
     </row>
@@ -60017,7 +61300,12 @@
       <c r="E263" s="3" t="n"/>
       <c r="F263" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses STEM education and research projects.
+Students investigate the Arctic Pole and climate change.
+They use various "hats" to approach problems, such as Green Hat for modification and Yellow Hat for optimism.
+Research topics include physics, biology, and the Large Hadron Collider.
+The goal is to promote interest in science, technology, engineering, and mathematics education.</t>
         </is>
       </c>
     </row>
@@ -60045,7 +61333,12 @@
       <c r="E264" s="3" t="n"/>
       <c r="F264" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text promotes STEM education, encouraging students to learn about science and climate change.
+Students investigate the Arctic Pole, its problems, and ways to prevent further climate change.
+The text also explores the applications of physics, biology, and chemistry in various fields.
+It discusses the Large Hadron Collider, its risks, and potential benefits.
+Overall, it aims to foster critical thinking and awareness about science and its implications.</t>
         </is>
       </c>
     </row>
@@ -60073,7 +61366,12 @@
       <c r="E265" s="3" t="n"/>
       <c r="F265" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a brief 5-line summary:
+The text promotes STEM education and encourages students to learn about the Arctic Pole.
+Students investigate climate changes and their consequences in the Arctic region.
+Objectives include learning about the Arctic Pole, understanding climate change, and finding prevention methods.
+The text also touches on critical thinking exercises using different colored hats to analyze problems.
+These exercises aim to develop research, risk assessment, and intuitive skills among students.</t>
         </is>
       </c>
     </row>
@@ -60101,7 +61399,11 @@
       <c r="E266" s="3" t="n"/>
       <c r="F266" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses critical thinking exercises using colored hats. 
+It involves analyzing information from a video and websites. 
+The colors represent different perspectives: white (facts), yellow (optimism), black (risks), and red (emotions). 
+These hats are used to evaluate topics like the Large Hadron Collider. 
+Critical thinking is applied to assess successes, risks, and emotions related to the topic.</t>
         </is>
       </c>
     </row>
@@ -60129,7 +61431,11 @@
       <c r="E267" s="3" t="n"/>
       <c r="F267" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses critical thinking exercises using different colored hats. 
+It covers research and analysis of successes and risks. 
+The Large Hadron Collider is used as a case study to assess benefits and threats. 
+Different perspectives, including optimistic and pessimistic views, are considered. 
+Critical thinking and evaluation of information are key themes.</t>
         </is>
       </c>
     </row>
@@ -60157,7 +61463,11 @@
       <c r="E268" s="3" t="n"/>
       <c r="F268" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text discusses critical thinking exercises using different colored hats. 
+Yellow hat focuses on successes and advantages.
+Black hat assesses risks and threats.
+Red hat considers emotions and intuition.
+The Large Hadron Collider is used as an example for these thought experiments.</t>
         </is>
       </c>
     </row>
@@ -60185,7 +61495,11 @@
       <c r="E269" s="3" t="n"/>
       <c r="F269" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>The text explores climate change and greenhouse gases.
+It discusses simulating the Greenhouse effect and atmospheric changes.
+The Large Hadron Collider is also mentioned, with its risks and benefits assessed.
+Applications of physics, biology, and chemistry are considered.
+The text invites experimentation and critical thinking about science and its implications.</t>
         </is>
       </c>
     </row>
@@ -60213,7 +61527,7 @@
       <c r="E270" s="3" t="n"/>
       <c r="F270" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text explores climate change and greenhouse effects through experiments and simulations. It discusses the impact of greenhouse gases on temperature and atmosphere. The text also touches on the applications of physics, biology, and chemistry in various fields. Additionally, it mentions the Large Hadron Collider and its potential risks and benefits. Overall, it covers science, technology, and environmental topics.</t>
         </is>
       </c>
     </row>
@@ -60241,7 +61555,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text covers various scientific topics, including climate change and greenhouse gases.
+It also touches on the Large Hadron Collider and its potential risks and benefits.
+Vaccinations are another topic, with discussions on herd immunity and disease prevention.
+The importance of high vaccination rates to protect vulnerable populations is highlighted.
+These topics are explored through experiments, simulations, and real-world examples.</t>
         </is>
       </c>
     </row>
@@ -60273,7 +61592,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses climate change and vaccinations.
+It explores the greenhouse effect and atmospheric gases.
+Vaccinations are also covered, including rotavirus and measles outbreaks.
+Herd immunity is mentioned as a key benefit of high vaccination rates.
+The text includes news articles and simulations related to these topics.</t>
         </is>
       </c>
     </row>
@@ -60305,7 +61629,11 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Vaccinations are increasingly available for various diseases. 
+Universal vaccination programs aim for high vaccination rates to protect all individuals.
+Herd immunity is achieved when a high percentage of the population is vaccinated.
+News articles highlight rotavirus vaccination results in India and a measles outbreak in New York.
+These examples illustrate the importance of vaccinations in preventing disease outbreaks.</t>
         </is>
       </c>
     </row>
@@ -60333,7 +61661,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses vaccinations and outbreaks.
+It mentions rotavirus and measles outbreaks in India and New York.
+The authors introduce an inquiry space on vaccines with limited immunity.
+They focus on the influenza vaccine, which doesn't provide lifelong immunity.
+The topic will explore a specific case related to the influenza vaccine.</t>
         </is>
       </c>
     </row>
@@ -60361,7 +61694,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief 5-line summary:
+The text discusses vaccination news and outbreaks.
+It mentions a measles outbreak in New York and rotavirus vaccination.
+The focus shifts to the influenza vaccine, which doesn't provide lifelong immunity.
+A specific case is examined: influenza vaccination for healthcare workers (HCW).
+This case highlights the impact of high influenza rates on hospital resources.</t>
         </is>
       </c>
     </row>
@@ -60393,7 +61731,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a brief summary:
+The text discusses vaccination news and outbreaks.
+It focuses on the influenza vaccine, which doesn't provide lifelong immunity.
+A specific case examines influenza vaccination for healthcare workers (HCW).
+In 2018, high influenza rates affected hospitals' resources and personnel.
+Hospitals were overwhelmed, with some treating patients in tents.</t>
         </is>
       </c>
     </row>
@@ -60421,7 +61764,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses recent outbreaks and vaccination news.
+It highlights the challenges faced during the 2017-2018 influenza season.
+Hospitals were overwhelmed, with some forced to postpone operations or close ERs.
+Influenza vaccinations are crucial, especially for healthcare workers.
+Vaccination of healthcare workers is a key topic due to their high risk of infection.</t>
         </is>
       </c>
     </row>
@@ -60449,7 +61797,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses various vaccination news and outbreaks.
+It highlights the challenges faced during the 2017-2018 influenza season.
+Influenza vaccinations are needed annually due to constantly changing viruses.
+Healthcare workers are at risk of contracting influenza, putting patients at greater risk.
+Vaccination for healthcare workers is a crucial topic to investigate and consider.</t>
         </is>
       </c>
     </row>
@@ -60477,7 +61830,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary of the text:
+The text discusses vaccination and prevention of diseases like rotavirus, measles, and influenza.
+Influenza vaccines must be given annually due to constantly changing virus types.
+Healthcare workers are at risk of contracting influenza, with 25% of hospital-infected patients dying.
+Vaccination of healthcare workers is a crucial topic, especially after seasons with high influenza rates.
+The debate centers around whether healthcare workers should get vaccinated for influenza every year.</t>
         </is>
       </c>
     </row>
@@ -60505,7 +61863,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+The text discusses vaccination news and outbreaks.
+It mentions rotavirus, measles, and influenza seasons.
+Healthcare workers' vaccination habits are questioned.
+Some workers claim vaccinations are ineffective due to past experiences.
+The text invites investigation into vaccine effectiveness.</t>
         </is>
       </c>
     </row>
@@ -60533,7 +61896,11 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>The text discusses vaccination news and influenza season updates. 
+It explores reasons healthcare workers decline flu vaccinations, including ineffective past vaccinations.
+A interactive graph is introduced to analyze vaccination effectiveness.
+Variables such as vaccination rates and illness percentages are considered.
+The goal is to investigate the benefits of influenza vaccination for healthcare workers.</t>
         </is>
       </c>
     </row>
@@ -60561,7 +61928,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Here is a 5-line summary:
+The text discusses vaccination news and outbreaks.
+It mentions rotavirus, measles, and influenza season updates.
+An interactive graph is introduced to investigate vaccination effects.
+The graph tracks variables such as vaccinated healthcare workers and influenza cases.
+The goal is to analyze the impact of vaccination on preventing illnesses.</t>
         </is>
       </c>
     </row>
@@ -60589,7 +61961,12 @@
       <c r="E283" s="3" t="n"/>
       <c r="F283" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+Measles outbreak in New York sparks investigation.
+Influenza season news requires analysis using interactive graphs.
+Variables include vaccination rates and illness cases among healthcare workers (HCW).
+Graphs track ILIs, influenza, and prevented cases based on vaccination rates.
+Investigation guidelines provide support for understanding the data.</t>
         </is>
       </c>
     </row>
@@ -60617,7 +61994,12 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>Here is a 5-line summary:
+A measles outbreak in New York and influenza season news are discussed.
+An interactive graph investigates identified cases and vaccination effectiveness.
+The graph tracks healthcare worker (HCW) vaccination rates and illness incidence.
+Variables include vaccination percentage, confirmed influenza, and prevented cases.
+Users can explore different scenarios by adjusting severity and vaccination quality.</t>
         </is>
       </c>
     </row>

--- a/Codebook.xlsx
+++ b/Codebook.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sabanov/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03A6A91B-C590-8148-B237-647538C0E41A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C436BD06-4394-D94F-922E-9311AC951249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17080" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11468" uniqueCount="915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11468" uniqueCount="914">
   <si>
     <t>This document was exported from Numbers. Each table was converted to an Excel worksheet. All other objects on each Numbers sheet were placed on separate worksheets. Please be aware that formula calculations may differ in Excel.</t>
   </si>
@@ -1989,12 +1989,6 @@
   </si>
   <si>
     <t>Summaries</t>
-  </si>
-  <si>
-    <t>The ILS content is based on the Kenyan Grade 10 curriculum. Images show various objects and their functions. The objects' roles are made possible by their materials, structures, and designs. These elements work together to create specific outcomes. This understanding is a fundamental concept in science and technology.</t>
-  </si>
-  <si>
-    <t>The content appears to be part of a Kenyan Grade 10 (Form 2) Integrated Learning System (ILS). It includes observations of images and a video. The task is likely to identify functions, roles, and underlying factors contributing to these roles in everyday life or nature. No specific details are provided about the images or video content. Further context is needed for an accurate summary.</t>
   </si>
   <si>
     <t>Here's a concise summary:
@@ -4220,6 +4214,9 @@
 The graph tracks healthcare worker (HCW) vaccination rates and illness incidence.
 Variables include vaccination percentage, confirmed influenza, and prevented cases.
 Users can explore different scenarios by adjusting severity and vaccination quality.</t>
+  </si>
+  <si>
+    <t>There is no previous content.</t>
   </si>
 </sst>
 </file>
@@ -4512,11 +4509,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5685,11 +5682,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4" ht="0" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B3" s="35" t="s">
+      <c r="B3" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="36"/>
-      <c r="D3" s="36"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
     </row>
     <row r="7" spans="2:4" ht="19" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
@@ -37051,7 +37048,7 @@
       <c r="E1" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="37" t="s">
+      <c r="F1" s="35" t="s">
         <v>631</v>
       </c>
       <c r="G1" s="25" t="s">
@@ -37109,7 +37106,7 @@
         <v>57</v>
       </c>
       <c r="F2" s="31" t="s">
-        <v>632</v>
+        <v>913</v>
       </c>
       <c r="G2" s="33"/>
       <c r="H2" s="31" t="s">
@@ -37141,8 +37138,8 @@
       <c r="E3" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="F3" s="32" t="s">
-        <v>633</v>
+      <c r="F3" s="31" t="s">
+        <v>913</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="32" t="s">
@@ -37175,7 +37172,7 @@
       </c>
       <c r="E4" s="29"/>
       <c r="F4" s="34" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="G4" s="7"/>
       <c r="H4" s="32" t="s">
@@ -37208,7 +37205,7 @@
         <v>66</v>
       </c>
       <c r="F5" s="34" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G5" s="7"/>
       <c r="H5" s="32" t="s">
@@ -37241,7 +37238,7 @@
         <v>69</v>
       </c>
       <c r="F6" s="34" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G6" s="7"/>
       <c r="H6" s="32" t="s">
@@ -37274,7 +37271,7 @@
         <v>71</v>
       </c>
       <c r="F7" s="34" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G7" s="7"/>
       <c r="H7" s="32" t="s">
@@ -37307,7 +37304,7 @@
         <v>73</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G8" s="7"/>
       <c r="H8" s="32" t="s">
@@ -37340,7 +37337,7 @@
       </c>
       <c r="E9" s="29"/>
       <c r="F9" s="34" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="G9" s="7"/>
       <c r="H9" s="32" t="s">
@@ -37373,7 +37370,7 @@
       </c>
       <c r="E10" s="29"/>
       <c r="F10" s="34" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="G10" s="7"/>
       <c r="H10" s="32" t="s">
@@ -37406,7 +37403,7 @@
       </c>
       <c r="E11" s="29"/>
       <c r="F11" s="34" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G11" s="7"/>
       <c r="H11" s="32" t="s">
@@ -37439,7 +37436,7 @@
       </c>
       <c r="E12" s="29"/>
       <c r="F12" s="34" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G12" s="7"/>
       <c r="H12" s="32" t="s">
@@ -37472,7 +37469,7 @@
       </c>
       <c r="E13" s="29"/>
       <c r="F13" s="34" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G13" s="7"/>
       <c r="H13" s="32" t="s">
@@ -37505,7 +37502,7 @@
       </c>
       <c r="E14" s="29"/>
       <c r="F14" s="34" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G14" s="7"/>
       <c r="H14" s="32" t="s">
@@ -37538,7 +37535,7 @@
       </c>
       <c r="E15" s="29"/>
       <c r="F15" s="34" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G15" s="7"/>
       <c r="H15" s="32" t="s">
@@ -37571,7 +37568,7 @@
       </c>
       <c r="E16" s="29"/>
       <c r="F16" s="34" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="G16" s="7"/>
       <c r="H16" s="32" t="s">
@@ -37604,7 +37601,7 @@
       </c>
       <c r="E17" s="29"/>
       <c r="F17" s="34" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="G17" s="7"/>
       <c r="H17" s="32" t="s">
@@ -37637,7 +37634,7 @@
       </c>
       <c r="E18" s="29"/>
       <c r="F18" s="34" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="G18" s="7"/>
       <c r="H18" s="32" t="s">
@@ -37670,7 +37667,7 @@
         <v>96</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="G19" s="7"/>
       <c r="H19" s="32" t="s">
@@ -37703,7 +37700,7 @@
         <v>98</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="G20" s="7"/>
       <c r="H20" s="32" t="s">
@@ -37736,7 +37733,7 @@
         <v>100</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="G21" s="7"/>
       <c r="H21" s="32" t="s">
@@ -37769,7 +37766,7 @@
       </c>
       <c r="E22" s="29"/>
       <c r="F22" s="34" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="G22" s="7"/>
       <c r="H22" s="32" t="s">
@@ -37802,7 +37799,7 @@
         <v>104</v>
       </c>
       <c r="F23" s="34" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="G23" s="7"/>
       <c r="H23" s="32" t="s">
@@ -37835,7 +37832,7 @@
         <v>106</v>
       </c>
       <c r="F24" s="34" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="G24" s="7"/>
       <c r="H24" s="32" t="s">
@@ -37868,7 +37865,7 @@
         <v>109</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="G25" s="7"/>
       <c r="H25" s="32" t="s">
@@ -37901,7 +37898,7 @@
         <v>111</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="G26" s="7"/>
       <c r="H26" s="32" t="s">
@@ -37934,7 +37931,7 @@
       </c>
       <c r="E27" s="29"/>
       <c r="F27" s="34" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="G27" s="7"/>
       <c r="H27" s="32" t="s">
@@ -37967,7 +37964,7 @@
       </c>
       <c r="E28" s="29"/>
       <c r="F28" s="34" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="G28" s="7"/>
       <c r="H28" s="32" t="s">
@@ -38000,7 +37997,7 @@
       </c>
       <c r="E29" s="29"/>
       <c r="F29" s="34" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="G29" s="7"/>
       <c r="H29" s="32" t="s">
@@ -38033,7 +38030,7 @@
       </c>
       <c r="E30" s="29"/>
       <c r="F30" s="34" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="G30" s="7"/>
       <c r="H30" s="32" t="s">
@@ -38066,7 +38063,7 @@
         <v>122</v>
       </c>
       <c r="F31" s="34" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="G31" s="7"/>
       <c r="H31" s="32" t="s">
@@ -38099,7 +38096,7 @@
         <v>124</v>
       </c>
       <c r="F32" s="34" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G32" s="7"/>
       <c r="H32" s="32" t="s">
@@ -38132,7 +38129,7 @@
         <v>126</v>
       </c>
       <c r="F33" s="34" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="G33" s="7"/>
       <c r="H33" s="32" t="s">
@@ -38165,7 +38162,7 @@
         <v>127</v>
       </c>
       <c r="F34" s="34" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="G34" s="7"/>
       <c r="H34" s="32" t="s">
@@ -38198,7 +38195,7 @@
         <v>129</v>
       </c>
       <c r="F35" s="34" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="G35" s="7"/>
       <c r="H35" s="32" t="s">
@@ -38231,7 +38228,7 @@
         <v>131</v>
       </c>
       <c r="F36" s="34" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="G36" s="7"/>
       <c r="H36" s="32" t="s">
@@ -38264,7 +38261,7 @@
       </c>
       <c r="E37" s="29"/>
       <c r="F37" s="34" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="G37" s="7"/>
       <c r="H37" s="32" t="s">
@@ -38297,7 +38294,7 @@
         <v>134</v>
       </c>
       <c r="F38" s="34" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G38" s="7"/>
       <c r="H38" s="32" t="s">
@@ -38330,7 +38327,7 @@
         <v>136</v>
       </c>
       <c r="F39" s="34" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="G39" s="7"/>
       <c r="H39" s="32" t="s">
@@ -38363,7 +38360,7 @@
         <v>139</v>
       </c>
       <c r="F40" s="34" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="G40" s="7"/>
       <c r="H40" s="32" t="s">
@@ -38396,7 +38393,7 @@
         <v>141</v>
       </c>
       <c r="F41" s="34" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="G41" s="7"/>
       <c r="H41" s="32" t="s">
@@ -38429,7 +38426,7 @@
         <v>143</v>
       </c>
       <c r="F42" s="34" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="G42" s="7"/>
       <c r="H42" s="32" t="s">
@@ -38462,7 +38459,7 @@
       </c>
       <c r="E43" s="29"/>
       <c r="F43" s="34" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="G43" s="7"/>
       <c r="H43" s="32" t="s">
@@ -38495,7 +38492,7 @@
       </c>
       <c r="E44" s="29"/>
       <c r="F44" s="34" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="G44" s="7"/>
       <c r="H44" s="32" t="s">
@@ -38528,7 +38525,7 @@
         <v>149</v>
       </c>
       <c r="F45" s="34" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="G45" s="7"/>
       <c r="H45" s="32" t="s">
@@ -38561,7 +38558,7 @@
       </c>
       <c r="E46" s="29"/>
       <c r="F46" s="34" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="32" t="s">
@@ -38594,7 +38591,7 @@
       </c>
       <c r="E47" s="29"/>
       <c r="F47" s="34" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="G47" s="7"/>
       <c r="H47" s="32" t="s">
@@ -38627,7 +38624,7 @@
         <v>156</v>
       </c>
       <c r="F48" s="34" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="G48" s="7"/>
       <c r="H48" s="32" t="s">
@@ -38660,7 +38657,7 @@
         <v>158</v>
       </c>
       <c r="F49" s="34" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="G49" s="7"/>
       <c r="H49" s="32" t="s">
@@ -38693,7 +38690,7 @@
         <v>160</v>
       </c>
       <c r="F50" s="34" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="G50" s="7"/>
       <c r="H50" s="32" t="s">
@@ -38726,7 +38723,7 @@
         <v>162</v>
       </c>
       <c r="F51" s="34" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="G51" s="7"/>
       <c r="H51" s="32" t="s">
@@ -38759,7 +38756,7 @@
         <v>164</v>
       </c>
       <c r="F52" s="34" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="G52" s="7"/>
       <c r="H52" s="32" t="s">
@@ -38792,7 +38789,7 @@
       </c>
       <c r="E53" s="29"/>
       <c r="F53" s="34" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G53" s="7"/>
       <c r="H53" s="32" t="s">
@@ -38825,7 +38822,7 @@
       </c>
       <c r="E54" s="29"/>
       <c r="F54" s="34" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="G54" s="7"/>
       <c r="H54" s="32" t="s">
@@ -38858,7 +38855,7 @@
         <v>169</v>
       </c>
       <c r="F55" s="34" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G55" s="7"/>
       <c r="H55" s="32" t="s">
@@ -38893,7 +38890,7 @@
         <v>173</v>
       </c>
       <c r="F56" s="34" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="G56" s="7"/>
       <c r="H56" s="32" t="s">
@@ -38928,7 +38925,7 @@
         <v>175</v>
       </c>
       <c r="F57" s="34" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="G57" s="7"/>
       <c r="H57" s="32" t="s">
@@ -38961,7 +38958,7 @@
       </c>
       <c r="E58" s="29"/>
       <c r="F58" s="34" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="G58" s="7"/>
       <c r="H58" s="32" t="s">
@@ -38996,7 +38993,7 @@
         <v>180</v>
       </c>
       <c r="F59" s="34" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="G59" s="7"/>
       <c r="H59" s="32" t="s">
@@ -39029,7 +39026,7 @@
       </c>
       <c r="E60" s="29"/>
       <c r="F60" s="34" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="G60" s="7"/>
       <c r="H60" s="32" t="s">
@@ -39064,7 +39061,7 @@
         <v>185</v>
       </c>
       <c r="F61" s="34" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G61" s="7"/>
       <c r="H61" s="32" t="s">
@@ -39099,7 +39096,7 @@
         <v>187</v>
       </c>
       <c r="F62" s="34" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G62" s="7"/>
       <c r="H62" s="32" t="s">
@@ -39134,7 +39131,7 @@
         <v>185</v>
       </c>
       <c r="F63" s="34" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="G63" s="7"/>
       <c r="H63" s="32" t="s">
@@ -39169,7 +39166,7 @@
         <v>188</v>
       </c>
       <c r="F64" s="34" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="G64" s="7"/>
       <c r="H64" s="32" t="s">
@@ -39204,7 +39201,7 @@
         <v>185</v>
       </c>
       <c r="F65" s="34" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G65" s="7"/>
       <c r="H65" s="32" t="s">
@@ -39237,7 +39234,7 @@
       </c>
       <c r="E66" s="29"/>
       <c r="F66" s="34" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="G66" s="7"/>
       <c r="H66" s="32" t="s">
@@ -39270,7 +39267,7 @@
       </c>
       <c r="E67" s="29"/>
       <c r="F67" s="34" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="G67" s="7"/>
       <c r="H67" s="32" t="s">
@@ -39303,7 +39300,7 @@
       </c>
       <c r="E68" s="29"/>
       <c r="F68" s="34" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="G68" s="7"/>
       <c r="H68" s="32" t="s">
@@ -39336,7 +39333,7 @@
         <v>197</v>
       </c>
       <c r="F69" s="34" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G69" s="7"/>
       <c r="H69" s="32" t="s">
@@ -39369,7 +39366,7 @@
         <v>199</v>
       </c>
       <c r="F70" s="34" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="G70" s="7"/>
       <c r="H70" s="32" t="s">
@@ -39402,7 +39399,7 @@
         <v>201</v>
       </c>
       <c r="F71" s="34" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="G71" s="7"/>
       <c r="H71" s="32" t="s">
@@ -39435,7 +39432,7 @@
       </c>
       <c r="E72" s="29"/>
       <c r="F72" s="34" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="G72" s="7"/>
       <c r="H72" s="32" t="s">
@@ -39468,7 +39465,7 @@
         <v>205</v>
       </c>
       <c r="F73" s="34" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="G73" s="7"/>
       <c r="H73" s="32" t="s">
@@ -39501,7 +39498,7 @@
         <v>208</v>
       </c>
       <c r="F74" s="34" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="G74" s="7"/>
       <c r="H74" s="32" t="s">
@@ -39534,7 +39531,7 @@
         <v>210</v>
       </c>
       <c r="F75" s="34" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G75" s="7"/>
       <c r="H75" s="32" t="s">
@@ -39567,7 +39564,7 @@
       </c>
       <c r="E76" s="29"/>
       <c r="F76" s="34" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="G76" s="7"/>
       <c r="H76" s="32" t="s">
@@ -39600,7 +39597,7 @@
       </c>
       <c r="E77" s="29"/>
       <c r="F77" s="34" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="G77" s="7"/>
       <c r="H77" s="32" t="s">
@@ -39633,7 +39630,7 @@
       </c>
       <c r="E78" s="29"/>
       <c r="F78" s="34" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="G78" s="7"/>
       <c r="H78" s="32" t="s">
@@ -39666,7 +39663,7 @@
       </c>
       <c r="E79" s="29"/>
       <c r="F79" s="34" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G79" s="7"/>
       <c r="H79" s="32" t="s">
@@ -39699,7 +39696,7 @@
         <v>217</v>
       </c>
       <c r="F80" s="34" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="G80" s="7"/>
       <c r="H80" s="32" t="s">
@@ -39732,7 +39729,7 @@
       </c>
       <c r="E81" s="29"/>
       <c r="F81" s="34" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G81" s="7"/>
       <c r="H81" s="32" t="s">
@@ -39765,7 +39762,7 @@
         <v>222</v>
       </c>
       <c r="F82" s="34" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="G82" s="7"/>
       <c r="H82" s="32" t="s">
@@ -39798,7 +39795,7 @@
       </c>
       <c r="E83" s="29"/>
       <c r="F83" s="34" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="G83" s="7"/>
       <c r="H83" s="32" t="s">
@@ -39831,7 +39828,7 @@
       </c>
       <c r="E84" s="29"/>
       <c r="F84" s="34" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G84" s="7"/>
       <c r="H84" s="32" t="s">
@@ -39864,7 +39861,7 @@
       </c>
       <c r="E85" s="29"/>
       <c r="F85" s="34" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="G85" s="7"/>
       <c r="H85" s="32" t="s">
@@ -39897,7 +39894,7 @@
         <v>230</v>
       </c>
       <c r="F86" s="34" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="G86" s="7"/>
       <c r="H86" s="32" t="s">
@@ -39930,7 +39927,7 @@
         <v>232</v>
       </c>
       <c r="F87" s="34" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="G87" s="7"/>
       <c r="H87" s="32" t="s">
@@ -39963,7 +39960,7 @@
         <v>234</v>
       </c>
       <c r="F88" s="34" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="G88" s="7"/>
       <c r="H88" s="32" t="s">
@@ -39996,7 +39993,7 @@
       </c>
       <c r="E89" s="29"/>
       <c r="F89" s="34" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="G89" s="7"/>
       <c r="H89" s="32" t="s">
@@ -40029,7 +40026,7 @@
         <v>239</v>
       </c>
       <c r="F90" s="34" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G90" s="7"/>
       <c r="H90" s="32" t="s">
@@ -40062,7 +40059,7 @@
         <v>241</v>
       </c>
       <c r="F91" s="34" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="G91" s="7"/>
       <c r="H91" s="32" t="s">
@@ -40095,7 +40092,7 @@
       </c>
       <c r="E92" s="29"/>
       <c r="F92" s="34" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="G92" s="7"/>
       <c r="H92" s="32" t="s">
@@ -40128,7 +40125,7 @@
         <v>246</v>
       </c>
       <c r="F93" s="34" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G93" s="7"/>
       <c r="H93" s="32" t="s">
@@ -40161,7 +40158,7 @@
       </c>
       <c r="E94" s="29"/>
       <c r="F94" s="34" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G94" s="7"/>
       <c r="H94" s="32" t="s">
@@ -40194,7 +40191,7 @@
         <v>250</v>
       </c>
       <c r="F95" s="34" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="G95" s="7"/>
       <c r="H95" s="32" t="s">
@@ -40227,7 +40224,7 @@
         <v>252</v>
       </c>
       <c r="F96" s="34" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G96" s="7"/>
       <c r="H96" s="32" t="s">
@@ -40260,7 +40257,7 @@
         <v>254</v>
       </c>
       <c r="F97" s="34" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="G97" s="7"/>
       <c r="H97" s="32" t="s">
@@ -40293,7 +40290,7 @@
         <v>256</v>
       </c>
       <c r="F98" s="34" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="G98" s="7"/>
       <c r="H98" s="32" t="s">
@@ -40326,7 +40323,7 @@
         <v>258</v>
       </c>
       <c r="F99" s="34" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="G99" s="7"/>
       <c r="H99" s="32" t="s">
@@ -40359,7 +40356,7 @@
       </c>
       <c r="E100" s="29"/>
       <c r="F100" s="34" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="G100" s="7"/>
       <c r="H100" s="32" t="s">
@@ -40392,7 +40389,7 @@
         <v>261</v>
       </c>
       <c r="F101" s="34" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="G101" s="7"/>
       <c r="H101" s="32" t="s">
@@ -40425,7 +40422,7 @@
       </c>
       <c r="E102" s="29"/>
       <c r="F102" s="34" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="G102" s="7"/>
       <c r="H102" s="32" t="s">
@@ -40458,7 +40455,7 @@
       </c>
       <c r="E103" s="29"/>
       <c r="F103" s="34" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G103" s="7"/>
       <c r="H103" s="32" t="s">
@@ -40491,7 +40488,7 @@
       </c>
       <c r="E104" s="29"/>
       <c r="F104" s="34" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="G104" s="7"/>
       <c r="H104" s="32" t="s">
@@ -40524,7 +40521,7 @@
       </c>
       <c r="E105" s="29"/>
       <c r="F105" s="34" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="G105" s="7"/>
       <c r="H105" s="32" t="s">
@@ -40557,7 +40554,7 @@
       </c>
       <c r="E106" s="29"/>
       <c r="F106" s="34" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="G106" s="7"/>
       <c r="H106" s="32" t="s">
@@ -40590,7 +40587,7 @@
       </c>
       <c r="E107" s="29"/>
       <c r="F107" s="34" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="G107" s="7"/>
       <c r="H107" s="32" t="s">
@@ -40623,7 +40620,7 @@
       </c>
       <c r="E108" s="29"/>
       <c r="F108" s="34" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="G108" s="7"/>
       <c r="H108" s="32" t="s">
@@ -40656,7 +40653,7 @@
       </c>
       <c r="E109" s="29"/>
       <c r="F109" s="34" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="G109" s="7"/>
       <c r="H109" s="32" t="s">
@@ -40689,7 +40686,7 @@
       </c>
       <c r="E110" s="29"/>
       <c r="F110" s="34" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="G110" s="7"/>
       <c r="H110" s="32" t="s">
@@ -40722,7 +40719,7 @@
         <v>285</v>
       </c>
       <c r="F111" s="34" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G111" s="7"/>
       <c r="H111" s="32" t="s">
@@ -40755,7 +40752,7 @@
       </c>
       <c r="E112" s="29"/>
       <c r="F112" s="34" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G112" s="7"/>
       <c r="H112" s="32" t="s">
@@ -40788,7 +40785,7 @@
       </c>
       <c r="E113" s="29"/>
       <c r="F113" s="34" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="G113" s="7"/>
       <c r="H113" s="32" t="s">
@@ -40821,7 +40818,7 @@
       </c>
       <c r="E114" s="29"/>
       <c r="F114" s="34" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="G114" s="7"/>
       <c r="H114" s="32" t="s">
@@ -40854,7 +40851,7 @@
         <v>294</v>
       </c>
       <c r="F115" s="34" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="G115" s="7"/>
       <c r="H115" s="32" t="s">
@@ -40887,7 +40884,7 @@
       </c>
       <c r="E116" s="29"/>
       <c r="F116" s="34" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G116" s="7"/>
       <c r="H116" s="32" t="s">
@@ -40920,7 +40917,7 @@
       </c>
       <c r="E117" s="29"/>
       <c r="F117" s="34" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G117" s="7"/>
       <c r="H117" s="32" t="s">
@@ -40953,7 +40950,7 @@
         <v>300</v>
       </c>
       <c r="F118" s="34" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G118" s="7"/>
       <c r="H118" s="32" t="s">
@@ -40986,7 +40983,7 @@
         <v>302</v>
       </c>
       <c r="F119" s="34" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="G119" s="7"/>
       <c r="H119" s="32" t="s">
@@ -41019,7 +41016,7 @@
         <v>304</v>
       </c>
       <c r="F120" s="34" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="G120" s="7"/>
       <c r="H120" s="32" t="s">
@@ -41052,7 +41049,7 @@
       </c>
       <c r="E121" s="29"/>
       <c r="F121" s="34" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G121" s="7"/>
       <c r="H121" s="32" t="s">
@@ -41085,7 +41082,7 @@
       </c>
       <c r="E122" s="29"/>
       <c r="F122" s="34" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="G122" s="7"/>
       <c r="H122" s="32" t="s">
@@ -41118,7 +41115,7 @@
       </c>
       <c r="E123" s="29"/>
       <c r="F123" s="34" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="G123" s="7"/>
       <c r="H123" s="32" t="s">
@@ -41151,7 +41148,7 @@
       </c>
       <c r="E124" s="29"/>
       <c r="F124" s="34" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="G124" s="7"/>
       <c r="H124" s="32" t="s">
@@ -41184,7 +41181,7 @@
       </c>
       <c r="E125" s="29"/>
       <c r="F125" s="34" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G125" s="7"/>
       <c r="H125" s="32" t="s">
@@ -41217,7 +41214,7 @@
       </c>
       <c r="E126" s="29"/>
       <c r="F126" s="34" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="G126" s="7"/>
       <c r="H126" s="32" t="s">
@@ -41250,7 +41247,7 @@
         <v>318</v>
       </c>
       <c r="F127" s="34" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="G127" s="7"/>
       <c r="H127" s="32" t="s">
@@ -41283,7 +41280,7 @@
       </c>
       <c r="E128" s="29"/>
       <c r="F128" s="34" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="G128" s="7"/>
       <c r="H128" s="32" t="s">
@@ -41316,7 +41313,7 @@
       </c>
       <c r="E129" s="29"/>
       <c r="F129" s="34" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="G129" s="7"/>
       <c r="H129" s="32" t="s">
@@ -41349,7 +41346,7 @@
       </c>
       <c r="E130" s="29"/>
       <c r="F130" s="34" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="G130" s="7"/>
       <c r="H130" s="32" t="s">
@@ -41382,7 +41379,7 @@
       </c>
       <c r="E131" s="29"/>
       <c r="F131" s="34" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="G131" s="7"/>
       <c r="H131" s="32" t="s">
@@ -41415,7 +41412,7 @@
       </c>
       <c r="E132" s="29"/>
       <c r="F132" s="34" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="G132" s="7"/>
       <c r="H132" s="32" t="s">
@@ -41448,7 +41445,7 @@
       </c>
       <c r="E133" s="29"/>
       <c r="F133" s="34" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="G133" s="7"/>
       <c r="H133" s="32" t="s">
@@ -41481,7 +41478,7 @@
       </c>
       <c r="E134" s="29"/>
       <c r="F134" s="34" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="G134" s="7"/>
       <c r="H134" s="32" t="s">
@@ -41514,7 +41511,7 @@
       </c>
       <c r="E135" s="29"/>
       <c r="F135" s="34" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="G135" s="7"/>
       <c r="H135" s="32" t="s">
@@ -41547,7 +41544,7 @@
       </c>
       <c r="E136" s="29"/>
       <c r="F136" s="34" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="G136" s="7"/>
       <c r="H136" s="32" t="s">
@@ -41580,7 +41577,7 @@
         <v>337</v>
       </c>
       <c r="F137" s="34" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G137" s="7"/>
       <c r="H137" s="32" t="s">
@@ -41613,7 +41610,7 @@
         <v>339</v>
       </c>
       <c r="F138" s="34" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="G138" s="7"/>
       <c r="H138" s="32" t="s">
@@ -41646,7 +41643,7 @@
         <v>341</v>
       </c>
       <c r="F139" s="34" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="G139" s="7"/>
       <c r="H139" s="32" t="s">
@@ -41679,7 +41676,7 @@
         <v>343</v>
       </c>
       <c r="F140" s="34" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="G140" s="7"/>
       <c r="H140" s="32" t="s">
@@ -41712,7 +41709,7 @@
         <v>344</v>
       </c>
       <c r="F141" s="34" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="G141" s="7"/>
       <c r="H141" s="32" t="s">
@@ -41747,7 +41744,7 @@
         <v>348</v>
       </c>
       <c r="F142" s="34" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="G142" s="7"/>
       <c r="H142" s="32" t="s">
@@ -41780,7 +41777,7 @@
       </c>
       <c r="E143" s="29"/>
       <c r="F143" s="34" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G143" s="7"/>
       <c r="H143" s="32" t="s">
@@ -41813,7 +41810,7 @@
       </c>
       <c r="E144" s="29"/>
       <c r="F144" s="34" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="G144" s="7"/>
       <c r="H144" s="32" t="s">
@@ -41846,7 +41843,7 @@
         <v>355</v>
       </c>
       <c r="F145" s="34" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="G145" s="7"/>
       <c r="H145" s="32" t="s">
@@ -41879,7 +41876,7 @@
       </c>
       <c r="E146" s="29"/>
       <c r="F146" s="34" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="G146" s="7"/>
       <c r="H146" s="32" t="s">
@@ -41912,7 +41909,7 @@
         <v>359</v>
       </c>
       <c r="F147" s="34" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="G147" s="7"/>
       <c r="H147" s="32" t="s">
@@ -41945,7 +41942,7 @@
         <v>361</v>
       </c>
       <c r="F148" s="34" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="G148" s="7"/>
       <c r="H148" s="32" t="s">
@@ -41978,7 +41975,7 @@
         <v>363</v>
       </c>
       <c r="F149" s="34" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="G149" s="7"/>
       <c r="H149" s="32" t="s">
@@ -42011,7 +42008,7 @@
         <v>364</v>
       </c>
       <c r="F150" s="34" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="G150" s="7"/>
       <c r="H150" s="32" t="s">
@@ -42044,7 +42041,7 @@
       </c>
       <c r="E151" s="29"/>
       <c r="F151" s="34" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G151" s="7"/>
       <c r="H151" s="32" t="s">
@@ -42077,7 +42074,7 @@
       </c>
       <c r="E152" s="29"/>
       <c r="F152" s="34" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="G152" s="7"/>
       <c r="H152" s="32" t="s">
@@ -42110,7 +42107,7 @@
       </c>
       <c r="E153" s="29"/>
       <c r="F153" s="34" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G153" s="7"/>
       <c r="H153" s="32" t="s">
@@ -42143,7 +42140,7 @@
         <v>371</v>
       </c>
       <c r="F154" s="34" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="G154" s="7"/>
       <c r="H154" s="32" t="s">
@@ -42176,7 +42173,7 @@
         <v>373</v>
       </c>
       <c r="F155" s="34" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="G155" s="7"/>
       <c r="H155" s="32" t="s">
@@ -42209,7 +42206,7 @@
       </c>
       <c r="E156" s="29"/>
       <c r="F156" s="34" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="G156" s="7"/>
       <c r="H156" s="32" t="s">
@@ -42242,7 +42239,7 @@
         <v>378</v>
       </c>
       <c r="F157" s="34" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="G157" s="7"/>
       <c r="H157" s="32" t="s">
@@ -42275,7 +42272,7 @@
       </c>
       <c r="E158" s="29"/>
       <c r="F158" s="34" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G158" s="7"/>
       <c r="H158" s="32" t="s">
@@ -42308,7 +42305,7 @@
         <v>382</v>
       </c>
       <c r="F159" s="34" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="G159" s="7"/>
       <c r="H159" s="32" t="s">
@@ -42341,7 +42338,7 @@
         <v>384</v>
       </c>
       <c r="F160" s="34" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="G160" s="7"/>
       <c r="H160" s="32" t="s">
@@ -42374,7 +42371,7 @@
         <v>386</v>
       </c>
       <c r="F161" s="34" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="G161" s="7"/>
       <c r="H161" s="32" t="s">
@@ -42407,7 +42404,7 @@
       </c>
       <c r="E162" s="29"/>
       <c r="F162" s="34" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="G162" s="7"/>
       <c r="H162" s="32" t="s">
@@ -42440,7 +42437,7 @@
       </c>
       <c r="E163" s="29"/>
       <c r="F163" s="34" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="G163" s="7"/>
       <c r="H163" s="32" t="s">
@@ -42473,7 +42470,7 @@
       </c>
       <c r="E164" s="29"/>
       <c r="F164" s="34" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="G164" s="7"/>
       <c r="H164" s="32" t="s">
@@ -42506,7 +42503,7 @@
       </c>
       <c r="E165" s="29"/>
       <c r="F165" s="34" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="G165" s="7"/>
       <c r="H165" s="32" t="s">
@@ -42539,7 +42536,7 @@
       </c>
       <c r="E166" s="29"/>
       <c r="F166" s="34" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="G166" s="7"/>
       <c r="H166" s="32" t="s">
@@ -42574,7 +42571,7 @@
         <v>400</v>
       </c>
       <c r="F167" s="34" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="G167" s="7"/>
       <c r="H167" s="32" t="s">
@@ -42609,7 +42606,7 @@
         <v>403</v>
       </c>
       <c r="F168" s="34" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="G168" s="7"/>
       <c r="H168" s="32" t="s">
@@ -42642,7 +42639,7 @@
       </c>
       <c r="E169" s="29"/>
       <c r="F169" s="34" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="G169" s="7"/>
       <c r="H169" s="32" t="s">
@@ -42677,7 +42674,7 @@
         <v>408</v>
       </c>
       <c r="F170" s="34" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G170" s="7"/>
       <c r="H170" s="32" t="s">
@@ -42710,7 +42707,7 @@
       </c>
       <c r="E171" s="29"/>
       <c r="F171" s="34" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="G171" s="7"/>
       <c r="H171" s="32" t="s">
@@ -42743,7 +42740,7 @@
       </c>
       <c r="E172" s="29"/>
       <c r="F172" s="34" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="G172" s="7"/>
       <c r="H172" s="32" t="s">
@@ -42776,7 +42773,7 @@
       </c>
       <c r="E173" s="29"/>
       <c r="F173" s="34" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="G173" s="7"/>
       <c r="H173" s="32" t="s">
@@ -42809,7 +42806,7 @@
       </c>
       <c r="E174" s="29"/>
       <c r="F174" s="34" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="G174" s="7"/>
       <c r="H174" s="32" t="s">
@@ -42842,7 +42839,7 @@
       </c>
       <c r="E175" s="29"/>
       <c r="F175" s="32" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="G175" s="7"/>
       <c r="H175" s="32" t="s">
@@ -42875,7 +42872,7 @@
       </c>
       <c r="E176" s="29"/>
       <c r="F176" s="34" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="G176" s="7"/>
       <c r="H176" s="32" t="s">
@@ -42908,7 +42905,7 @@
       </c>
       <c r="E177" s="29"/>
       <c r="F177" s="34" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="G177" s="7"/>
       <c r="H177" s="32" t="s">
@@ -42941,7 +42938,7 @@
       </c>
       <c r="E178" s="29"/>
       <c r="F178" s="34" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="G178" s="7"/>
       <c r="H178" s="32" t="s">
@@ -42974,7 +42971,7 @@
       </c>
       <c r="E179" s="29"/>
       <c r="F179" s="34" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="G179" s="7"/>
       <c r="H179" s="32" t="s">
@@ -43007,7 +43004,7 @@
       </c>
       <c r="E180" s="29"/>
       <c r="F180" s="34" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="G180" s="7"/>
       <c r="H180" s="32" t="s">
@@ -43040,7 +43037,7 @@
         <v>430</v>
       </c>
       <c r="F181" s="34" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="G181" s="7"/>
       <c r="H181" s="32" t="s">
@@ -43073,7 +43070,7 @@
         <v>431</v>
       </c>
       <c r="F182" s="34" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="G182" s="7"/>
       <c r="H182" s="32" t="s">
@@ -43106,7 +43103,7 @@
       </c>
       <c r="E183" s="29"/>
       <c r="F183" s="34" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="G183" s="7"/>
       <c r="H183" s="32" t="s">
@@ -43139,7 +43136,7 @@
         <v>435</v>
       </c>
       <c r="F184" s="34" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="G184" s="7"/>
       <c r="H184" s="32" t="s">
@@ -43172,7 +43169,7 @@
         <v>436</v>
       </c>
       <c r="F185" s="34" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="G185" s="7"/>
       <c r="H185" s="32" t="s">
@@ -43205,7 +43202,7 @@
       </c>
       <c r="E186" s="29"/>
       <c r="F186" s="34" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="G186" s="7"/>
       <c r="H186" s="32" t="s">
@@ -43238,7 +43235,7 @@
         <v>440</v>
       </c>
       <c r="F187" s="34" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="G187" s="7"/>
       <c r="H187" s="32" t="s">
@@ -43271,7 +43268,7 @@
         <v>341</v>
       </c>
       <c r="F188" s="34" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="G188" s="7"/>
       <c r="H188" s="32" t="s">
@@ -43304,7 +43301,7 @@
         <v>442</v>
       </c>
       <c r="F189" s="34" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="G189" s="7"/>
       <c r="H189" s="32" t="s">
@@ -43337,7 +43334,7 @@
       </c>
       <c r="E190" s="29"/>
       <c r="F190" s="34" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="G190" s="7"/>
       <c r="H190" s="32" t="s">
@@ -43370,7 +43367,7 @@
         <v>446</v>
       </c>
       <c r="F191" s="34" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="G191" s="7"/>
       <c r="H191" s="32" t="s">
@@ -43403,7 +43400,7 @@
       </c>
       <c r="E192" s="29"/>
       <c r="F192" s="34" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="G192" s="7"/>
       <c r="H192" s="32" t="s">
@@ -43438,7 +43435,7 @@
         <v>451</v>
       </c>
       <c r="F193" s="34" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="G193" s="7"/>
       <c r="H193" s="32" t="s">
@@ -43471,7 +43468,7 @@
         <v>453</v>
       </c>
       <c r="F194" s="34" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="G194" s="7"/>
       <c r="H194" s="32" t="s">
@@ -43504,7 +43501,7 @@
         <v>454</v>
       </c>
       <c r="F195" s="34" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="G195" s="7"/>
       <c r="H195" s="32" t="s">
@@ -43537,7 +43534,7 @@
       </c>
       <c r="E196" s="29"/>
       <c r="F196" s="34" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="G196" s="7"/>
       <c r="H196" s="32" t="s">
@@ -43570,7 +43567,7 @@
       </c>
       <c r="E197" s="29"/>
       <c r="F197" s="34" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="G197" s="7"/>
       <c r="H197" s="32" t="s">
@@ -43603,7 +43600,7 @@
       </c>
       <c r="E198" s="29"/>
       <c r="F198" s="34" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="G198" s="7"/>
       <c r="H198" s="32" t="s">
@@ -43636,7 +43633,7 @@
         <v>343</v>
       </c>
       <c r="F199" s="34" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="G199" s="7"/>
       <c r="H199" s="32" t="s">
@@ -43669,7 +43666,7 @@
       </c>
       <c r="E200" s="29"/>
       <c r="F200" s="34" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="G200" s="7"/>
       <c r="H200" s="32" t="s">
@@ -43704,7 +43701,7 @@
         <v>466</v>
       </c>
       <c r="F201" s="34" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G201" s="7"/>
       <c r="H201" s="32" t="s">
@@ -43737,7 +43734,7 @@
       </c>
       <c r="E202" s="29"/>
       <c r="F202" s="34" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="G202" s="7"/>
       <c r="H202" s="32" t="s">
@@ -43770,7 +43767,7 @@
       </c>
       <c r="E203" s="29"/>
       <c r="F203" s="34" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G203" s="7"/>
       <c r="H203" s="32" t="s">
@@ -43803,7 +43800,7 @@
       </c>
       <c r="E204" s="29"/>
       <c r="F204" s="34" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="G204" s="7"/>
       <c r="H204" s="32" t="s">
@@ -43836,7 +43833,7 @@
         <v>474</v>
       </c>
       <c r="F205" s="34" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="G205" s="7"/>
       <c r="H205" s="32" t="s">
@@ -43869,7 +43866,7 @@
         <v>476</v>
       </c>
       <c r="F206" s="34" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="G206" s="7"/>
       <c r="H206" s="32" t="s">
@@ -43902,7 +43899,7 @@
         <v>478</v>
       </c>
       <c r="F207" s="34" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="G207" s="7"/>
       <c r="H207" s="32" t="s">
@@ -43937,7 +43934,7 @@
         <v>481</v>
       </c>
       <c r="F208" s="34" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="G208" s="7"/>
       <c r="H208" s="32" t="s">
@@ -43970,7 +43967,7 @@
       </c>
       <c r="E209" s="29"/>
       <c r="F209" s="34" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="G209" s="7"/>
       <c r="H209" s="32" t="s">
@@ -44003,7 +44000,7 @@
       </c>
       <c r="E210" s="29"/>
       <c r="F210" s="34" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="G210" s="7"/>
       <c r="H210" s="32" t="s">
@@ -44036,7 +44033,7 @@
       </c>
       <c r="E211" s="29"/>
       <c r="F211" s="34" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="G211" s="7"/>
       <c r="H211" s="32" t="s">
@@ -44069,7 +44066,7 @@
       </c>
       <c r="E212" s="29"/>
       <c r="F212" s="34" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="G212" s="7"/>
       <c r="H212" s="32" t="s">
@@ -44102,7 +44099,7 @@
       </c>
       <c r="E213" s="29"/>
       <c r="F213" s="34" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="G213" s="7"/>
       <c r="H213" s="32" t="s">
@@ -44135,7 +44132,7 @@
       </c>
       <c r="E214" s="29"/>
       <c r="F214" s="34" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="G214" s="7"/>
       <c r="H214" s="32" t="s">
@@ -44168,7 +44165,7 @@
       </c>
       <c r="E215" s="29"/>
       <c r="F215" s="34" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="G215" s="7"/>
       <c r="H215" s="32" t="s">
@@ -44201,7 +44198,7 @@
         <v>493</v>
       </c>
       <c r="F216" s="34" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="G216" s="7"/>
       <c r="H216" s="32" t="s">
@@ -44234,7 +44231,7 @@
         <v>495</v>
       </c>
       <c r="F217" s="34" t="s">
-        <v>847</v>
+        <v>845</v>
       </c>
       <c r="G217" s="7"/>
       <c r="H217" s="32" t="s">
@@ -44267,7 +44264,7 @@
         <v>497</v>
       </c>
       <c r="F218" s="34" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="G218" s="7"/>
       <c r="H218" s="32" t="s">
@@ -44300,7 +44297,7 @@
       </c>
       <c r="E219" s="29"/>
       <c r="F219" s="34" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="G219" s="7"/>
       <c r="H219" s="32" t="s">
@@ -44333,7 +44330,7 @@
       </c>
       <c r="E220" s="29"/>
       <c r="F220" s="34" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="G220" s="7"/>
       <c r="H220" s="32" t="s">
@@ -44366,7 +44363,7 @@
       </c>
       <c r="E221" s="29"/>
       <c r="F221" s="34" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="G221" s="7"/>
       <c r="H221" s="32" t="s">
@@ -44399,7 +44396,7 @@
         <v>505</v>
       </c>
       <c r="F222" s="34" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G222" s="7"/>
       <c r="H222" s="32" t="s">
@@ -44432,7 +44429,7 @@
       </c>
       <c r="E223" s="29"/>
       <c r="F223" s="34" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="G223" s="7"/>
       <c r="H223" s="32" t="s">
@@ -44465,7 +44462,7 @@
       </c>
       <c r="E224" s="29"/>
       <c r="F224" s="34" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="G224" s="7"/>
       <c r="H224" s="32" t="s">
@@ -44500,7 +44497,7 @@
         <v>511</v>
       </c>
       <c r="F225" s="34" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="G225" s="7"/>
       <c r="H225" s="32" t="s">
@@ -44533,7 +44530,7 @@
       </c>
       <c r="E226" s="29"/>
       <c r="F226" s="34" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G226" s="7"/>
       <c r="H226" s="32" t="s">
@@ -44566,7 +44563,7 @@
       </c>
       <c r="E227" s="29"/>
       <c r="F227" s="34" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="G227" s="7"/>
       <c r="H227" s="32" t="s">
@@ -44599,7 +44596,7 @@
       </c>
       <c r="E228" s="29"/>
       <c r="F228" s="34" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="G228" s="7"/>
       <c r="H228" s="32" t="s">
@@ -44632,7 +44629,7 @@
       </c>
       <c r="E229" s="29"/>
       <c r="F229" s="34" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="G229" s="7"/>
       <c r="H229" s="32" t="s">
@@ -44665,7 +44662,7 @@
       </c>
       <c r="E230" s="29"/>
       <c r="F230" s="34" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G230" s="7"/>
       <c r="H230" s="32" t="s">
@@ -44700,7 +44697,7 @@
         <v>525</v>
       </c>
       <c r="F231" s="34" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="G231" s="7"/>
       <c r="H231" s="32" t="s">
@@ -44733,7 +44730,7 @@
         <v>527</v>
       </c>
       <c r="F232" s="34" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="G232" s="7"/>
       <c r="H232" s="32" t="s">
@@ -44766,7 +44763,7 @@
       </c>
       <c r="E233" s="29"/>
       <c r="F233" s="34" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="G233" s="7"/>
       <c r="H233" s="32" t="s">
@@ -44799,7 +44796,7 @@
       </c>
       <c r="E234" s="29"/>
       <c r="F234" s="34" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="G234" s="7"/>
       <c r="H234" s="32" t="s">
@@ -44832,7 +44829,7 @@
       </c>
       <c r="E235" s="29"/>
       <c r="F235" s="34" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="G235" s="7"/>
       <c r="H235" s="32" t="s">
@@ -44865,7 +44862,7 @@
       </c>
       <c r="E236" s="29"/>
       <c r="F236" s="34" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="G236" s="7"/>
       <c r="H236" s="32" t="s">
@@ -44898,7 +44895,7 @@
       </c>
       <c r="E237" s="29"/>
       <c r="F237" s="34" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="G237" s="7"/>
       <c r="H237" s="32" t="s">
@@ -44931,7 +44928,7 @@
       </c>
       <c r="E238" s="29"/>
       <c r="F238" s="34" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="G238" s="7"/>
       <c r="H238" s="32" t="s">
@@ -44964,7 +44961,7 @@
       </c>
       <c r="E239" s="29"/>
       <c r="F239" s="34" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="G239" s="7"/>
       <c r="H239" s="32" t="s">
@@ -44997,7 +44994,7 @@
       </c>
       <c r="E240" s="29"/>
       <c r="F240" s="34" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="G240" s="7"/>
       <c r="H240" s="32" t="s">
@@ -45030,7 +45027,7 @@
       </c>
       <c r="E241" s="29"/>
       <c r="F241" s="34" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="G241" s="7"/>
       <c r="H241" s="32" t="s">
@@ -45063,7 +45060,7 @@
         <v>547</v>
       </c>
       <c r="F242" s="34" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="G242" s="7"/>
       <c r="H242" s="32" t="s">
@@ -45096,7 +45093,7 @@
         <v>549</v>
       </c>
       <c r="F243" s="34" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="G243" s="7"/>
       <c r="H243" s="32" t="s">
@@ -45129,7 +45126,7 @@
         <v>551</v>
       </c>
       <c r="F244" s="34" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G244" s="7"/>
       <c r="H244" s="32" t="s">
@@ -45162,7 +45159,7 @@
         <v>553</v>
       </c>
       <c r="F245" s="34" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="G245" s="7"/>
       <c r="H245" s="32" t="s">
@@ -45195,7 +45192,7 @@
         <v>555</v>
       </c>
       <c r="F246" s="34" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="G246" s="7"/>
       <c r="H246" s="32" t="s">
@@ -45228,7 +45225,7 @@
         <v>557</v>
       </c>
       <c r="F247" s="34" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="G247" s="7"/>
       <c r="H247" s="32" t="s">
@@ -45261,7 +45258,7 @@
         <v>559</v>
       </c>
       <c r="F248" s="34" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G248" s="7"/>
       <c r="H248" s="32" t="s">
@@ -45294,7 +45291,7 @@
         <v>561</v>
       </c>
       <c r="F249" s="34" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="G249" s="7"/>
       <c r="H249" s="32" t="s">
@@ -45327,7 +45324,7 @@
         <v>563</v>
       </c>
       <c r="F250" s="34" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="G250" s="7"/>
       <c r="H250" s="32" t="s">
@@ -45360,7 +45357,7 @@
         <v>565</v>
       </c>
       <c r="F251" s="34" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="G251" s="7"/>
       <c r="H251" s="32" t="s">
@@ -45393,7 +45390,7 @@
         <v>567</v>
       </c>
       <c r="F252" s="34" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="G252" s="7"/>
       <c r="H252" s="32" t="s">
@@ -45426,7 +45423,7 @@
         <v>569</v>
       </c>
       <c r="F253" s="34" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="G253" s="7"/>
       <c r="H253" s="32" t="s">
@@ -45459,7 +45456,7 @@
         <v>570</v>
       </c>
       <c r="F254" s="34" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="G254" s="7"/>
       <c r="H254" s="32" t="s">
@@ -45492,7 +45489,7 @@
       </c>
       <c r="E255" s="29"/>
       <c r="F255" s="34" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="G255" s="7"/>
       <c r="H255" s="32" t="s">
@@ -45525,7 +45522,7 @@
       </c>
       <c r="E256" s="29"/>
       <c r="F256" s="34" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="G256" s="7"/>
       <c r="H256" s="32" t="s">
@@ -45558,7 +45555,7 @@
         <v>576</v>
       </c>
       <c r="F257" s="34" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="G257" s="7"/>
       <c r="H257" s="32" t="s">
@@ -45591,7 +45588,7 @@
         <v>578</v>
       </c>
       <c r="F258" s="34" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="G258" s="7"/>
       <c r="H258" s="32" t="s">
@@ -45624,7 +45621,7 @@
         <v>580</v>
       </c>
       <c r="F259" s="34" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="G259" s="7"/>
       <c r="H259" s="32" t="s">
@@ -45657,7 +45654,7 @@
         <v>582</v>
       </c>
       <c r="F260" s="34" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
@@ -45688,7 +45685,7 @@
       </c>
       <c r="E261" s="29"/>
       <c r="F261" s="34" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
@@ -45719,7 +45716,7 @@
       </c>
       <c r="E262" s="29"/>
       <c r="F262" s="34" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="G262" s="7"/>
       <c r="H262" s="7"/>
@@ -45750,7 +45747,7 @@
       </c>
       <c r="E263" s="29"/>
       <c r="F263" s="34" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
@@ -45781,7 +45778,7 @@
       </c>
       <c r="E264" s="29"/>
       <c r="F264" s="34" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
@@ -45812,7 +45809,7 @@
       </c>
       <c r="E265" s="29"/>
       <c r="F265" s="34" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
@@ -45843,7 +45840,7 @@
       </c>
       <c r="E266" s="29"/>
       <c r="F266" s="34" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G266" s="7"/>
       <c r="H266" s="7"/>
@@ -45874,7 +45871,7 @@
       </c>
       <c r="E267" s="29"/>
       <c r="F267" s="34" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
@@ -45905,7 +45902,7 @@
       </c>
       <c r="E268" s="29"/>
       <c r="F268" s="34" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="G268" s="7"/>
       <c r="H268" s="7"/>
@@ -45936,7 +45933,7 @@
       </c>
       <c r="E269" s="29"/>
       <c r="F269" s="34" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
@@ -45967,7 +45964,7 @@
       </c>
       <c r="E270" s="29"/>
       <c r="F270" s="32" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
@@ -45998,7 +45995,7 @@
         <v>601</v>
       </c>
       <c r="F271" s="34" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
@@ -46031,7 +46028,7 @@
         <v>604</v>
       </c>
       <c r="F272" s="34" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
@@ -46064,7 +46061,7 @@
         <v>607</v>
       </c>
       <c r="F273" s="34" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
@@ -46095,7 +46092,7 @@
         <v>609</v>
       </c>
       <c r="F274" s="34" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
@@ -46126,7 +46123,7 @@
         <v>611</v>
       </c>
       <c r="F275" s="34" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
@@ -46159,7 +46156,7 @@
         <v>614</v>
       </c>
       <c r="F276" s="34" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
@@ -46190,7 +46187,7 @@
         <v>615</v>
       </c>
       <c r="F277" s="34" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
@@ -46221,7 +46218,7 @@
         <v>617</v>
       </c>
       <c r="F278" s="34" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
@@ -46252,7 +46249,7 @@
         <v>619</v>
       </c>
       <c r="F279" s="34" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
@@ -46283,7 +46280,7 @@
         <v>621</v>
       </c>
       <c r="F280" s="34" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
@@ -46314,7 +46311,7 @@
         <v>623</v>
       </c>
       <c r="F281" s="34" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
@@ -46345,7 +46342,7 @@
         <v>625</v>
       </c>
       <c r="F282" s="34" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
@@ -46376,7 +46373,7 @@
       </c>
       <c r="E283" s="29"/>
       <c r="F283" s="34" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
@@ -46407,7 +46404,7 @@
         <v>628</v>
       </c>
       <c r="F284" s="34" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
